--- a/model/data/descriptions-buy_price.xlsx
+++ b/model/data/descriptions-buy_price.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8252" uniqueCount="2689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8361" uniqueCount="2708">
   <si>
     <t>brand</t>
   </si>
@@ -8080,9 +8080,6 @@
     <t>مداد لب آدور مدل Waterproof شماره 401</t>
   </si>
   <si>
-    <t>۲٬۵۰۰٬۰۰۰</t>
-  </si>
-  <si>
     <t>کرم مرطوب کننده کامان مدل NORMAL حجم 75 میلی لیتر</t>
   </si>
   <si>
@@ -8090,6 +8087,66 @@
   </si>
   <si>
     <t>00324013</t>
+  </si>
+  <si>
+    <t>روغن آرگان محافظت‌کننده، شاداب‌کننده، تقویت‌کننده ، ترمیم‌کننده گلدن رز مدل ارگانیک SMOOTH &amp; SHINE مناسب موهای خشک، شکننده، آسیب دیده، انواع مو، کراتین شده، دکلره شده حجم 100 میلی‌لیتر</t>
+  </si>
+  <si>
+    <t>۹٬۰۰۰٬۰۰۰</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>محصول در اکسل تعریف نشده</t>
+  </si>
+  <si>
+    <t>رژگونه مایع مات ورشیپ مدل SMART CHEEK شماره C04</t>
+  </si>
+  <si>
+    <t>۱۱٬۰۰۰٬۰۰۰</t>
+  </si>
+  <si>
+    <t>ریمل حجم‌دهنده، حالت‌دهنده، بلند‌کننده، جداکننده گلدن رز مدل ICONIC LASH</t>
+  </si>
+  <si>
+    <t>۸٬۵۰۰٬۰۰۰</t>
+  </si>
+  <si>
+    <t>رژگونه مایع مات ورشیپ مدل SMART CHEEK شماره C02</t>
+  </si>
+  <si>
+    <t>رژگونه مایع مات ورشیپ مدل SMART CHEEK شماره C03</t>
+  </si>
+  <si>
+    <t>رژگونه مایع مات ورشیپ مدل SMART شماره C01</t>
+  </si>
+  <si>
+    <t>۱۰٬۰۰۰٬۰۰۰</t>
+  </si>
+  <si>
+    <t>محلول تثبیت‌کننده آرایش صورت ایلماز مدل FERESH حجم 120 میلی لیتر</t>
+  </si>
+  <si>
+    <t>۵۹۸٬۰۰۰</t>
+  </si>
+  <si>
+    <t>ریمل حجم‌دهنده گلدن رز مدل Power</t>
+  </si>
+  <si>
+    <t>۵٬۲۵۰٬۰۰۰</t>
+  </si>
+  <si>
+    <t>ریمل بلند‌کننده ضد آب گلدن رز مدل Touch</t>
+  </si>
+  <si>
+    <t>ریمل حجم‌دهنده گلدن رز مدل Eyeful</t>
+  </si>
+  <si>
+    <t>رژلب جامد گلدن رز مدل Mix شماره 1 مجموعه 4 عددی</t>
+  </si>
+  <si>
+    <t>۷٬۴۵۰٬۰۰۰</t>
   </si>
 </sst>
 </file>
@@ -8524,11 +8581,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AC2744"/>
+  <dimension ref="A1:AC2755"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="40.85546875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="50" style="4" customWidth="1"/>
     <col min="3" max="3" width="10.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.85546875" style="2" customWidth="1"/>
@@ -8615,7 +8672,7 @@
       </c>
       <c r="G2" s="13">
         <f t="shared" ref="G2:G59" si="0">IF(J2&lt;&gt;"",J2*$J$1,K2)</f>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H2" s="6">
         <v>200000</v>
@@ -8624,7 +8681,7 @@
         <v>2326</v>
       </c>
       <c r="K2" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
@@ -8643,7 +8700,7 @@
       <c r="E3" s="4"/>
       <c r="G3" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H3" s="6">
         <v>200000</v>
@@ -8652,7 +8709,7 @@
         <v>2326</v>
       </c>
       <c r="K3" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -8671,7 +8728,7 @@
       <c r="E4" s="4"/>
       <c r="G4" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H4" s="6">
         <v>200000</v>
@@ -8680,7 +8737,7 @@
         <v>2326</v>
       </c>
       <c r="K4" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
@@ -8699,7 +8756,7 @@
       <c r="E5" s="4"/>
       <c r="G5" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H5" s="6">
         <v>200000</v>
@@ -8708,7 +8765,7 @@
         <v>2326</v>
       </c>
       <c r="K5" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
@@ -8727,7 +8784,7 @@
       <c r="E6" s="4"/>
       <c r="G6" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H6" s="6">
         <v>200000</v>
@@ -8736,7 +8793,7 @@
         <v>2326</v>
       </c>
       <c r="K6" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
@@ -8755,7 +8812,7 @@
       <c r="E7" s="4"/>
       <c r="G7" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H7" s="6">
         <v>200000</v>
@@ -8764,7 +8821,7 @@
         <v>2326</v>
       </c>
       <c r="K7" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
@@ -8783,7 +8840,7 @@
       <c r="E8" s="4"/>
       <c r="G8" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H8" s="6">
         <v>200000</v>
@@ -8792,7 +8849,7 @@
         <v>2326</v>
       </c>
       <c r="K8" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
@@ -8811,7 +8868,7 @@
       <c r="E9" s="4"/>
       <c r="G9" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H9" s="6">
         <v>200000</v>
@@ -8820,7 +8877,7 @@
         <v>2326</v>
       </c>
       <c r="K9" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
@@ -8839,7 +8896,7 @@
       <c r="E10" s="4"/>
       <c r="G10" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H10" s="6">
         <v>200000</v>
@@ -8848,7 +8905,7 @@
         <v>2326</v>
       </c>
       <c r="K10" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
@@ -8867,7 +8924,7 @@
       <c r="E11" s="4"/>
       <c r="G11" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H11" s="6">
         <v>207900</v>
@@ -8876,7 +8933,7 @@
         <v>2326</v>
       </c>
       <c r="K11" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
@@ -8895,7 +8952,7 @@
       <c r="E12" s="4"/>
       <c r="G12" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H12" s="6">
         <v>207900</v>
@@ -8904,7 +8961,7 @@
         <v>2326</v>
       </c>
       <c r="K12" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
@@ -8923,7 +8980,7 @@
       <c r="E13" s="4"/>
       <c r="G13" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H13" s="6">
         <v>200000</v>
@@ -8932,7 +8989,7 @@
         <v>2326</v>
       </c>
       <c r="K13" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.25">
@@ -8951,7 +9008,7 @@
       <c r="E14" s="4"/>
       <c r="G14" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H14" s="6">
         <v>207900</v>
@@ -8960,7 +9017,7 @@
         <v>2326</v>
       </c>
       <c r="K14" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
@@ -8979,7 +9036,7 @@
       <c r="E15" s="4"/>
       <c r="G15" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H15" s="6">
         <v>200000</v>
@@ -8988,7 +9045,7 @@
         <v>2326</v>
       </c>
       <c r="K15" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
@@ -9007,7 +9064,7 @@
       <c r="E16" s="4"/>
       <c r="G16" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H16" s="6">
         <v>207900</v>
@@ -9016,7 +9073,7 @@
         <v>2326</v>
       </c>
       <c r="K16" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -9035,7 +9092,7 @@
       <c r="E17" s="4"/>
       <c r="G17" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H17" s="6">
         <v>200000</v>
@@ -9044,7 +9101,7 @@
         <v>2326</v>
       </c>
       <c r="K17" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -9063,7 +9120,7 @@
       <c r="E18" s="4"/>
       <c r="G18" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H18" s="6">
         <v>200000</v>
@@ -9072,7 +9129,7 @@
         <v>2326</v>
       </c>
       <c r="K18" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -9091,7 +9148,7 @@
       <c r="E19" s="4"/>
       <c r="G19" s="13">
         <f t="shared" si="0"/>
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
       <c r="H19" s="6">
         <v>200000</v>
@@ -9100,7 +9157,7 @@
         <v>2326</v>
       </c>
       <c r="K19" s="6">
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -9119,7 +9176,7 @@
       <c r="E20" s="4"/>
       <c r="G20" s="13">
         <f t="shared" si="0"/>
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
       <c r="H20" s="6">
         <v>200000</v>
@@ -9128,7 +9185,7 @@
         <v>2326</v>
       </c>
       <c r="K20" s="6">
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -9147,7 +9204,7 @@
       <c r="E21" s="4"/>
       <c r="G21" s="13">
         <f t="shared" si="0"/>
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
       <c r="H21" s="6">
         <v>200000</v>
@@ -9156,7 +9213,7 @@
         <v>2326</v>
       </c>
       <c r="K21" s="6">
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -9175,7 +9232,7 @@
       <c r="E22" s="4"/>
       <c r="G22" s="13">
         <f t="shared" si="0"/>
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
       <c r="H22" s="6">
         <v>200000</v>
@@ -9184,7 +9241,7 @@
         <v>2326</v>
       </c>
       <c r="K22" s="6">
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -9203,7 +9260,7 @@
       <c r="E23" s="4"/>
       <c r="G23" s="13">
         <f t="shared" si="0"/>
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
       <c r="H23" s="6">
         <v>200000</v>
@@ -9212,7 +9269,7 @@
         <v>2326</v>
       </c>
       <c r="K23" s="6">
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -9231,7 +9288,7 @@
       <c r="E24" s="4"/>
       <c r="G24" s="13">
         <f t="shared" si="0"/>
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
       <c r="H24" s="6">
         <v>200000</v>
@@ -9240,7 +9297,7 @@
         <v>2326</v>
       </c>
       <c r="K24" s="6">
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -9259,7 +9316,7 @@
       <c r="E25" s="4"/>
       <c r="G25" s="13">
         <f t="shared" si="0"/>
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
       <c r="H25" s="6">
         <v>200000</v>
@@ -9268,7 +9325,7 @@
         <v>2326</v>
       </c>
       <c r="K25" s="6">
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -9287,7 +9344,7 @@
       <c r="E26" s="4"/>
       <c r="G26" s="13">
         <f t="shared" si="0"/>
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
       <c r="H26" s="6">
         <v>200000</v>
@@ -9296,7 +9353,7 @@
         <v>2326</v>
       </c>
       <c r="K26" s="6">
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -9315,7 +9372,7 @@
       <c r="E27" s="4"/>
       <c r="G27" s="13">
         <f t="shared" si="0"/>
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
       <c r="H27" s="6">
         <v>200000</v>
@@ -9324,7 +9381,7 @@
         <v>2326</v>
       </c>
       <c r="K27" s="6">
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -9343,7 +9400,7 @@
       <c r="E28" s="4"/>
       <c r="G28" s="13">
         <f t="shared" si="0"/>
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
       <c r="H28" s="6">
         <v>207900</v>
@@ -9352,7 +9409,7 @@
         <v>2326</v>
       </c>
       <c r="K28" s="6">
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -9371,7 +9428,7 @@
       <c r="E29" s="4"/>
       <c r="G29" s="13">
         <f t="shared" si="0"/>
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
       <c r="H29" s="6">
         <v>202300</v>
@@ -9380,7 +9437,7 @@
         <v>2326</v>
       </c>
       <c r="K29" s="6">
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -9399,7 +9456,7 @@
       <c r="E30" s="4"/>
       <c r="G30" s="13">
         <f t="shared" si="0"/>
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
       <c r="H30" s="6">
         <v>200000</v>
@@ -9408,7 +9465,7 @@
         <v>2326</v>
       </c>
       <c r="K30" s="6">
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -9427,7 +9484,7 @@
       <c r="E31" s="4"/>
       <c r="G31" s="13">
         <f t="shared" si="0"/>
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
       <c r="H31" s="6">
         <v>200000</v>
@@ -9436,7 +9493,7 @@
         <v>2326</v>
       </c>
       <c r="K31" s="6">
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -9455,7 +9512,7 @@
       <c r="E32" s="4"/>
       <c r="G32" s="13">
         <f t="shared" si="0"/>
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
       <c r="H32" s="6">
         <v>207900</v>
@@ -9464,7 +9521,7 @@
         <v>2326</v>
       </c>
       <c r="K32" s="6">
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -9483,7 +9540,7 @@
       <c r="E33" s="4"/>
       <c r="G33" s="13">
         <f t="shared" si="0"/>
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
       <c r="H33" s="6">
         <v>207900</v>
@@ -9492,7 +9549,7 @@
         <v>2326</v>
       </c>
       <c r="K33" s="6">
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -9511,7 +9568,7 @@
       <c r="E34" s="4"/>
       <c r="G34" s="13">
         <f t="shared" si="0"/>
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
       <c r="H34" s="6">
         <v>218400</v>
@@ -9520,7 +9577,7 @@
         <v>2326</v>
       </c>
       <c r="K34" s="6">
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -9539,7 +9596,7 @@
       <c r="E35" s="4"/>
       <c r="G35" s="13">
         <f t="shared" si="0"/>
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
       <c r="H35" s="6">
         <v>203000</v>
@@ -9548,7 +9605,7 @@
         <v>2326</v>
       </c>
       <c r="K35" s="6">
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -9567,7 +9624,7 @@
       <c r="E36" s="4"/>
       <c r="G36" s="13">
         <f t="shared" si="0"/>
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
       <c r="H36" s="6">
         <v>200000</v>
@@ -9576,7 +9633,7 @@
         <v>2326</v>
       </c>
       <c r="K36" s="6">
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -9595,7 +9652,7 @@
       <c r="E37" s="4"/>
       <c r="G37" s="13">
         <f t="shared" si="0"/>
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
       <c r="H37" s="6">
         <v>200000</v>
@@ -9604,7 +9661,7 @@
         <v>2326</v>
       </c>
       <c r="K37" s="6">
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -9623,7 +9680,7 @@
       <c r="E38" s="4"/>
       <c r="G38" s="13">
         <f t="shared" si="0"/>
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
       <c r="H38" s="6">
         <v>200000</v>
@@ -9632,7 +9689,7 @@
         <v>2326</v>
       </c>
       <c r="K38" s="6">
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -9651,7 +9708,7 @@
       <c r="E39" s="4"/>
       <c r="G39" s="13">
         <f t="shared" si="0"/>
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
       <c r="H39" s="6">
         <v>200000</v>
@@ -9660,7 +9717,7 @@
         <v>2326</v>
       </c>
       <c r="K39" s="6">
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -9679,7 +9736,7 @@
       <c r="E40" s="4"/>
       <c r="G40" s="13">
         <f t="shared" si="0"/>
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
       <c r="H40" s="6">
         <v>207900</v>
@@ -9688,7 +9745,7 @@
         <v>2326</v>
       </c>
       <c r="K40" s="6">
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -9707,7 +9764,7 @@
       <c r="E41" s="4"/>
       <c r="G41" s="13">
         <f t="shared" si="0"/>
-        <v>2026700</v>
+        <v>2818700</v>
       </c>
       <c r="H41" s="6">
         <v>200000</v>
@@ -9716,7 +9773,7 @@
         <v>2326</v>
       </c>
       <c r="K41" s="6">
-        <v>2026700</v>
+        <v>2818700</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -9735,7 +9792,7 @@
       <c r="E42" s="4"/>
       <c r="G42" s="13">
         <f t="shared" si="0"/>
-        <v>2026700</v>
+        <v>2818700</v>
       </c>
       <c r="H42" s="6">
         <v>200000</v>
@@ -9744,7 +9801,7 @@
         <v>2326</v>
       </c>
       <c r="K42" s="6">
-        <v>2026700</v>
+        <v>2818700</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -9763,7 +9820,7 @@
       <c r="E43" s="4"/>
       <c r="G43" s="13">
         <f t="shared" si="0"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H43" s="6">
         <v>207900</v>
@@ -9772,7 +9829,7 @@
         <v>2326</v>
       </c>
       <c r="K43" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -9791,7 +9848,7 @@
       <c r="E44" s="4"/>
       <c r="G44" s="13">
         <f t="shared" si="0"/>
-        <v>1324060</v>
+        <v>1997600</v>
       </c>
       <c r="H44" s="6">
         <v>200000</v>
@@ -9800,7 +9857,7 @@
         <v>2326</v>
       </c>
       <c r="K44" s="6">
-        <v>1324060</v>
+        <v>1997600</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -9819,7 +9876,7 @@
       <c r="E45" s="4"/>
       <c r="G45" s="13">
         <f t="shared" si="0"/>
-        <v>1324060</v>
+        <v>1997600</v>
       </c>
       <c r="H45" s="6">
         <v>200000</v>
@@ -9828,7 +9885,7 @@
         <v>2326</v>
       </c>
       <c r="K45" s="6">
-        <v>1324060</v>
+        <v>1997600</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -9847,7 +9904,7 @@
       <c r="E46" s="4"/>
       <c r="G46" s="13">
         <f t="shared" si="0"/>
-        <v>1324060</v>
+        <v>1997600</v>
       </c>
       <c r="H46" s="6">
         <v>200000</v>
@@ -9856,7 +9913,7 @@
         <v>2326</v>
       </c>
       <c r="K46" s="6">
-        <v>1324060</v>
+        <v>1997600</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -9875,7 +9932,7 @@
       <c r="E47" s="4"/>
       <c r="G47" s="13">
         <f t="shared" si="0"/>
-        <v>1324060</v>
+        <v>1997600</v>
       </c>
       <c r="H47" s="6">
         <v>200000</v>
@@ -9884,7 +9941,7 @@
         <v>2326</v>
       </c>
       <c r="K47" s="6">
-        <v>1324060</v>
+        <v>1997600</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -9903,7 +9960,7 @@
       <c r="E48" s="4"/>
       <c r="G48" s="13">
         <f t="shared" si="0"/>
-        <v>1324060</v>
+        <v>1997600</v>
       </c>
       <c r="H48" s="6">
         <v>200000</v>
@@ -9912,7 +9969,7 @@
         <v>2326</v>
       </c>
       <c r="K48" s="6">
-        <v>1324060</v>
+        <v>1997600</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -9931,7 +9988,7 @@
       <c r="E49" s="4"/>
       <c r="G49" s="13">
         <f t="shared" si="0"/>
-        <v>2087630</v>
+        <v>2664360</v>
       </c>
       <c r="H49" s="6">
         <v>200000</v>
@@ -9940,7 +9997,7 @@
         <v>2326</v>
       </c>
       <c r="K49" s="6">
-        <v>2087630</v>
+        <v>2664360</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -9959,7 +10016,7 @@
       <c r="E50" s="4"/>
       <c r="G50" s="13">
         <f t="shared" si="0"/>
-        <v>2087630</v>
+        <v>2664360</v>
       </c>
       <c r="H50" s="6">
         <v>200000</v>
@@ -9968,7 +10025,7 @@
         <v>2326</v>
       </c>
       <c r="K50" s="6">
-        <v>2087630</v>
+        <v>2664360</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -9987,7 +10044,7 @@
       <c r="E51" s="4"/>
       <c r="G51" s="13">
         <f t="shared" si="0"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H51" s="6">
         <v>207900</v>
@@ -9996,7 +10053,7 @@
         <v>2326</v>
       </c>
       <c r="K51" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -10017,7 +10074,7 @@
       </c>
       <c r="G52" s="13">
         <f t="shared" si="0"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H52" s="6">
         <v>200000</v>
@@ -10026,7 +10083,7 @@
         <v>2326</v>
       </c>
       <c r="K52" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -10047,7 +10104,7 @@
       </c>
       <c r="G53" s="13">
         <f t="shared" si="0"/>
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
       <c r="H53" s="6">
         <v>200000</v>
@@ -10056,7 +10113,7 @@
         <v>2326</v>
       </c>
       <c r="K53" s="6">
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -10077,7 +10134,7 @@
       </c>
       <c r="G54" s="13">
         <f t="shared" si="0"/>
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
       <c r="H54" s="6">
         <v>200000</v>
@@ -10086,7 +10143,7 @@
         <v>2326</v>
       </c>
       <c r="K54" s="6">
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -10107,7 +10164,7 @@
       </c>
       <c r="G55" s="13">
         <f t="shared" si="0"/>
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
       <c r="H55" s="6">
         <v>200000</v>
@@ -10116,7 +10173,7 @@
         <v>2326</v>
       </c>
       <c r="K55" s="6">
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -10137,7 +10194,7 @@
       </c>
       <c r="G56" s="13">
         <f t="shared" si="0"/>
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
       <c r="H56" s="6">
         <v>200000</v>
@@ -10146,7 +10203,7 @@
         <v>2326</v>
       </c>
       <c r="K56" s="6">
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -10167,7 +10224,7 @@
       </c>
       <c r="G57" s="13">
         <f t="shared" si="0"/>
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
       <c r="H57" s="6">
         <v>200000</v>
@@ -10176,7 +10233,7 @@
         <v>2326</v>
       </c>
       <c r="K57" s="6">
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -10197,7 +10254,7 @@
       </c>
       <c r="G58" s="13">
         <f t="shared" si="0"/>
-        <v>1876430</v>
+        <v>2607500</v>
       </c>
       <c r="H58" s="6">
         <v>200000</v>
@@ -10206,7 +10263,7 @@
         <v>2326</v>
       </c>
       <c r="K58" s="6">
-        <v>1876430</v>
+        <v>2607500</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -10227,7 +10284,7 @@
       </c>
       <c r="G59" s="13">
         <f t="shared" si="0"/>
-        <v>3379200</v>
+        <v>4708000</v>
       </c>
       <c r="H59" s="6">
         <v>266000</v>
@@ -10236,7 +10293,7 @@
         <v>2326</v>
       </c>
       <c r="K59" s="6">
-        <v>3379200</v>
+        <v>4708000</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -10336,7 +10393,7 @@
       </c>
       <c r="G63" s="13">
         <f t="shared" si="1"/>
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
       <c r="H63" s="6">
         <v>200000</v>
@@ -10345,7 +10402,7 @@
         <v>2326</v>
       </c>
       <c r="K63" s="6">
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -10366,7 +10423,7 @@
       </c>
       <c r="G64" s="13">
         <f t="shared" si="1"/>
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
       <c r="H64" s="6">
         <v>200000</v>
@@ -10375,7 +10432,7 @@
         <v>2326</v>
       </c>
       <c r="K64" s="6">
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -10396,7 +10453,7 @@
       </c>
       <c r="G65" s="13">
         <f t="shared" si="1"/>
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
       <c r="H65" s="6">
         <v>200000</v>
@@ -10405,7 +10462,7 @@
         <v>2326</v>
       </c>
       <c r="K65" s="6">
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -10426,7 +10483,7 @@
       </c>
       <c r="G66" s="13">
         <f t="shared" si="1"/>
-        <v>2968980</v>
+        <v>4142760</v>
       </c>
       <c r="H66" s="6">
         <v>261800</v>
@@ -10435,7 +10492,7 @@
         <v>2326</v>
       </c>
       <c r="K66" s="6">
-        <v>2968980</v>
+        <v>4142760</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -10456,7 +10513,7 @@
       </c>
       <c r="G67" s="13">
         <f t="shared" si="1"/>
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
       <c r="H67" s="6">
         <v>200000</v>
@@ -10465,7 +10522,7 @@
         <v>2326</v>
       </c>
       <c r="K67" s="6">
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -10486,7 +10543,7 @@
       </c>
       <c r="G68" s="13">
         <f t="shared" si="1"/>
-        <v>2968980</v>
+        <v>4142760</v>
       </c>
       <c r="H68" s="6">
         <v>277900</v>
@@ -10495,7 +10552,7 @@
         <v>2326</v>
       </c>
       <c r="K68" s="6">
-        <v>2968980</v>
+        <v>4142760</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -10516,7 +10573,7 @@
       </c>
       <c r="G69" s="13">
         <f t="shared" si="1"/>
-        <v>2968980</v>
+        <v>4142760</v>
       </c>
       <c r="H69" s="6">
         <v>262500</v>
@@ -10525,7 +10582,7 @@
         <v>2326</v>
       </c>
       <c r="K69" s="6">
-        <v>2968980</v>
+        <v>4142760</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -10546,7 +10603,7 @@
       </c>
       <c r="G70" s="13">
         <f t="shared" si="1"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H70" s="6">
         <v>200000</v>
@@ -10555,7 +10612,7 @@
         <v>2326</v>
       </c>
       <c r="K70" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -10576,7 +10633,7 @@
       </c>
       <c r="G71" s="13">
         <f t="shared" si="1"/>
-        <v>1876430</v>
+        <v>2607500</v>
       </c>
       <c r="H71" s="6">
         <v>200000</v>
@@ -10585,7 +10642,7 @@
         <v>2326</v>
       </c>
       <c r="K71" s="6">
-        <v>1876430</v>
+        <v>2607500</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -10606,7 +10663,7 @@
       </c>
       <c r="G72" s="13">
         <f t="shared" si="1"/>
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
       <c r="H72" s="6">
         <v>200000</v>
@@ -10615,7 +10672,7 @@
         <v>2326</v>
       </c>
       <c r="K72" s="6">
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -10636,7 +10693,7 @@
       </c>
       <c r="G73" s="13">
         <f t="shared" si="1"/>
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
       <c r="H73" s="6">
         <v>200000</v>
@@ -10645,7 +10702,7 @@
         <v>2326</v>
       </c>
       <c r="K73" s="6">
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -10666,7 +10723,7 @@
       </c>
       <c r="G74" s="13">
         <f t="shared" si="1"/>
-        <v>1876430</v>
+        <v>2607500</v>
       </c>
       <c r="H74" s="6">
         <v>200000</v>
@@ -10675,7 +10732,7 @@
         <v>2326</v>
       </c>
       <c r="K74" s="6">
-        <v>1876430</v>
+        <v>2607500</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -10696,7 +10753,7 @@
       </c>
       <c r="G75" s="13">
         <f t="shared" si="1"/>
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
       <c r="H75" s="6">
         <v>200000</v>
@@ -10705,7 +10762,7 @@
         <v>2326</v>
       </c>
       <c r="K75" s="6">
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -10726,7 +10783,7 @@
       </c>
       <c r="G76" s="13">
         <f t="shared" si="1"/>
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
       <c r="H76" s="6">
         <v>200000</v>
@@ -10735,7 +10792,7 @@
         <v>2326</v>
       </c>
       <c r="K76" s="6">
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -10756,7 +10813,7 @@
       </c>
       <c r="G77" s="13">
         <f t="shared" si="1"/>
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
       <c r="H77" s="6">
         <v>200000</v>
@@ -10765,7 +10822,7 @@
         <v>2326</v>
       </c>
       <c r="K77" s="6">
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -10786,7 +10843,7 @@
       </c>
       <c r="G78" s="13">
         <f t="shared" si="1"/>
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
       <c r="H78" s="6">
         <v>200000</v>
@@ -10795,7 +10852,7 @@
         <v>2326</v>
       </c>
       <c r="K78" s="6">
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -10816,7 +10873,7 @@
       </c>
       <c r="G79" s="13">
         <f t="shared" si="1"/>
-        <v>4505600</v>
+        <v>6256800</v>
       </c>
       <c r="H79" s="6">
         <v>303100</v>
@@ -10825,7 +10882,7 @@
         <v>2326</v>
       </c>
       <c r="K79" s="6">
-        <v>4505600</v>
+        <v>6256800</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -10846,7 +10903,7 @@
       </c>
       <c r="G80" s="13">
         <f t="shared" si="1"/>
-        <v>2968980</v>
+        <v>4142760</v>
       </c>
       <c r="H80" s="6">
         <v>263900</v>
@@ -10855,7 +10912,7 @@
         <v>2326</v>
       </c>
       <c r="K80" s="6">
-        <v>2968980</v>
+        <v>4142760</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -10876,7 +10933,7 @@
       </c>
       <c r="G81" s="13">
         <f t="shared" si="1"/>
-        <v>2968980</v>
+        <v>4142760</v>
       </c>
       <c r="H81" s="6">
         <v>263200</v>
@@ -10885,7 +10942,7 @@
         <v>2326</v>
       </c>
       <c r="K81" s="6">
-        <v>2968980</v>
+        <v>4142760</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -10906,7 +10963,7 @@
       </c>
       <c r="G82" s="13">
         <f t="shared" si="1"/>
-        <v>1876430</v>
+        <v>2607500</v>
       </c>
       <c r="H82" s="6">
         <v>200000</v>
@@ -10915,7 +10972,7 @@
         <v>2326</v>
       </c>
       <c r="K82" s="6">
-        <v>1876430</v>
+        <v>2607500</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -10936,7 +10993,7 @@
       </c>
       <c r="G83" s="13">
         <f t="shared" si="1"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H83" s="6">
         <v>200000</v>
@@ -10945,7 +11002,7 @@
         <v>2326</v>
       </c>
       <c r="K83" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -10966,7 +11023,7 @@
       </c>
       <c r="G84" s="13">
         <f t="shared" si="1"/>
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
       <c r="H84" s="6">
         <v>200000</v>
@@ -10975,7 +11032,7 @@
         <v>2326</v>
       </c>
       <c r="K84" s="6">
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -10996,7 +11053,7 @@
       </c>
       <c r="G85" s="13">
         <f t="shared" si="1"/>
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
       <c r="H85" s="6">
         <v>200000</v>
@@ -11005,7 +11062,7 @@
         <v>2326</v>
       </c>
       <c r="K85" s="6">
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -11026,7 +11083,7 @@
       </c>
       <c r="G86" s="13">
         <f t="shared" si="1"/>
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
       <c r="H86" s="6">
         <v>200000</v>
@@ -11035,7 +11092,7 @@
         <v>2326</v>
       </c>
       <c r="K86" s="6">
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -11056,7 +11113,7 @@
       </c>
       <c r="G87" s="13">
         <f t="shared" si="1"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H87" s="6">
         <v>200000</v>
@@ -11065,7 +11122,7 @@
         <v>2326</v>
       </c>
       <c r="K87" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -11086,7 +11143,7 @@
       </c>
       <c r="G88" s="13">
         <f t="shared" si="1"/>
-        <v>1876430</v>
+        <v>2607500</v>
       </c>
       <c r="H88" s="6">
         <v>200000</v>
@@ -11095,7 +11152,7 @@
         <v>2326</v>
       </c>
       <c r="K88" s="6">
-        <v>1876430</v>
+        <v>2607500</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -11116,7 +11173,7 @@
       </c>
       <c r="G89" s="13">
         <f t="shared" si="1"/>
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
       <c r="H89" s="6">
         <v>200000</v>
@@ -11125,7 +11182,7 @@
         <v>2326</v>
       </c>
       <c r="K89" s="6">
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -11146,7 +11203,7 @@
       </c>
       <c r="G90" s="13">
         <f t="shared" si="1"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H90" s="6">
         <v>200000</v>
@@ -11155,7 +11212,7 @@
         <v>2326</v>
       </c>
       <c r="K90" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -11176,7 +11233,7 @@
       </c>
       <c r="G91" s="13">
         <f t="shared" si="1"/>
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
       <c r="H91" s="6">
         <v>200000</v>
@@ -11185,7 +11242,7 @@
         <v>2326</v>
       </c>
       <c r="K91" s="6">
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -11206,7 +11263,7 @@
       </c>
       <c r="G92" s="13">
         <f t="shared" si="1"/>
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
       <c r="H92" s="6">
         <v>200000</v>
@@ -11215,7 +11272,7 @@
         <v>2326</v>
       </c>
       <c r="K92" s="6">
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -11236,7 +11293,7 @@
       </c>
       <c r="G93" s="13">
         <f t="shared" si="1"/>
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
       <c r="H93" s="6">
         <v>200000</v>
@@ -11245,7 +11302,7 @@
         <v>2326</v>
       </c>
       <c r="K93" s="6">
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -11266,7 +11323,7 @@
       </c>
       <c r="G94" s="13">
         <f t="shared" si="1"/>
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
       <c r="H94" s="6">
         <v>200000</v>
@@ -11275,7 +11332,7 @@
         <v>2326</v>
       </c>
       <c r="K94" s="6">
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -11296,7 +11353,7 @@
       </c>
       <c r="G95" s="13">
         <f t="shared" si="1"/>
-        <v>2968980</v>
+        <v>4142760</v>
       </c>
       <c r="H95" s="6">
         <v>266000</v>
@@ -11305,7 +11362,7 @@
         <v>2326</v>
       </c>
       <c r="K95" s="6">
-        <v>2968980</v>
+        <v>4142760</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -11326,7 +11383,7 @@
       </c>
       <c r="G96" s="13">
         <f t="shared" si="1"/>
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
       <c r="H96" s="6">
         <v>200000</v>
@@ -11335,7 +11392,7 @@
         <v>2326</v>
       </c>
       <c r="K96" s="6">
-        <v>1704680</v>
+        <v>2383540</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -11356,7 +11413,7 @@
       </c>
       <c r="G97" s="13">
         <f t="shared" si="1"/>
-        <v>3660800</v>
+        <v>5104000</v>
       </c>
       <c r="H97" s="6">
         <v>282100</v>
@@ -11365,7 +11422,7 @@
         <v>2326</v>
       </c>
       <c r="K97" s="6">
-        <v>3660800</v>
+        <v>5104000</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -11386,7 +11443,7 @@
       </c>
       <c r="G98" s="13">
         <f t="shared" si="1"/>
-        <v>5112800</v>
+        <v>7110400</v>
       </c>
       <c r="H98" s="6">
         <v>415800</v>
@@ -11395,7 +11452,7 @@
         <v>2326</v>
       </c>
       <c r="K98" s="6">
-        <v>5112800</v>
+        <v>7110400</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -12694,7 +12751,7 @@
       </c>
       <c r="G146" s="13">
         <f t="shared" si="3"/>
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
       <c r="H146" s="6">
         <v>200000</v>
@@ -12703,7 +12760,7 @@
         <v>2326</v>
       </c>
       <c r="K146" s="6">
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -12724,7 +12781,7 @@
       </c>
       <c r="G147" s="13">
         <f t="shared" si="3"/>
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
       <c r="H147" s="6">
         <v>200000</v>
@@ -12733,7 +12790,7 @@
         <v>2326</v>
       </c>
       <c r="K147" s="6">
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -12754,7 +12811,7 @@
       </c>
       <c r="G148" s="13">
         <f t="shared" si="3"/>
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
       <c r="H148" s="6">
         <v>200000</v>
@@ -12763,7 +12820,7 @@
         <v>2326</v>
       </c>
       <c r="K148" s="6">
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -12784,7 +12841,7 @@
       </c>
       <c r="G149" s="13">
         <f t="shared" si="3"/>
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
       <c r="H149" s="6">
         <v>200000</v>
@@ -12793,7 +12850,7 @@
         <v>2326</v>
       </c>
       <c r="K149" s="6">
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -12814,7 +12871,7 @@
       </c>
       <c r="G150" s="13">
         <f t="shared" si="3"/>
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
       <c r="H150" s="6">
         <v>200000</v>
@@ -12823,7 +12880,7 @@
         <v>2326</v>
       </c>
       <c r="K150" s="6">
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -12844,7 +12901,7 @@
       </c>
       <c r="G151" s="13">
         <f t="shared" si="3"/>
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
       <c r="H151" s="6">
         <v>200000</v>
@@ -12853,7 +12910,7 @@
         <v>2326</v>
       </c>
       <c r="K151" s="6">
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -12874,7 +12931,7 @@
       </c>
       <c r="G152" s="13">
         <f t="shared" si="3"/>
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
       <c r="H152" s="6">
         <v>200000</v>
@@ -12883,7 +12940,7 @@
         <v>2326</v>
       </c>
       <c r="K152" s="6">
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -12904,7 +12961,7 @@
       </c>
       <c r="G153" s="13">
         <f t="shared" si="3"/>
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
       <c r="H153" s="6">
         <v>200000</v>
@@ -12913,7 +12970,7 @@
         <v>2326</v>
       </c>
       <c r="K153" s="6">
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -12934,7 +12991,7 @@
       </c>
       <c r="G154" s="13">
         <f t="shared" si="3"/>
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
       <c r="H154" s="6">
         <v>200000</v>
@@ -12943,7 +13000,7 @@
         <v>2326</v>
       </c>
       <c r="K154" s="6">
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -12964,7 +13021,7 @@
       </c>
       <c r="G155" s="13">
         <f t="shared" si="3"/>
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
       <c r="H155" s="6">
         <v>200000</v>
@@ -12973,7 +13030,7 @@
         <v>2326</v>
       </c>
       <c r="K155" s="6">
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -12994,7 +13051,7 @@
       </c>
       <c r="G156" s="13">
         <f t="shared" si="3"/>
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
       <c r="H156" s="6">
         <v>200000</v>
@@ -13003,7 +13060,7 @@
         <v>2326</v>
       </c>
       <c r="K156" s="6">
-        <v>2455200</v>
+        <v>2669040</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -13024,7 +13081,7 @@
       </c>
       <c r="G157" s="13">
         <f t="shared" si="3"/>
-        <v>2688840</v>
+        <v>3001680</v>
       </c>
       <c r="H157" s="6">
         <v>202300</v>
@@ -13033,7 +13090,7 @@
         <v>2326</v>
       </c>
       <c r="K157" s="6">
-        <v>2688840</v>
+        <v>3001680</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -13054,7 +13111,7 @@
       </c>
       <c r="G158" s="13">
         <f t="shared" si="3"/>
-        <v>2003760</v>
+        <v>2185920</v>
       </c>
       <c r="H158" s="6">
         <v>200000</v>
@@ -13063,7 +13120,7 @@
         <v>2326</v>
       </c>
       <c r="K158" s="6">
-        <v>2003760</v>
+        <v>2185920</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -13084,7 +13141,7 @@
       </c>
       <c r="G159" s="13">
         <f t="shared" si="3"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H159" s="6">
         <v>200000</v>
@@ -13093,7 +13150,7 @@
         <v>2326</v>
       </c>
       <c r="K159" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -13114,7 +13171,7 @@
       </c>
       <c r="G160" s="13">
         <f t="shared" si="3"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H160" s="6">
         <v>184800</v>
@@ -13123,7 +13180,7 @@
         <v>2326</v>
       </c>
       <c r="K160" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -13144,7 +13201,7 @@
       </c>
       <c r="G161" s="13">
         <f t="shared" si="3"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H161" s="6">
         <v>188300</v>
@@ -13153,7 +13210,7 @@
         <v>2326</v>
       </c>
       <c r="K161" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -13174,7 +13231,7 @@
       </c>
       <c r="G162" s="13">
         <f t="shared" si="3"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H162" s="6">
         <v>198800</v>
@@ -13183,7 +13240,7 @@
         <v>2326</v>
       </c>
       <c r="K162" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
@@ -13204,7 +13261,7 @@
       </c>
       <c r="G163" s="13">
         <f t="shared" si="3"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H163" s="6">
         <v>202300</v>
@@ -13213,7 +13270,7 @@
         <v>2326</v>
       </c>
       <c r="K163" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -13234,7 +13291,7 @@
       </c>
       <c r="G164" s="13">
         <f t="shared" si="3"/>
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
       <c r="H164" s="6">
         <v>200000</v>
@@ -13243,7 +13300,7 @@
         <v>2326</v>
       </c>
       <c r="K164" s="6">
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -13264,7 +13321,7 @@
       </c>
       <c r="G165" s="13">
         <f t="shared" si="3"/>
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
       <c r="H165" s="6">
         <v>200000</v>
@@ -13273,7 +13330,7 @@
         <v>2326</v>
       </c>
       <c r="K165" s="6">
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -13294,7 +13351,7 @@
       </c>
       <c r="G166" s="13">
         <f t="shared" si="3"/>
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
       <c r="H166" s="6">
         <v>200000</v>
@@ -13303,7 +13360,7 @@
         <v>2326</v>
       </c>
       <c r="K166" s="6">
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -13324,7 +13381,7 @@
       </c>
       <c r="G167" s="13">
         <f t="shared" si="3"/>
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
       <c r="H167" s="6">
         <v>200000</v>
@@ -13333,7 +13390,7 @@
         <v>2326</v>
       </c>
       <c r="K167" s="6">
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -13354,7 +13411,7 @@
       </c>
       <c r="G168" s="13">
         <f t="shared" si="3"/>
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
       <c r="H168" s="6">
         <v>200000</v>
@@ -13363,7 +13420,7 @@
         <v>2326</v>
       </c>
       <c r="K168" s="6">
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -13384,7 +13441,7 @@
       </c>
       <c r="G169" s="13">
         <f t="shared" si="3"/>
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
       <c r="H169" s="6">
         <v>200000</v>
@@ -13393,7 +13450,7 @@
         <v>2326</v>
       </c>
       <c r="K169" s="6">
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -13412,7 +13469,7 @@
       <c r="E170" s="4"/>
       <c r="G170" s="13">
         <f t="shared" si="3"/>
-        <v>2542320</v>
+        <v>2779920</v>
       </c>
       <c r="H170" s="6">
         <v>200000</v>
@@ -13421,7 +13478,7 @@
         <v>2326</v>
       </c>
       <c r="K170" s="6">
-        <v>2542320</v>
+        <v>2779920</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -13442,7 +13499,7 @@
       </c>
       <c r="G171" s="13">
         <f t="shared" si="3"/>
-        <v>2542320</v>
+        <v>2779920</v>
       </c>
       <c r="H171" s="6">
         <v>200000</v>
@@ -13451,7 +13508,7 @@
         <v>2326</v>
       </c>
       <c r="K171" s="6">
-        <v>2542320</v>
+        <v>2779920</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
@@ -13472,7 +13529,7 @@
       </c>
       <c r="G172" s="13">
         <f t="shared" si="3"/>
-        <v>5583600</v>
+        <v>6058800</v>
       </c>
       <c r="H172" s="6">
         <v>347200</v>
@@ -13481,7 +13538,7 @@
         <v>2326</v>
       </c>
       <c r="K172" s="6">
-        <v>5583600</v>
+        <v>6058800</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -13502,7 +13559,7 @@
       </c>
       <c r="G173" s="13">
         <f t="shared" si="3"/>
-        <v>5583600</v>
+        <v>6058800</v>
       </c>
       <c r="H173" s="6">
         <v>347200</v>
@@ -13511,7 +13568,7 @@
         <v>2326</v>
       </c>
       <c r="K173" s="6">
-        <v>5583600</v>
+        <v>6058800</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -13532,7 +13589,7 @@
       </c>
       <c r="G174" s="13">
         <f t="shared" si="3"/>
-        <v>2542320</v>
+        <v>2764080</v>
       </c>
       <c r="H174" s="6">
         <v>200000</v>
@@ -13541,7 +13598,7 @@
         <v>2326</v>
       </c>
       <c r="K174" s="6">
-        <v>2542320</v>
+        <v>2764080</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -13562,7 +13619,7 @@
       </c>
       <c r="G175" s="13">
         <f t="shared" si="3"/>
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
       <c r="H175" s="6">
         <v>206500</v>
@@ -13571,7 +13628,7 @@
         <v>2326</v>
       </c>
       <c r="K175" s="6">
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -13592,7 +13649,7 @@
       </c>
       <c r="G176" s="13">
         <f t="shared" si="3"/>
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
       <c r="H176" s="6">
         <v>209300</v>
@@ -13601,7 +13658,7 @@
         <v>2326</v>
       </c>
       <c r="K176" s="6">
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -13622,7 +13679,7 @@
       </c>
       <c r="G177" s="13">
         <f t="shared" si="3"/>
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
       <c r="H177" s="6">
         <v>206500</v>
@@ -13631,7 +13688,7 @@
         <v>2326</v>
       </c>
       <c r="K177" s="6">
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -13652,7 +13709,7 @@
       </c>
       <c r="G178" s="13">
         <f t="shared" si="3"/>
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
       <c r="H178" s="6">
         <v>206500</v>
@@ -13661,7 +13718,7 @@
         <v>2326</v>
       </c>
       <c r="K178" s="6">
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -13682,7 +13739,7 @@
       </c>
       <c r="G179" s="13">
         <f t="shared" si="3"/>
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
       <c r="H179" s="6">
         <v>206500</v>
@@ -13691,7 +13748,7 @@
         <v>2326</v>
       </c>
       <c r="K179" s="6">
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -13712,7 +13769,7 @@
       </c>
       <c r="G180" s="13">
         <f t="shared" si="3"/>
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
       <c r="H180" s="6">
         <v>200000</v>
@@ -13721,7 +13778,7 @@
         <v>2326</v>
       </c>
       <c r="K180" s="6">
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -13742,7 +13799,7 @@
       </c>
       <c r="G181" s="13">
         <f t="shared" si="3"/>
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
       <c r="H181" s="6">
         <v>200000</v>
@@ -13751,7 +13808,7 @@
         <v>2326</v>
       </c>
       <c r="K181" s="6">
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -13772,7 +13829,7 @@
       </c>
       <c r="G182" s="13">
         <f t="shared" si="3"/>
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
       <c r="H182" s="6">
         <v>206500</v>
@@ -13781,7 +13838,7 @@
         <v>2326</v>
       </c>
       <c r="K182" s="6">
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -13802,7 +13859,7 @@
       </c>
       <c r="G183" s="13">
         <f t="shared" si="3"/>
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
       <c r="H183" s="6">
         <v>206500</v>
@@ -13811,7 +13868,7 @@
         <v>2326</v>
       </c>
       <c r="K183" s="6">
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -13952,7 +14009,7 @@
       </c>
       <c r="G188" s="13">
         <f t="shared" si="3"/>
-        <v>2688840</v>
+        <v>2930400</v>
       </c>
       <c r="H188" s="6">
         <v>209300</v>
@@ -13961,7 +14018,7 @@
         <v>2326</v>
       </c>
       <c r="K188" s="6">
-        <v>2688840</v>
+        <v>2930400</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -14012,7 +14069,7 @@
       </c>
       <c r="G190" s="13">
         <f t="shared" si="3"/>
-        <v>2688840</v>
+        <v>2930400</v>
       </c>
       <c r="H190" s="6">
         <v>209300</v>
@@ -14021,7 +14078,7 @@
         <v>2326</v>
       </c>
       <c r="K190" s="6">
-        <v>2688840</v>
+        <v>2930400</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -14042,7 +14099,7 @@
       </c>
       <c r="G191" s="13">
         <f t="shared" si="3"/>
-        <v>2688840</v>
+        <v>2930400</v>
       </c>
       <c r="H191" s="6">
         <v>209300</v>
@@ -14051,7 +14108,7 @@
         <v>2326</v>
       </c>
       <c r="K191" s="6">
-        <v>2688840</v>
+        <v>2930400</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -14072,7 +14129,7 @@
       </c>
       <c r="G192" s="13">
         <f t="shared" si="3"/>
-        <v>2688840</v>
+        <v>2930400</v>
       </c>
       <c r="H192" s="6">
         <v>209300</v>
@@ -14081,7 +14138,7 @@
         <v>2326</v>
       </c>
       <c r="K192" s="6">
-        <v>2688840</v>
+        <v>2930400</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -14102,7 +14159,7 @@
       </c>
       <c r="G193" s="13">
         <f t="shared" si="3"/>
-        <v>2688840</v>
+        <v>2930400</v>
       </c>
       <c r="H193" s="6">
         <v>209300</v>
@@ -14111,7 +14168,7 @@
         <v>2326</v>
       </c>
       <c r="K193" s="6">
-        <v>2688840</v>
+        <v>2930400</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -14132,7 +14189,7 @@
       </c>
       <c r="G194" s="13">
         <f t="shared" si="3"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H194" s="6">
         <v>200000</v>
@@ -14141,7 +14198,7 @@
         <v>2326</v>
       </c>
       <c r="K194" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -14162,7 +14219,7 @@
       </c>
       <c r="G195" s="13">
         <f t="shared" ref="G195:G214" si="4">IF(J195&lt;&gt;"",J195*$J$1,K195)</f>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H195" s="6">
         <v>200000</v>
@@ -14171,7 +14228,7 @@
         <v>2326</v>
       </c>
       <c r="K195" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -14192,7 +14249,7 @@
       </c>
       <c r="G196" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H196" s="6">
         <v>200000</v>
@@ -14201,7 +14258,7 @@
         <v>2326</v>
       </c>
       <c r="K196" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -14222,7 +14279,7 @@
       </c>
       <c r="G197" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H197" s="6">
         <v>200000</v>
@@ -14231,7 +14288,7 @@
         <v>2326</v>
       </c>
       <c r="K197" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -14252,7 +14309,7 @@
       </c>
       <c r="G198" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H198" s="6">
         <v>200000</v>
@@ -14261,7 +14318,7 @@
         <v>2326</v>
       </c>
       <c r="K198" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -14282,7 +14339,7 @@
       </c>
       <c r="G199" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H199" s="6">
         <v>200000</v>
@@ -14291,7 +14348,7 @@
         <v>2326</v>
       </c>
       <c r="K199" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -14312,7 +14369,7 @@
       </c>
       <c r="G200" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H200" s="6">
         <v>200000</v>
@@ -14321,7 +14378,7 @@
         <v>2326</v>
       </c>
       <c r="K200" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -14342,7 +14399,7 @@
       </c>
       <c r="G201" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H201" s="6">
         <v>200000</v>
@@ -14351,7 +14408,7 @@
         <v>2326</v>
       </c>
       <c r="K201" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -14372,7 +14429,7 @@
       </c>
       <c r="G202" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H202" s="6">
         <v>200000</v>
@@ -14381,7 +14438,7 @@
         <v>2326</v>
       </c>
       <c r="K202" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -14402,7 +14459,7 @@
       </c>
       <c r="G203" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H203" s="6">
         <v>200000</v>
@@ -14411,7 +14468,7 @@
         <v>2326</v>
       </c>
       <c r="K203" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -14432,7 +14489,7 @@
       </c>
       <c r="G204" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H204" s="6">
         <v>200000</v>
@@ -14441,7 +14498,7 @@
         <v>2326</v>
       </c>
       <c r="K204" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -14462,7 +14519,7 @@
       </c>
       <c r="G205" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H205" s="6">
         <v>200000</v>
@@ -14471,7 +14528,7 @@
         <v>2326</v>
       </c>
       <c r="K205" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -14492,7 +14549,7 @@
       </c>
       <c r="G206" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H206" s="6">
         <v>200000</v>
@@ -14501,7 +14558,7 @@
         <v>2326</v>
       </c>
       <c r="K206" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -14522,7 +14579,7 @@
       </c>
       <c r="G207" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H207" s="6">
         <v>200000</v>
@@ -14531,7 +14588,7 @@
         <v>2326</v>
       </c>
       <c r="K207" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -14552,7 +14609,7 @@
       </c>
       <c r="G208" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H208" s="6">
         <v>200000</v>
@@ -14561,7 +14618,7 @@
         <v>2326</v>
       </c>
       <c r="K208" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -14582,7 +14639,7 @@
       </c>
       <c r="G209" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H209" s="6">
         <v>200000</v>
@@ -14591,7 +14648,7 @@
         <v>2326</v>
       </c>
       <c r="K209" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -14612,7 +14669,7 @@
       </c>
       <c r="G210" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H210" s="6">
         <v>200000</v>
@@ -14621,7 +14678,7 @@
         <v>2326</v>
       </c>
       <c r="K210" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -14642,7 +14699,7 @@
       </c>
       <c r="G211" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H211" s="6">
         <v>200000</v>
@@ -14651,7 +14708,7 @@
         <v>2326</v>
       </c>
       <c r="K211" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -14672,7 +14729,7 @@
       </c>
       <c r="G212" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H212" s="6">
         <v>200000</v>
@@ -14681,7 +14738,7 @@
         <v>2326</v>
       </c>
       <c r="K212" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -14702,7 +14759,7 @@
       </c>
       <c r="G213" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H213" s="6">
         <v>200000</v>
@@ -14711,7 +14768,7 @@
         <v>2326</v>
       </c>
       <c r="K213" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -14732,7 +14789,7 @@
       </c>
       <c r="G214" s="13">
         <f t="shared" si="4"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="H214" s="6">
         <v>200000</v>
@@ -14741,7 +14798,7 @@
         <v>2326</v>
       </c>
       <c r="K214" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -14937,7 +14994,7 @@
       </c>
       <c r="G221" s="13">
         <f t="shared" si="5"/>
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
       <c r="H221" s="6">
         <v>200000</v>
@@ -14946,7 +15003,7 @@
         <v>2326</v>
       </c>
       <c r="K221" s="6">
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -14967,7 +15024,7 @@
       </c>
       <c r="G222" s="13">
         <f t="shared" si="5"/>
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
       <c r="H222" s="6">
         <v>200000</v>
@@ -14976,7 +15033,7 @@
         <v>2326</v>
       </c>
       <c r="K222" s="6">
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
@@ -14997,7 +15054,7 @@
       </c>
       <c r="G223" s="13">
         <f t="shared" si="5"/>
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
       <c r="H223" s="6">
         <v>200000</v>
@@ -15006,7 +15063,7 @@
         <v>2326</v>
       </c>
       <c r="K223" s="6">
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -15027,7 +15084,7 @@
       </c>
       <c r="G224" s="13">
         <f t="shared" si="5"/>
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
       <c r="H224" s="6">
         <v>200000</v>
@@ -15036,7 +15093,7 @@
         <v>2326</v>
       </c>
       <c r="K224" s="6">
-        <v>2827440</v>
+        <v>3049200</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
@@ -15057,7 +15114,7 @@
       </c>
       <c r="G225" s="13">
         <f t="shared" si="5"/>
-        <v>2455200</v>
+        <v>2669240</v>
       </c>
       <c r="H225" s="6">
         <v>200000</v>
@@ -15066,7 +15123,7 @@
         <v>2326</v>
       </c>
       <c r="K225" s="6">
-        <v>2455200</v>
+        <v>2669240</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
@@ -15088,7 +15145,7 @@
       <c r="F226" s="5"/>
       <c r="G226" s="13">
         <f t="shared" si="5"/>
-        <v>2455200</v>
+        <v>2669240</v>
       </c>
       <c r="H226" s="6">
         <v>200000</v>
@@ -15097,7 +15154,7 @@
         <v>2326</v>
       </c>
       <c r="K226" s="6">
-        <v>2455200</v>
+        <v>2669240</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
@@ -15118,7 +15175,7 @@
       </c>
       <c r="G227" s="13">
         <f t="shared" si="5"/>
-        <v>2455200</v>
+        <v>2669240</v>
       </c>
       <c r="H227" s="6">
         <v>200000</v>
@@ -15127,7 +15184,7 @@
         <v>2326</v>
       </c>
       <c r="K227" s="6">
-        <v>2455200</v>
+        <v>2669240</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -15148,7 +15205,7 @@
       </c>
       <c r="G228" s="13">
         <f t="shared" si="5"/>
-        <v>2874960</v>
+        <v>3120480</v>
       </c>
       <c r="H228" s="6">
         <v>200000</v>
@@ -15157,7 +15214,7 @@
         <v>2326</v>
       </c>
       <c r="K228" s="6">
-        <v>2874960</v>
+        <v>3120480</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -15206,7 +15263,7 @@
       </c>
       <c r="G230" s="13">
         <f t="shared" si="5"/>
-        <v>2542320</v>
+        <v>2764080</v>
       </c>
       <c r="H230" s="6">
         <v>200000</v>
@@ -15215,7 +15272,7 @@
         <v>2326</v>
       </c>
       <c r="K230" s="6">
-        <v>2542320</v>
+        <v>2764080</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
@@ -15236,7 +15293,7 @@
       </c>
       <c r="G231" s="13">
         <f t="shared" si="5"/>
-        <v>2542320</v>
+        <v>2764080</v>
       </c>
       <c r="H231" s="6">
         <v>202300</v>
@@ -15245,7 +15302,7 @@
         <v>2326</v>
       </c>
       <c r="K231" s="6">
-        <v>2542320</v>
+        <v>2764080</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
@@ -15266,7 +15323,7 @@
       </c>
       <c r="G232" s="13">
         <f t="shared" si="5"/>
-        <v>2241360</v>
+        <v>2447280</v>
       </c>
       <c r="H232" s="6">
         <v>200000</v>
@@ -15275,7 +15332,7 @@
         <v>2326</v>
       </c>
       <c r="K232" s="6">
-        <v>2241360</v>
+        <v>2447280</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
@@ -17966,7 +18023,7 @@
       </c>
       <c r="G325" s="13">
         <f t="shared" si="7"/>
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
       <c r="H325" s="6">
         <v>200000</v>
@@ -17975,7 +18032,7 @@
         <v>2326</v>
       </c>
       <c r="K325" s="6">
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.25">
@@ -17996,7 +18053,7 @@
       </c>
       <c r="G326" s="13">
         <f t="shared" si="7"/>
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
       <c r="H326" s="6">
         <v>200000</v>
@@ -18005,7 +18062,7 @@
         <v>2326</v>
       </c>
       <c r="K326" s="6">
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.25">
@@ -18026,7 +18083,7 @@
       </c>
       <c r="G327" s="13">
         <f t="shared" si="7"/>
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
       <c r="H327" s="6">
         <v>200000</v>
@@ -18035,7 +18092,7 @@
         <v>2326</v>
       </c>
       <c r="K327" s="6">
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
@@ -18056,7 +18113,7 @@
       </c>
       <c r="G328" s="13">
         <f t="shared" si="7"/>
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
       <c r="H328" s="6">
         <v>200000</v>
@@ -18065,7 +18122,7 @@
         <v>2326</v>
       </c>
       <c r="K328" s="6">
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.25">
@@ -18086,7 +18143,7 @@
       </c>
       <c r="G329" s="13">
         <f t="shared" si="7"/>
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
       <c r="H329" s="6">
         <v>200000</v>
@@ -18095,7 +18152,7 @@
         <v>2326</v>
       </c>
       <c r="K329" s="6">
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.25">
@@ -18116,7 +18173,7 @@
       </c>
       <c r="G330" s="13">
         <f t="shared" si="7"/>
-        <v>2579070</v>
+        <v>3582200</v>
       </c>
       <c r="H330" s="6">
         <v>200000</v>
@@ -18125,7 +18182,7 @@
         <v>2326</v>
       </c>
       <c r="K330" s="6">
-        <v>2579070</v>
+        <v>3582200</v>
       </c>
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.25">
@@ -18146,7 +18203,7 @@
       </c>
       <c r="G331" s="13">
         <f t="shared" si="7"/>
-        <v>2579070</v>
+        <v>3582200</v>
       </c>
       <c r="H331" s="6">
         <v>200000</v>
@@ -18155,7 +18212,7 @@
         <v>2326</v>
       </c>
       <c r="K331" s="6">
-        <v>2579070</v>
+        <v>3582200</v>
       </c>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
@@ -18176,7 +18233,7 @@
       </c>
       <c r="G332" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H332" s="6">
         <v>200000</v>
@@ -18185,7 +18242,7 @@
         <v>2326</v>
       </c>
       <c r="K332" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.25">
@@ -18206,7 +18263,7 @@
       </c>
       <c r="G333" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H333" s="6">
         <v>200000</v>
@@ -18215,7 +18272,7 @@
         <v>2326</v>
       </c>
       <c r="K333" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
@@ -18236,7 +18293,7 @@
       </c>
       <c r="G334" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H334" s="6">
         <v>205100</v>
@@ -18245,7 +18302,7 @@
         <v>2326</v>
       </c>
       <c r="K334" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.25">
@@ -18266,7 +18323,7 @@
       </c>
       <c r="G335" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H335" s="6">
         <v>200000</v>
@@ -18275,7 +18332,7 @@
         <v>2326</v>
       </c>
       <c r="K335" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.25">
@@ -18296,7 +18353,7 @@
       </c>
       <c r="G336" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H336" s="6">
         <v>200000</v>
@@ -18305,7 +18362,7 @@
         <v>2326</v>
       </c>
       <c r="K336" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.25">
@@ -18326,7 +18383,7 @@
       </c>
       <c r="G337" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H337" s="6">
         <v>200000</v>
@@ -18335,7 +18392,7 @@
         <v>2326</v>
       </c>
       <c r="K337" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
@@ -18356,7 +18413,7 @@
       </c>
       <c r="G338" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H338" s="6">
         <v>200000</v>
@@ -18365,7 +18422,7 @@
         <v>2326</v>
       </c>
       <c r="K338" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.25">
@@ -18386,7 +18443,7 @@
       </c>
       <c r="G339" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H339" s="6">
         <v>200000</v>
@@ -18395,7 +18452,7 @@
         <v>2326</v>
       </c>
       <c r="K339" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.25">
@@ -18416,7 +18473,7 @@
       </c>
       <c r="G340" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H340" s="6">
         <v>201600</v>
@@ -18425,7 +18482,7 @@
         <v>2326</v>
       </c>
       <c r="K340" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
@@ -18446,7 +18503,7 @@
       </c>
       <c r="G341" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H341" s="6">
         <v>200000</v>
@@ -18455,7 +18512,7 @@
         <v>2326</v>
       </c>
       <c r="K341" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
@@ -18476,7 +18533,7 @@
       </c>
       <c r="G342" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H342" s="6">
         <v>200000</v>
@@ -18485,7 +18542,7 @@
         <v>2326</v>
       </c>
       <c r="K342" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
@@ -18506,7 +18563,7 @@
       </c>
       <c r="G343" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H343" s="6">
         <v>200000</v>
@@ -18515,7 +18572,7 @@
         <v>2326</v>
       </c>
       <c r="K343" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
@@ -18536,7 +18593,7 @@
       </c>
       <c r="G344" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H344" s="6">
         <v>200000</v>
@@ -18545,7 +18602,7 @@
         <v>2326</v>
       </c>
       <c r="K344" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
@@ -18566,7 +18623,7 @@
       </c>
       <c r="G345" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H345" s="6">
         <v>200000</v>
@@ -18575,7 +18632,7 @@
         <v>2326</v>
       </c>
       <c r="K345" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
@@ -18596,7 +18653,7 @@
       </c>
       <c r="G346" s="13">
         <f t="shared" si="7"/>
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
       <c r="H346" s="6">
         <v>200000</v>
@@ -18605,7 +18662,7 @@
         <v>2326</v>
       </c>
       <c r="K346" s="6">
-        <v>2514090</v>
+        <v>3501040</v>
       </c>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.25">
@@ -18626,7 +18683,7 @@
       </c>
       <c r="G347" s="13">
         <f t="shared" si="7"/>
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
       <c r="H347" s="6">
         <v>200000</v>
@@ -18635,7 +18692,7 @@
         <v>2326</v>
       </c>
       <c r="K347" s="6">
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
@@ -18656,7 +18713,7 @@
       </c>
       <c r="G348" s="13">
         <f t="shared" si="7"/>
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
       <c r="H348" s="6">
         <v>200000</v>
@@ -18665,7 +18722,7 @@
         <v>2326</v>
       </c>
       <c r="K348" s="6">
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.25">
@@ -18686,7 +18743,7 @@
       </c>
       <c r="G349" s="13">
         <f t="shared" si="7"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H349" s="6">
         <v>200000</v>
@@ -18695,7 +18752,7 @@
         <v>2326</v>
       </c>
       <c r="K349" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
@@ -18716,7 +18773,7 @@
       </c>
       <c r="G350" s="13">
         <f t="shared" si="7"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H350" s="6">
         <v>200000</v>
@@ -18725,7 +18782,7 @@
         <v>2326</v>
       </c>
       <c r="K350" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.25">
@@ -18746,7 +18803,7 @@
       </c>
       <c r="G351" s="13">
         <f t="shared" si="7"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H351" s="6">
         <v>200000</v>
@@ -18755,7 +18812,7 @@
         <v>2326</v>
       </c>
       <c r="K351" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.25">
@@ -18776,7 +18833,7 @@
       </c>
       <c r="G352" s="13">
         <f t="shared" si="7"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H352" s="6">
         <v>200000</v>
@@ -18785,7 +18842,7 @@
         <v>2326</v>
       </c>
       <c r="K352" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
@@ -18806,7 +18863,7 @@
       </c>
       <c r="G353" s="13">
         <f t="shared" si="7"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H353" s="6">
         <v>200000</v>
@@ -18815,7 +18872,7 @@
         <v>2326</v>
       </c>
       <c r="K353" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.25">
@@ -18836,7 +18893,7 @@
       </c>
       <c r="G354" s="13">
         <f t="shared" si="7"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H354" s="6">
         <v>200000</v>
@@ -18845,7 +18902,7 @@
         <v>2326</v>
       </c>
       <c r="K354" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
@@ -18866,7 +18923,7 @@
       </c>
       <c r="G355" s="13">
         <f t="shared" si="7"/>
-        <v>2359750</v>
+        <v>3555200</v>
       </c>
       <c r="H355" s="6">
         <v>200000</v>
@@ -18875,7 +18932,7 @@
         <v>2326</v>
       </c>
       <c r="K355" s="6">
-        <v>2359750</v>
+        <v>3555200</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
@@ -18896,7 +18953,7 @@
       </c>
       <c r="G356" s="13">
         <f t="shared" si="7"/>
-        <v>2359750</v>
+        <v>3555200</v>
       </c>
       <c r="H356" s="6">
         <v>207900</v>
@@ -18905,7 +18962,7 @@
         <v>2326</v>
       </c>
       <c r="K356" s="6">
-        <v>2359750</v>
+        <v>3555200</v>
       </c>
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.25">
@@ -18926,7 +18983,7 @@
       </c>
       <c r="G357" s="13">
         <f t="shared" si="7"/>
-        <v>2359750</v>
+        <v>3555200</v>
       </c>
       <c r="H357" s="6">
         <v>200000</v>
@@ -18935,7 +18992,7 @@
         <v>2326</v>
       </c>
       <c r="K357" s="6">
-        <v>2359750</v>
+        <v>3555200</v>
       </c>
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.25">
@@ -18956,7 +19013,7 @@
       </c>
       <c r="G358" s="13">
         <f t="shared" si="7"/>
-        <v>2359750</v>
+        <v>3555200</v>
       </c>
       <c r="H358" s="6">
         <v>200000</v>
@@ -18965,7 +19022,7 @@
         <v>2326</v>
       </c>
       <c r="K358" s="6">
-        <v>2359750</v>
+        <v>3555200</v>
       </c>
     </row>
     <row r="359" spans="1:11" x14ac:dyDescent="0.25">
@@ -18986,7 +19043,7 @@
       </c>
       <c r="G359" s="13">
         <f t="shared" si="7"/>
-        <v>2359750</v>
+        <v>3555200</v>
       </c>
       <c r="H359" s="6">
         <v>200000</v>
@@ -18995,7 +19052,7 @@
         <v>2326</v>
       </c>
       <c r="K359" s="6">
-        <v>2359750</v>
+        <v>3555200</v>
       </c>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.25">
@@ -19016,7 +19073,7 @@
       </c>
       <c r="G360" s="13">
         <f t="shared" si="7"/>
-        <v>2359750</v>
+        <v>3555200</v>
       </c>
       <c r="H360" s="6">
         <v>200000</v>
@@ -19025,7 +19082,7 @@
         <v>2326</v>
       </c>
       <c r="K360" s="6">
-        <v>2359750</v>
+        <v>3555200</v>
       </c>
     </row>
     <row r="361" spans="1:11" x14ac:dyDescent="0.25">
@@ -19046,7 +19103,7 @@
       </c>
       <c r="G361" s="13">
         <f t="shared" si="7"/>
-        <v>1760000</v>
+        <v>2446400</v>
       </c>
       <c r="H361" s="6">
         <v>200000</v>
@@ -19055,7 +19112,7 @@
         <v>2326</v>
       </c>
       <c r="K361" s="6">
-        <v>1760000</v>
+        <v>2446400</v>
       </c>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
@@ -19076,7 +19133,7 @@
       </c>
       <c r="G362" s="13">
         <f t="shared" si="7"/>
-        <v>1760000</v>
+        <v>2446400</v>
       </c>
       <c r="H362" s="6">
         <v>200000</v>
@@ -19085,7 +19142,7 @@
         <v>2326</v>
       </c>
       <c r="K362" s="6">
-        <v>1760000</v>
+        <v>2446400</v>
       </c>
     </row>
     <row r="363" spans="1:11" x14ac:dyDescent="0.25">
@@ -19106,7 +19163,7 @@
       </c>
       <c r="G363" s="13">
         <f t="shared" si="7"/>
-        <v>1760000</v>
+        <v>2446400</v>
       </c>
       <c r="H363" s="6">
         <v>200000</v>
@@ -19115,7 +19172,7 @@
         <v>2326</v>
       </c>
       <c r="K363" s="6">
-        <v>1760000</v>
+        <v>2446400</v>
       </c>
     </row>
     <row r="364" spans="1:11" x14ac:dyDescent="0.25">
@@ -19136,7 +19193,7 @@
       </c>
       <c r="G364" s="13">
         <f t="shared" si="7"/>
-        <v>1760000</v>
+        <v>2446400</v>
       </c>
       <c r="H364" s="6">
         <v>200000</v>
@@ -19145,7 +19202,7 @@
         <v>2326</v>
       </c>
       <c r="K364" s="6">
-        <v>1760000</v>
+        <v>2446400</v>
       </c>
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.25">
@@ -19166,7 +19223,7 @@
       </c>
       <c r="G365" s="13">
         <f t="shared" si="7"/>
-        <v>1760000</v>
+        <v>2446400</v>
       </c>
       <c r="H365" s="6">
         <v>200000</v>
@@ -19175,7 +19232,7 @@
         <v>2326</v>
       </c>
       <c r="K365" s="6">
-        <v>1760000</v>
+        <v>2446400</v>
       </c>
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.25">
@@ -19196,7 +19253,7 @@
       </c>
       <c r="G366" s="13">
         <f t="shared" si="7"/>
-        <v>1877040</v>
+        <v>2043360</v>
       </c>
       <c r="H366" s="6">
         <v>200000</v>
@@ -19205,7 +19262,7 @@
         <v>2326</v>
       </c>
       <c r="K366" s="6">
-        <v>1877040</v>
+        <v>2043360</v>
       </c>
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.25">
@@ -19226,7 +19283,7 @@
       </c>
       <c r="G367" s="13">
         <f t="shared" si="7"/>
-        <v>2138400</v>
+        <v>2336400</v>
       </c>
       <c r="H367" s="6">
         <v>200000</v>
@@ -19235,7 +19292,7 @@
         <v>2326</v>
       </c>
       <c r="K367" s="6">
-        <v>2138400</v>
+        <v>2336400</v>
       </c>
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.25">
@@ -19256,7 +19313,7 @@
       </c>
       <c r="G368" s="13">
         <f t="shared" si="7"/>
-        <v>1877040</v>
+        <v>2043360</v>
       </c>
       <c r="H368" s="6">
         <v>200000</v>
@@ -19265,7 +19322,7 @@
         <v>2326</v>
       </c>
       <c r="K368" s="6">
-        <v>1877040</v>
+        <v>2043360</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.25">
@@ -25039,7 +25096,7 @@
       <c r="E579" s="4"/>
       <c r="G579" s="13">
         <f t="shared" si="11"/>
-        <v>2579070</v>
+        <v>3582200</v>
       </c>
       <c r="H579" s="6">
         <v>200000</v>
@@ -25048,7 +25105,7 @@
         <v>2326</v>
       </c>
       <c r="K579" s="6">
-        <v>2579070</v>
+        <v>3582200</v>
       </c>
     </row>
     <row r="580" spans="1:11" x14ac:dyDescent="0.25">
@@ -73892,7 +73949,7 @@
       </c>
       <c r="G2389" s="13">
         <f t="shared" si="41"/>
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
       <c r="H2389" s="6">
         <v>200000</v>
@@ -73901,7 +73958,7 @@
         <v>2326</v>
       </c>
       <c r="K2389" s="6">
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
     </row>
     <row r="2390" spans="1:11" x14ac:dyDescent="0.25">
@@ -73922,7 +73979,7 @@
       </c>
       <c r="G2390" s="13">
         <f t="shared" si="41"/>
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
       <c r="H2390" s="6">
         <v>207900</v>
@@ -73931,7 +73988,7 @@
         <v>2326</v>
       </c>
       <c r="K2390" s="6">
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
     </row>
     <row r="2391" spans="1:11" x14ac:dyDescent="0.25">
@@ -73952,7 +74009,7 @@
       </c>
       <c r="G2391" s="13">
         <f t="shared" si="41"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H2391" s="6">
         <v>200000</v>
@@ -73961,7 +74018,7 @@
         <v>2326</v>
       </c>
       <c r="K2391" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="2392" spans="1:11" x14ac:dyDescent="0.25">
@@ -73982,7 +74039,7 @@
       </c>
       <c r="G2392" s="13">
         <f t="shared" si="41"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H2392" s="6">
         <v>200000</v>
@@ -73991,7 +74048,7 @@
         <v>2326</v>
       </c>
       <c r="K2392" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="2393" spans="1:11" x14ac:dyDescent="0.25">
@@ -74043,7 +74100,7 @@
       </c>
       <c r="G2394" s="13">
         <f t="shared" si="41"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H2394" s="9">
         <v>200000</v>
@@ -74053,7 +74110,7 @@
       </c>
       <c r="J2394" s="12"/>
       <c r="K2394" s="9">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="2395" spans="1:11" x14ac:dyDescent="0.25">
@@ -74074,7 +74131,7 @@
       </c>
       <c r="G2395" s="13">
         <f t="shared" si="41"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H2395" s="6">
         <v>200000</v>
@@ -74083,7 +74140,7 @@
         <v>2326</v>
       </c>
       <c r="K2395" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="2396" spans="1:11" x14ac:dyDescent="0.25">
@@ -74507,7 +74564,7 @@
       </c>
       <c r="G2409" s="13">
         <f t="shared" si="41"/>
-        <v>2018580</v>
+        <v>2810580</v>
       </c>
       <c r="H2409" s="6">
         <v>200000</v>
@@ -74516,7 +74573,7 @@
         <v>2326</v>
       </c>
       <c r="K2409" s="6">
-        <v>2018580</v>
+        <v>2810580</v>
       </c>
     </row>
     <row r="2410" spans="1:11" x14ac:dyDescent="0.25">
@@ -74537,7 +74594,7 @@
       </c>
       <c r="G2410" s="13">
         <f t="shared" si="41"/>
-        <v>2018580</v>
+        <v>2810580</v>
       </c>
       <c r="H2410" s="6">
         <v>200000</v>
@@ -74546,7 +74603,7 @@
         <v>2326</v>
       </c>
       <c r="K2410" s="6">
-        <v>2018580</v>
+        <v>2810580</v>
       </c>
     </row>
     <row r="2411" spans="1:11" x14ac:dyDescent="0.25">
@@ -74567,7 +74624,7 @@
       </c>
       <c r="G2411" s="13">
         <f t="shared" si="41"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H2411" s="6">
         <v>200000</v>
@@ -74576,7 +74633,7 @@
         <v>2326</v>
       </c>
       <c r="K2411" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="2412" spans="1:11" x14ac:dyDescent="0.25">
@@ -74597,7 +74654,7 @@
       </c>
       <c r="G2412" s="13">
         <f t="shared" si="41"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H2412" s="6">
         <v>200000</v>
@@ -74606,7 +74663,7 @@
         <v>2326</v>
       </c>
       <c r="K2412" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="2413" spans="1:11" x14ac:dyDescent="0.25">
@@ -74627,7 +74684,7 @@
       </c>
       <c r="G2413" s="13">
         <f t="shared" si="41"/>
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
       <c r="H2413" s="6">
         <v>200000</v>
@@ -74636,7 +74693,7 @@
         <v>2326</v>
       </c>
       <c r="K2413" s="6">
-        <v>2415600</v>
+        <v>2653200</v>
       </c>
     </row>
     <row r="2414" spans="1:11" x14ac:dyDescent="0.25">
@@ -74657,7 +74714,7 @@
       </c>
       <c r="G2414" s="13">
         <f t="shared" si="41"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H2414" s="6">
         <v>200000</v>
@@ -74666,7 +74723,7 @@
         <v>2326</v>
       </c>
       <c r="K2414" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="2415" spans="1:11" x14ac:dyDescent="0.25">
@@ -74687,7 +74744,7 @@
       </c>
       <c r="G2415" s="13">
         <f t="shared" si="41"/>
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
       <c r="H2415" s="6">
         <v>200000</v>
@@ -74696,7 +74753,7 @@
         <v>2326</v>
       </c>
       <c r="K2415" s="6">
-        <v>2360910</v>
+        <v>3541660</v>
       </c>
     </row>
     <row r="2416" spans="1:11" x14ac:dyDescent="0.25">
@@ -74747,7 +74804,7 @@
       </c>
       <c r="G2417" s="13">
         <f t="shared" si="41"/>
-        <v>1520640</v>
+        <v>1742400</v>
       </c>
       <c r="H2417" s="6">
         <v>200000</v>
@@ -74756,7 +74813,7 @@
         <v>2326</v>
       </c>
       <c r="K2417" s="6">
-        <v>1520640</v>
+        <v>1742400</v>
       </c>
     </row>
     <row r="2418" spans="1:11" x14ac:dyDescent="0.25">
@@ -74777,7 +74834,7 @@
       </c>
       <c r="G2418" s="13">
         <f t="shared" si="41"/>
-        <v>1378080</v>
+        <v>1520640</v>
       </c>
       <c r="H2418" s="6">
         <v>200000</v>
@@ -74786,7 +74843,7 @@
         <v>2326</v>
       </c>
       <c r="K2418" s="6">
-        <v>1378080</v>
+        <v>1520640</v>
       </c>
     </row>
     <row r="2419" spans="1:11" x14ac:dyDescent="0.25">
@@ -74807,7 +74864,7 @@
       </c>
       <c r="G2419" s="13">
         <f t="shared" si="41"/>
-        <v>1185960</v>
+        <v>1657100</v>
       </c>
       <c r="H2419" s="6">
         <v>200000</v>
@@ -74816,7 +74873,7 @@
         <v>2326</v>
       </c>
       <c r="K2419" s="6">
-        <v>1185960</v>
+        <v>1657100</v>
       </c>
     </row>
     <row r="2420" spans="1:11" x14ac:dyDescent="0.25">
@@ -74837,7 +74894,7 @@
       </c>
       <c r="G2420" s="13">
         <f t="shared" si="41"/>
-        <v>1185960</v>
+        <v>1657100</v>
       </c>
       <c r="H2420" s="6">
         <v>200000</v>
@@ -74846,7 +74903,7 @@
         <v>2326</v>
       </c>
       <c r="K2420" s="6">
-        <v>1185960</v>
+        <v>1657100</v>
       </c>
     </row>
     <row r="2421" spans="1:11" x14ac:dyDescent="0.25">
@@ -74867,7 +74924,7 @@
       </c>
       <c r="G2421" s="13">
         <f t="shared" si="41"/>
-        <v>1185960</v>
+        <v>1657100</v>
       </c>
       <c r="H2421" s="6">
         <v>200000</v>
@@ -74876,7 +74933,7 @@
         <v>2326</v>
       </c>
       <c r="K2421" s="6">
-        <v>1185960</v>
+        <v>1657100</v>
       </c>
     </row>
     <row r="2422" spans="1:11" x14ac:dyDescent="0.25">
@@ -74897,7 +74954,7 @@
       </c>
       <c r="G2422" s="13">
         <f t="shared" si="41"/>
-        <v>1185960</v>
+        <v>1657100</v>
       </c>
       <c r="H2422" s="6">
         <v>200000</v>
@@ -74906,7 +74963,7 @@
         <v>2326</v>
       </c>
       <c r="K2422" s="6">
-        <v>1185960</v>
+        <v>1657100</v>
       </c>
     </row>
     <row r="2423" spans="1:11" x14ac:dyDescent="0.25">
@@ -74927,7 +74984,7 @@
       </c>
       <c r="G2423" s="13">
         <f t="shared" si="41"/>
-        <v>1921100</v>
+        <v>2672490</v>
       </c>
       <c r="H2423" s="6">
         <v>200000</v>
@@ -74936,7 +74993,7 @@
         <v>2326</v>
       </c>
       <c r="K2423" s="6">
-        <v>1921100</v>
+        <v>2672490</v>
       </c>
     </row>
     <row r="2424" spans="1:11" x14ac:dyDescent="0.25">
@@ -74957,7 +75014,7 @@
       </c>
       <c r="G2424" s="13">
         <f t="shared" si="41"/>
-        <v>2688840</v>
+        <v>2930400</v>
       </c>
       <c r="H2424" s="6">
         <v>259000</v>
@@ -74966,7 +75023,7 @@
         <v>2326</v>
       </c>
       <c r="K2424" s="6">
-        <v>2688840</v>
+        <v>2930400</v>
       </c>
     </row>
     <row r="2425" spans="1:11" x14ac:dyDescent="0.25">
@@ -74987,7 +75044,7 @@
       </c>
       <c r="G2425" s="13">
         <f t="shared" si="41"/>
-        <v>1185960</v>
+        <v>1657100</v>
       </c>
       <c r="H2425" s="6">
         <v>200000</v>
@@ -74996,7 +75053,7 @@
         <v>2326</v>
       </c>
       <c r="K2425" s="6">
-        <v>1185960</v>
+        <v>1657100</v>
       </c>
     </row>
     <row r="2426" spans="1:11" x14ac:dyDescent="0.25">
@@ -75017,7 +75074,7 @@
       </c>
       <c r="G2426" s="13">
         <f t="shared" si="41"/>
-        <v>1185960</v>
+        <v>1657100</v>
       </c>
       <c r="H2426" s="6">
         <v>200000</v>
@@ -75026,7 +75083,7 @@
         <v>2326</v>
       </c>
       <c r="K2426" s="6">
-        <v>1185960</v>
+        <v>1657100</v>
       </c>
     </row>
     <row r="2427" spans="1:11" x14ac:dyDescent="0.25">
@@ -75047,7 +75104,7 @@
       </c>
       <c r="G2427" s="13">
         <f t="shared" si="41"/>
-        <v>1921100</v>
+        <v>2672490</v>
       </c>
       <c r="H2427" s="6">
         <v>200000</v>
@@ -75056,7 +75113,7 @@
         <v>2326</v>
       </c>
       <c r="K2427" s="6">
-        <v>1921100</v>
+        <v>2672490</v>
       </c>
     </row>
     <row r="2428" spans="1:11" x14ac:dyDescent="0.25">
@@ -75077,7 +75134,7 @@
       </c>
       <c r="G2428" s="13">
         <f t="shared" si="41"/>
-        <v>1921100</v>
+        <v>2672491</v>
       </c>
       <c r="H2428" s="6">
         <v>200000</v>
@@ -75086,7 +75143,7 @@
         <v>2326</v>
       </c>
       <c r="K2428" s="6">
-        <v>1921100</v>
+        <v>2672491</v>
       </c>
     </row>
     <row r="2429" spans="1:11" x14ac:dyDescent="0.25">
@@ -75107,7 +75164,7 @@
       </c>
       <c r="G2429" s="13">
         <f t="shared" si="41"/>
-        <v>1921100</v>
+        <v>2672492</v>
       </c>
       <c r="H2429" s="6">
         <v>200000</v>
@@ -75116,7 +75173,7 @@
         <v>2326</v>
       </c>
       <c r="K2429" s="6">
-        <v>1921100</v>
+        <v>2672492</v>
       </c>
     </row>
     <row r="2430" spans="1:11" x14ac:dyDescent="0.25">
@@ -75137,7 +75194,7 @@
       </c>
       <c r="G2430" s="13">
         <f t="shared" si="41"/>
-        <v>1921100</v>
+        <v>2672493</v>
       </c>
       <c r="H2430" s="6">
         <v>200000</v>
@@ -75146,7 +75203,7 @@
         <v>2326</v>
       </c>
       <c r="K2430" s="6">
-        <v>1921100</v>
+        <v>2672493</v>
       </c>
     </row>
     <row r="2431" spans="1:11" x14ac:dyDescent="0.25">
@@ -75167,7 +75224,7 @@
       </c>
       <c r="G2431" s="13">
         <f t="shared" si="41"/>
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
       <c r="H2431" s="6">
         <v>245000</v>
@@ -75176,7 +75233,7 @@
         <v>2326</v>
       </c>
       <c r="K2431" s="6">
-        <v>2501900</v>
+        <v>3484800</v>
       </c>
     </row>
     <row r="2432" spans="1:11" x14ac:dyDescent="0.25">
@@ -75197,7 +75254,7 @@
       </c>
       <c r="G2432" s="13">
         <f t="shared" si="41"/>
-        <v>2579070</v>
+        <v>3880800</v>
       </c>
       <c r="H2432" s="6">
         <v>238000</v>
@@ -75206,7 +75263,7 @@
         <v>2326</v>
       </c>
       <c r="K2432" s="6">
-        <v>2579070</v>
+        <v>3880800</v>
       </c>
     </row>
     <row r="2433" spans="1:11" x14ac:dyDescent="0.25">
@@ -75227,7 +75284,7 @@
       </c>
       <c r="G2433" s="13">
         <f t="shared" si="41"/>
-        <v>1921100</v>
+        <v>2672492</v>
       </c>
       <c r="H2433" s="6">
         <v>200000</v>
@@ -75236,7 +75293,7 @@
         <v>2326</v>
       </c>
       <c r="K2433" s="6">
-        <v>1921100</v>
+        <v>2672492</v>
       </c>
     </row>
     <row r="2434" spans="1:11" x14ac:dyDescent="0.25">
@@ -75257,7 +75314,7 @@
       </c>
       <c r="G2434" s="13">
         <f t="shared" si="41"/>
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
       <c r="H2434" s="6">
         <v>200000</v>
@@ -75266,7 +75323,7 @@
         <v>2326</v>
       </c>
       <c r="K2434" s="6">
-        <v>1640860</v>
+        <v>1705840</v>
       </c>
     </row>
     <row r="2435" spans="1:11" x14ac:dyDescent="0.25">
@@ -75287,7 +75344,7 @@
       </c>
       <c r="G2435" s="13">
         <f t="shared" ref="G2435:G2454" si="42">IF(J2435&lt;&gt;"",J2435*$J$1,K2435)</f>
-        <v>2579070</v>
+        <v>3582270</v>
       </c>
       <c r="H2435" s="6">
         <v>245000</v>
@@ -75296,7 +75353,7 @@
         <v>2326</v>
       </c>
       <c r="K2435" s="6">
-        <v>2579070</v>
+        <v>3582270</v>
       </c>
     </row>
     <row r="2436" spans="1:11" x14ac:dyDescent="0.25">
@@ -75317,7 +75374,7 @@
       </c>
       <c r="G2436" s="13">
         <f t="shared" si="42"/>
-        <v>2579070</v>
+        <v>3582270</v>
       </c>
       <c r="H2436" s="6">
         <v>245000</v>
@@ -75326,7 +75383,7 @@
         <v>2326</v>
       </c>
       <c r="K2436" s="6">
-        <v>2579070</v>
+        <v>3582270</v>
       </c>
     </row>
     <row r="2437" spans="1:11" x14ac:dyDescent="0.25">
@@ -75347,7 +75404,7 @@
       </c>
       <c r="G2437" s="13">
         <f t="shared" si="42"/>
-        <v>2579070</v>
+        <v>3582270</v>
       </c>
       <c r="H2437" s="6">
         <v>245000</v>
@@ -75356,7 +75413,7 @@
         <v>2326</v>
       </c>
       <c r="K2437" s="6">
-        <v>2579070</v>
+        <v>3582270</v>
       </c>
     </row>
     <row r="2438" spans="1:11" x14ac:dyDescent="0.25">
@@ -75377,7 +75434,7 @@
       </c>
       <c r="G2438" s="13">
         <f t="shared" si="42"/>
-        <v>2579070</v>
+        <v>3582270</v>
       </c>
       <c r="H2438" s="6">
         <v>245000</v>
@@ -75386,7 +75443,7 @@
         <v>2326</v>
       </c>
       <c r="K2438" s="6">
-        <v>2579070</v>
+        <v>3582270</v>
       </c>
     </row>
     <row r="2439" spans="1:11" x14ac:dyDescent="0.25">
@@ -75407,7 +75464,7 @@
       </c>
       <c r="G2439" s="13">
         <f t="shared" si="42"/>
-        <v>2579070</v>
+        <v>3582270</v>
       </c>
       <c r="H2439" s="6">
         <v>245000</v>
@@ -75416,7 +75473,7 @@
         <v>2326</v>
       </c>
       <c r="K2439" s="6">
-        <v>2579070</v>
+        <v>3582270</v>
       </c>
     </row>
     <row r="2440" spans="1:11" x14ac:dyDescent="0.25">
@@ -75437,7 +75494,7 @@
       </c>
       <c r="G2440" s="13">
         <f t="shared" si="42"/>
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
       <c r="H2440" s="6">
         <v>245000</v>
@@ -75446,7 +75503,7 @@
         <v>2326</v>
       </c>
       <c r="K2440" s="6">
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
     </row>
     <row r="2441" spans="1:11" x14ac:dyDescent="0.25">
@@ -75467,7 +75524,7 @@
       </c>
       <c r="G2441" s="13">
         <f t="shared" si="42"/>
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
       <c r="H2441" s="6">
         <v>245000</v>
@@ -75476,7 +75533,7 @@
         <v>2326</v>
       </c>
       <c r="K2441" s="6">
-        <v>2376000</v>
+        <v>3314210</v>
       </c>
     </row>
     <row r="2442" spans="1:11" x14ac:dyDescent="0.25">
@@ -75497,7 +75554,7 @@
       </c>
       <c r="G2442" s="13">
         <f t="shared" si="42"/>
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
       <c r="H2442" s="6">
         <v>245000</v>
@@ -75506,7 +75563,7 @@
         <v>2326</v>
       </c>
       <c r="K2442" s="6">
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
     </row>
     <row r="2443" spans="1:11" x14ac:dyDescent="0.25">
@@ -75527,7 +75584,7 @@
       </c>
       <c r="G2443" s="13">
         <f t="shared" si="42"/>
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
       <c r="H2443" s="6">
         <v>245000</v>
@@ -75536,7 +75593,7 @@
         <v>2326</v>
       </c>
       <c r="K2443" s="6">
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
     </row>
     <row r="2444" spans="1:11" x14ac:dyDescent="0.25">
@@ -75557,7 +75614,7 @@
       </c>
       <c r="G2444" s="13">
         <f t="shared" si="42"/>
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
       <c r="H2444" s="6">
         <v>245000</v>
@@ -75566,7 +75623,7 @@
         <v>2326</v>
       </c>
       <c r="K2444" s="6">
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
     </row>
     <row r="2445" spans="1:11" x14ac:dyDescent="0.25">
@@ -75587,7 +75644,7 @@
       </c>
       <c r="G2445" s="13">
         <f t="shared" si="42"/>
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
       <c r="H2445" s="6">
         <v>245000</v>
@@ -75596,7 +75653,7 @@
         <v>2326</v>
       </c>
       <c r="K2445" s="6">
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
     </row>
     <row r="2446" spans="1:11" x14ac:dyDescent="0.25">
@@ -75617,7 +75674,7 @@
       </c>
       <c r="G2446" s="13">
         <f t="shared" si="42"/>
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
       <c r="H2446" s="6">
         <v>245000</v>
@@ -75626,7 +75683,7 @@
         <v>2326</v>
       </c>
       <c r="K2446" s="6">
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
     </row>
     <row r="2447" spans="1:11" x14ac:dyDescent="0.25">
@@ -75647,7 +75704,7 @@
       </c>
       <c r="G2447" s="13">
         <f t="shared" si="42"/>
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
       <c r="H2447" s="6">
         <v>238000</v>
@@ -75656,7 +75713,7 @@
         <v>2326</v>
       </c>
       <c r="K2447" s="6">
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
     </row>
     <row r="2448" spans="1:11" x14ac:dyDescent="0.25">
@@ -75677,7 +75734,7 @@
       </c>
       <c r="G2448" s="13">
         <f t="shared" si="42"/>
-        <v>5420800</v>
+        <v>8395200</v>
       </c>
       <c r="H2448" s="6">
         <v>490000</v>
@@ -75686,7 +75743,7 @@
         <v>2326</v>
       </c>
       <c r="K2448" s="6">
-        <v>5420800</v>
+        <v>8395200</v>
       </c>
     </row>
     <row r="2449" spans="1:11" x14ac:dyDescent="0.25">
@@ -75707,7 +75764,7 @@
       </c>
       <c r="G2449" s="13">
         <f t="shared" si="42"/>
-        <v>5561600</v>
+        <v>8597600</v>
       </c>
       <c r="H2449" s="6">
         <v>490000</v>
@@ -75716,7 +75773,7 @@
         <v>2326</v>
       </c>
       <c r="K2449" s="6">
-        <v>5561600</v>
+        <v>8597600</v>
       </c>
     </row>
     <row r="2450" spans="1:11" x14ac:dyDescent="0.25">
@@ -75737,7 +75794,7 @@
       </c>
       <c r="G2450" s="13">
         <f t="shared" si="42"/>
-        <v>2168860</v>
+        <v>3021780</v>
       </c>
       <c r="H2450" s="6">
         <v>238000</v>
@@ -75746,7 +75803,7 @@
         <v>2326</v>
       </c>
       <c r="K2450" s="6">
-        <v>2168860</v>
+        <v>3021780</v>
       </c>
     </row>
     <row r="2451" spans="1:11" x14ac:dyDescent="0.25">
@@ -75767,7 +75824,7 @@
       </c>
       <c r="G2451" s="13">
         <f t="shared" si="42"/>
-        <v>2168860</v>
+        <v>3021780</v>
       </c>
       <c r="H2451" s="6">
         <v>238000</v>
@@ -75776,7 +75833,7 @@
         <v>2326</v>
       </c>
       <c r="K2451" s="6">
-        <v>2168860</v>
+        <v>3021780</v>
       </c>
     </row>
     <row r="2452" spans="1:11" x14ac:dyDescent="0.25">
@@ -75797,7 +75854,7 @@
       </c>
       <c r="G2452" s="13">
         <f t="shared" si="42"/>
-        <v>2168860</v>
+        <v>3021780</v>
       </c>
       <c r="H2452" s="6">
         <v>238000</v>
@@ -75806,7 +75863,7 @@
         <v>2326</v>
       </c>
       <c r="K2452" s="6">
-        <v>2168860</v>
+        <v>3021780</v>
       </c>
     </row>
     <row r="2453" spans="1:11" x14ac:dyDescent="0.25">
@@ -75827,7 +75884,7 @@
       </c>
       <c r="G2453" s="13">
         <f t="shared" si="42"/>
-        <v>2168860</v>
+        <v>3021780</v>
       </c>
       <c r="H2453" s="6">
         <v>238000</v>
@@ -75836,7 +75893,7 @@
         <v>2326</v>
       </c>
       <c r="K2453" s="6">
-        <v>2168860</v>
+        <v>3021780</v>
       </c>
     </row>
     <row r="2454" spans="1:11" x14ac:dyDescent="0.25">
@@ -75857,7 +75914,7 @@
       </c>
       <c r="G2454" s="13">
         <f t="shared" si="42"/>
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
       <c r="H2454" s="6">
         <v>259000</v>
@@ -75866,7 +75923,7 @@
         <v>2326</v>
       </c>
       <c r="K2454" s="6">
-        <v>2258210</v>
+        <v>3414400</v>
       </c>
     </row>
     <row r="2455" spans="1:11" x14ac:dyDescent="0.25">
@@ -75971,7 +76028,7 @@
       </c>
       <c r="G2458" s="13">
         <f t="shared" si="43"/>
-        <v>2542320</v>
+        <v>2779920</v>
       </c>
       <c r="H2458" s="6">
         <v>208600</v>
@@ -75980,7 +76037,7 @@
         <v>2326</v>
       </c>
       <c r="K2458" s="6">
-        <v>2542320</v>
+        <v>2779920</v>
       </c>
     </row>
     <row r="2459" spans="1:11" x14ac:dyDescent="0.25">
@@ -76001,7 +76058,7 @@
       </c>
       <c r="G2459" s="13">
         <f t="shared" si="43"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H2459" s="6">
         <v>200740</v>
@@ -76010,7 +76067,7 @@
         <v>2326</v>
       </c>
       <c r="K2459" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="2460" spans="1:11" x14ac:dyDescent="0.25">
@@ -76031,7 +76088,7 @@
       </c>
       <c r="G2460" s="13">
         <f t="shared" si="43"/>
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
       <c r="H2460" s="6">
         <v>200000</v>
@@ -76040,7 +76097,7 @@
         <v>2326</v>
       </c>
       <c r="K2460" s="6">
-        <v>1855540</v>
+        <v>2786210</v>
       </c>
     </row>
     <row r="2461" spans="1:11" x14ac:dyDescent="0.25">
@@ -76154,13 +76211,13 @@
       </c>
       <c r="G2464" s="13">
         <f t="shared" si="43"/>
-        <v>3455200</v>
+        <v>3738240</v>
       </c>
       <c r="I2464" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2464" s="6">
-        <v>3455200</v>
+        <v>3738240</v>
       </c>
     </row>
     <row r="2465" spans="1:11" x14ac:dyDescent="0.25">
@@ -76181,13 +76238,13 @@
       </c>
       <c r="G2465" s="13">
         <f t="shared" si="43"/>
-        <v>3455200</v>
+        <v>3738240</v>
       </c>
       <c r="I2465" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2465" s="6">
-        <v>3455200</v>
+        <v>3738240</v>
       </c>
     </row>
     <row r="2466" spans="1:11" x14ac:dyDescent="0.25">
@@ -76208,13 +76265,13 @@
       </c>
       <c r="G2466" s="13">
         <f t="shared" si="43"/>
-        <v>3455200</v>
+        <v>3738240</v>
       </c>
       <c r="I2466" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2466" s="6">
-        <v>3455200</v>
+        <v>3738240</v>
       </c>
     </row>
     <row r="2467" spans="1:11" x14ac:dyDescent="0.25">
@@ -76235,13 +76292,13 @@
       </c>
       <c r="G2467" s="13">
         <f t="shared" si="43"/>
-        <v>3455200</v>
+        <v>3738240</v>
       </c>
       <c r="I2467" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2467" s="6">
-        <v>3455200</v>
+        <v>3738240</v>
       </c>
     </row>
     <row r="2468" spans="1:11" x14ac:dyDescent="0.25">
@@ -76343,13 +76400,13 @@
       </c>
       <c r="G2471" s="13">
         <f t="shared" si="43"/>
-        <v>2018580</v>
+        <v>2810580</v>
       </c>
       <c r="I2471" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2471" s="6">
-        <v>2018580</v>
+        <v>2810580</v>
       </c>
     </row>
     <row r="2472" spans="1:11" x14ac:dyDescent="0.25">
@@ -76370,13 +76427,13 @@
       </c>
       <c r="G2472" s="13">
         <f t="shared" si="43"/>
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
       <c r="I2472" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2472" s="6">
-        <v>2779920</v>
+        <v>3057120</v>
       </c>
     </row>
     <row r="2473" spans="1:11" x14ac:dyDescent="0.25">
@@ -76451,13 +76508,13 @@
       </c>
       <c r="G2475" s="13">
         <f t="shared" si="43"/>
-        <v>2026700</v>
+        <v>2818700</v>
       </c>
       <c r="I2475" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2475" s="6">
-        <v>2026700</v>
+        <v>2818700</v>
       </c>
     </row>
     <row r="2476" spans="1:11" x14ac:dyDescent="0.25">
@@ -76478,13 +76535,13 @@
       </c>
       <c r="G2476" s="13">
         <f t="shared" si="43"/>
-        <v>2026700</v>
+        <v>2818700</v>
       </c>
       <c r="I2476" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2476" s="6">
-        <v>2026700</v>
+        <v>2818700</v>
       </c>
     </row>
     <row r="2477" spans="1:11" x14ac:dyDescent="0.25">
@@ -76505,13 +76562,13 @@
       </c>
       <c r="G2477" s="13">
         <f t="shared" si="43"/>
-        <v>1876430</v>
+        <v>2607500</v>
       </c>
       <c r="I2477" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2477" s="6">
-        <v>1876430</v>
+        <v>2607500</v>
       </c>
     </row>
     <row r="2478" spans="1:11" x14ac:dyDescent="0.25">
@@ -76532,13 +76589,13 @@
       </c>
       <c r="G2478" s="13">
         <f t="shared" si="43"/>
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
       <c r="I2478" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2478" s="6">
-        <v>2044110</v>
+        <v>2851200</v>
       </c>
     </row>
     <row r="2479" spans="1:11" x14ac:dyDescent="0.25">
@@ -76586,13 +76643,13 @@
       </c>
       <c r="G2480" s="13">
         <f t="shared" si="43"/>
-        <v>4505600</v>
+        <v>6265600</v>
       </c>
       <c r="I2480" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2480" s="6">
-        <v>4505600</v>
+        <v>6265600</v>
       </c>
     </row>
     <row r="2481" spans="1:11" x14ac:dyDescent="0.25">
@@ -76613,13 +76670,13 @@
       </c>
       <c r="G2481" s="13">
         <f t="shared" si="43"/>
-        <v>4505600</v>
+        <v>6265600</v>
       </c>
       <c r="I2481" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2481" s="6">
-        <v>4505600</v>
+        <v>6265600</v>
       </c>
     </row>
     <row r="2482" spans="1:11" x14ac:dyDescent="0.25">
@@ -76640,13 +76697,13 @@
       </c>
       <c r="G2482" s="13">
         <f t="shared" si="43"/>
-        <v>4505600</v>
+        <v>6265600</v>
       </c>
       <c r="I2482" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2482" s="6">
-        <v>4505600</v>
+        <v>6265600</v>
       </c>
     </row>
     <row r="2483" spans="1:11" x14ac:dyDescent="0.25">
@@ -76667,13 +76724,13 @@
       </c>
       <c r="G2483" s="13">
         <f t="shared" si="43"/>
-        <v>4505600</v>
+        <v>6265600</v>
       </c>
       <c r="I2483" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2483" s="6">
-        <v>4505600</v>
+        <v>6265600</v>
       </c>
     </row>
     <row r="2484" spans="1:11" x14ac:dyDescent="0.25">
@@ -76694,13 +76751,13 @@
       </c>
       <c r="G2484" s="13">
         <f t="shared" si="43"/>
-        <v>5583600</v>
+        <v>6058800</v>
       </c>
       <c r="I2484" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2484" s="6">
-        <v>5583600</v>
+        <v>6058800</v>
       </c>
     </row>
     <row r="2485" spans="1:11" x14ac:dyDescent="0.25">
@@ -76721,13 +76778,13 @@
       </c>
       <c r="G2485" s="13">
         <f t="shared" si="43"/>
-        <v>5583600</v>
+        <v>6058800</v>
       </c>
       <c r="I2485" s="4" t="s">
         <v>2326</v>
       </c>
       <c r="K2485" s="6">
-        <v>5583600</v>
+        <v>6058800</v>
       </c>
     </row>
     <row r="2486" spans="1:11" x14ac:dyDescent="0.25">
@@ -82592,7 +82649,7 @@
         <v>221800</v>
       </c>
       <c r="G2698" s="13">
-        <f t="shared" ref="G2698:G2742" si="49">IF(J2698&lt;&gt;"",J2698*$J$1,K2698)</f>
+        <f t="shared" ref="G2698:G2755" si="49">IF(J2698&lt;&gt;"",J2698*$J$1,K2698)</f>
         <v>1701900</v>
       </c>
       <c r="I2698" s="4" t="s">
@@ -83026,7 +83083,9 @@
       </c>
     </row>
     <row r="2715" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2715"/>
+      <c r="A2715" s="4" t="s">
+        <v>241</v>
+      </c>
       <c r="B2715" t="s">
         <v>2649</v>
       </c>
@@ -83622,6 +83681,9 @@
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
+      <c r="I2742" s="4" t="s">
+        <v>2674</v>
+      </c>
     </row>
     <row r="2743" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2743" s="4" t="s">
@@ -83637,7 +83699,14 @@
         <v>79804490</v>
       </c>
       <c r="E2743" s="2" t="s">
-        <v>2687</v>
+        <v>2686</v>
+      </c>
+      <c r="G2743" s="13">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I2743" s="4" t="s">
+        <v>2674</v>
       </c>
     </row>
     <row r="2744" spans="1:10" x14ac:dyDescent="0.25">
@@ -83645,7 +83714,7 @@
         <v>1984</v>
       </c>
       <c r="B2744" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="C2744">
         <v>665764</v>
@@ -83654,7 +83723,278 @@
         <v>79804782</v>
       </c>
       <c r="E2744" s="2" t="s">
+        <v>2687</v>
+      </c>
+      <c r="G2744" s="13">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I2744" s="4" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2745" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2745" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2745" t="s">
         <v>2688</v>
+      </c>
+      <c r="C2745">
+        <v>21969878</v>
+      </c>
+      <c r="D2745">
+        <v>80158484</v>
+      </c>
+      <c r="E2745">
+        <v>221826</v>
+      </c>
+      <c r="G2745" s="13">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I2745" s="4" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2746" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2746" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2746" t="s">
+        <v>2692</v>
+      </c>
+      <c r="C2746">
+        <v>21970283</v>
+      </c>
+      <c r="D2746">
+        <v>80158467</v>
+      </c>
+      <c r="E2746">
+        <v>216056</v>
+      </c>
+      <c r="G2746" s="13">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I2746" s="4" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2747" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2747" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2747" t="s">
+        <v>2694</v>
+      </c>
+      <c r="C2747">
+        <v>21971527</v>
+      </c>
+      <c r="D2747">
+        <v>80158453</v>
+      </c>
+      <c r="E2747" s="8">
+        <v>221825</v>
+      </c>
+      <c r="G2747" s="13">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I2747" s="4" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2748" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2748" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2748" t="s">
+        <v>2696</v>
+      </c>
+      <c r="C2748">
+        <v>21976437</v>
+      </c>
+      <c r="D2748">
+        <v>80158422</v>
+      </c>
+      <c r="E2748">
+        <v>216054</v>
+      </c>
+      <c r="G2748" s="13">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I2748" s="4" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2749" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2749" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2749" t="s">
+        <v>2697</v>
+      </c>
+      <c r="C2749">
+        <v>21976447</v>
+      </c>
+      <c r="D2749">
+        <v>80158374</v>
+      </c>
+      <c r="E2749">
+        <v>216055</v>
+      </c>
+      <c r="G2749" s="13">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I2749" s="4" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2750" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2750" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2750" t="s">
+        <v>2698</v>
+      </c>
+      <c r="C2750">
+        <v>21969947</v>
+      </c>
+      <c r="D2750">
+        <v>80142413</v>
+      </c>
+      <c r="E2750">
+        <v>216053</v>
+      </c>
+      <c r="G2750" s="13">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I2750" s="4" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2751" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2751" t="s">
+        <v>645</v>
+      </c>
+      <c r="B2751" t="s">
+        <v>2700</v>
+      </c>
+      <c r="C2751">
+        <v>21340899</v>
+      </c>
+      <c r="D2751">
+        <v>80040980</v>
+      </c>
+      <c r="E2751">
+        <v>208020</v>
+      </c>
+      <c r="G2751" s="13">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I2751" s="4" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2752" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2752" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2752" t="s">
+        <v>2702</v>
+      </c>
+      <c r="C2752">
+        <v>21847305</v>
+      </c>
+      <c r="D2752">
+        <v>79809762</v>
+      </c>
+      <c r="E2752">
+        <v>221824</v>
+      </c>
+      <c r="G2752" s="13">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I2752" s="4" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2753" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2753" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2753" t="s">
+        <v>2704</v>
+      </c>
+      <c r="C2753">
+        <v>21847371</v>
+      </c>
+      <c r="D2753">
+        <v>79809706</v>
+      </c>
+      <c r="E2753">
+        <v>221823</v>
+      </c>
+      <c r="G2753" s="13">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I2753" s="4" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2754" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2754" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2754" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C2754">
+        <v>21847434</v>
+      </c>
+      <c r="D2754">
+        <v>79809616</v>
+      </c>
+      <c r="E2754">
+        <v>221822</v>
+      </c>
+      <c r="G2754" s="13">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I2754" s="4" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2755" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2755" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2755" t="s">
+        <v>2706</v>
+      </c>
+      <c r="C2755">
+        <v>21847523</v>
+      </c>
+      <c r="D2755">
+        <v>79809549</v>
+      </c>
+      <c r="E2755">
+        <v>221821</v>
+      </c>
+      <c r="G2755" s="13">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I2755" s="4" t="s">
+        <v>2674</v>
       </c>
     </row>
   </sheetData>
@@ -83666,7 +84006,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="E5:V71"/>
+  <dimension ref="C5:V71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="28.85546875" customWidth="1"/>
@@ -83792,19 +84132,19 @@
       <c r="O16" s="8"/>
       <c r="T16" s="8"/>
     </row>
-    <row r="17" spans="5:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:22" x14ac:dyDescent="0.25">
       <c r="I17" s="8"/>
       <c r="L17" s="8"/>
       <c r="O17" s="8"/>
       <c r="T17" s="8"/>
     </row>
-    <row r="18" spans="5:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.25">
       <c r="I18" s="8"/>
       <c r="L18" s="8"/>
       <c r="O18" s="8"/>
       <c r="T18" s="8"/>
     </row>
-    <row r="19" spans="5:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.25">
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
       <c r="L19" s="8"/>
@@ -83813,7 +84153,7 @@
       <c r="P19" s="8"/>
       <c r="T19" s="8"/>
     </row>
-    <row r="20" spans="5:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:22" x14ac:dyDescent="0.25">
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
       <c r="L20" s="8"/>
@@ -83822,66 +84162,284 @@
       <c r="P20" s="8"/>
       <c r="T20" s="8"/>
     </row>
-    <row r="21" spans="5:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.25">
       <c r="I21" s="8"/>
       <c r="L21" s="8"/>
       <c r="O21" s="8"/>
       <c r="T21" s="8"/>
     </row>
-    <row r="22" spans="5:21" x14ac:dyDescent="0.25">
-      <c r="I22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="T22" s="8"/>
-    </row>
-    <row r="23" spans="5:21" x14ac:dyDescent="0.25">
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
-      <c r="T23" s="8"/>
-    </row>
-    <row r="24" spans="5:21" x14ac:dyDescent="0.25">
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-    </row>
-    <row r="25" spans="5:21" x14ac:dyDescent="0.25">
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-    </row>
-    <row r="26" spans="5:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>241</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2688</v>
+      </c>
+      <c r="F22">
+        <v>21969878</v>
+      </c>
+      <c r="G22">
+        <v>80158484</v>
+      </c>
+      <c r="H22">
+        <v>221826</v>
+      </c>
+      <c r="I22" s="8">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>2643</v>
+      </c>
+      <c r="L22" s="8">
+        <v>0</v>
+      </c>
+      <c r="M22" t="s">
+        <v>2689</v>
+      </c>
+      <c r="N22" s="8">
+        <v>0</v>
+      </c>
+      <c r="O22" s="8">
+        <v>0</v>
+      </c>
+      <c r="P22" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>2689</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22" t="s">
+        <v>2690</v>
+      </c>
+      <c r="T22" s="8">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2692</v>
+      </c>
+      <c r="F23">
+        <v>21970283</v>
+      </c>
+      <c r="G23">
+        <v>80158467</v>
+      </c>
+      <c r="H23">
+        <v>216056</v>
+      </c>
+      <c r="I23" s="8">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>2643</v>
+      </c>
+      <c r="L23" s="8">
+        <v>0</v>
+      </c>
+      <c r="M23" t="s">
+        <v>2693</v>
+      </c>
+      <c r="N23" s="8">
+        <v>0</v>
+      </c>
+      <c r="O23" s="8">
+        <v>0</v>
+      </c>
+      <c r="P23" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>2693</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23" t="s">
+        <v>2690</v>
+      </c>
+      <c r="T23" s="8">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2694</v>
+      </c>
+      <c r="F24">
+        <v>21971527</v>
+      </c>
+      <c r="G24">
+        <v>80158453</v>
+      </c>
+      <c r="H24" s="8">
+        <v>221825</v>
+      </c>
+      <c r="I24" s="8">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8">
+        <v>0</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>2643</v>
+      </c>
+      <c r="L24" s="8">
+        <v>0</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>2695</v>
+      </c>
+      <c r="N24" s="8">
+        <v>0</v>
+      </c>
+      <c r="O24" s="8">
+        <v>0</v>
+      </c>
+      <c r="P24" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>2695</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24" s="8" t="s">
+        <v>2690</v>
+      </c>
+      <c r="T24" s="8">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>214</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2696</v>
+      </c>
+      <c r="F25">
+        <v>21976437</v>
+      </c>
+      <c r="G25">
+        <v>80158422</v>
+      </c>
+      <c r="H25">
+        <v>216054</v>
+      </c>
+      <c r="I25" s="8">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>2643</v>
+      </c>
+      <c r="L25" s="8">
+        <v>0</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>2693</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0</v>
+      </c>
+      <c r="O25" s="8">
+        <v>0</v>
+      </c>
+      <c r="P25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="8" t="s">
+        <v>2693</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25" t="s">
+        <v>2690</v>
+      </c>
+      <c r="T25" s="8">
+        <v>0</v>
+      </c>
+      <c r="U25" s="8">
+        <v>0</v>
+      </c>
+      <c r="V25" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>214</v>
+      </c>
       <c r="E26" t="s">
-        <v>2684</v>
+        <v>2697</v>
       </c>
       <c r="F26">
-        <v>9653193</v>
+        <v>21976447</v>
       </c>
       <c r="G26">
-        <v>79804490</v>
+        <v>80158374</v>
+      </c>
+      <c r="H26">
+        <v>216055</v>
       </c>
       <c r="I26" s="8">
         <v>0</v>
       </c>
-      <c r="J26" s="8" t="s">
-        <v>2643</v>
+      <c r="J26" s="8">
+        <v>0</v>
       </c>
       <c r="K26" t="s">
         <v>2643</v>
@@ -83890,7 +84448,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>2685</v>
+        <v>2693</v>
       </c>
       <c r="N26" s="8">
         <v>0</v>
@@ -83898,91 +84456,399 @@
       <c r="O26" s="8">
         <v>0</v>
       </c>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-    </row>
-    <row r="27" spans="5:21" x14ac:dyDescent="0.25">
+      <c r="P26" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="8" t="s">
+        <v>2693</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26" t="s">
+        <v>2690</v>
+      </c>
+      <c r="T26" s="8">
+        <v>0</v>
+      </c>
+      <c r="U26" s="8">
+        <v>0</v>
+      </c>
+      <c r="V26" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C27">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>214</v>
+      </c>
       <c r="E27" t="s">
-        <v>2686</v>
+        <v>2698</v>
       </c>
       <c r="F27">
-        <v>665764</v>
+        <v>21969947</v>
       </c>
       <c r="G27">
-        <v>79804782</v>
-      </c>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-    </row>
-    <row r="28" spans="5:21" x14ac:dyDescent="0.25">
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="8"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
-    </row>
-    <row r="29" spans="5:21" x14ac:dyDescent="0.25">
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="8"/>
-    </row>
-    <row r="30" spans="5:21" x14ac:dyDescent="0.25">
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="8"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="8"/>
-    </row>
-    <row r="31" spans="5:21" x14ac:dyDescent="0.25">
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="8"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="8"/>
-    </row>
-    <row r="32" spans="5:21" x14ac:dyDescent="0.25">
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-      <c r="P32" s="8"/>
-      <c r="Q32" s="8"/>
-      <c r="T32" s="8"/>
-      <c r="U32" s="8"/>
+        <v>80142413</v>
+      </c>
+      <c r="H27">
+        <v>216053</v>
+      </c>
+      <c r="I27" s="8">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>2643</v>
+      </c>
+      <c r="L27" s="8">
+        <v>0</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>2699</v>
+      </c>
+      <c r="N27" s="8">
+        <v>0</v>
+      </c>
+      <c r="O27" s="8">
+        <v>0</v>
+      </c>
+      <c r="P27" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="8" t="s">
+        <v>2699</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27" t="s">
+        <v>2690</v>
+      </c>
+      <c r="T27" s="8">
+        <v>0</v>
+      </c>
+      <c r="U27" s="8">
+        <v>0</v>
+      </c>
+      <c r="V27" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C28">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>645</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2700</v>
+      </c>
+      <c r="F28">
+        <v>21340899</v>
+      </c>
+      <c r="G28">
+        <v>80040980</v>
+      </c>
+      <c r="H28">
+        <v>208020</v>
+      </c>
+      <c r="I28" s="8">
+        <v>0</v>
+      </c>
+      <c r="J28" s="8">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>2643</v>
+      </c>
+      <c r="L28" s="8">
+        <v>0</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>2701</v>
+      </c>
+      <c r="N28" s="8">
+        <v>0</v>
+      </c>
+      <c r="O28" s="8">
+        <v>0</v>
+      </c>
+      <c r="P28" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>2699</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28" t="s">
+        <v>2690</v>
+      </c>
+      <c r="T28" s="8">
+        <v>0</v>
+      </c>
+      <c r="U28" s="8">
+        <v>0</v>
+      </c>
+      <c r="V28" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C29">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>241</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2702</v>
+      </c>
+      <c r="F29">
+        <v>21847305</v>
+      </c>
+      <c r="G29">
+        <v>79809762</v>
+      </c>
+      <c r="H29">
+        <v>221824</v>
+      </c>
+      <c r="I29" s="8">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8">
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>2643</v>
+      </c>
+      <c r="L29" s="8">
+        <v>0</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>2703</v>
+      </c>
+      <c r="N29" s="8">
+        <v>0</v>
+      </c>
+      <c r="O29" s="8">
+        <v>0</v>
+      </c>
+      <c r="P29" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>2703</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29" t="s">
+        <v>2690</v>
+      </c>
+      <c r="T29" s="8">
+        <v>0</v>
+      </c>
+      <c r="U29" s="8">
+        <v>0</v>
+      </c>
+      <c r="V29" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C30">
+        <v>9</v>
+      </c>
+      <c r="D30" t="s">
+        <v>241</v>
+      </c>
+      <c r="E30" t="s">
+        <v>2704</v>
+      </c>
+      <c r="F30">
+        <v>21847371</v>
+      </c>
+      <c r="G30">
+        <v>79809706</v>
+      </c>
+      <c r="H30">
+        <v>221823</v>
+      </c>
+      <c r="I30" s="8">
+        <v>0</v>
+      </c>
+      <c r="J30" s="8">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>2643</v>
+      </c>
+      <c r="L30" s="8">
+        <v>0</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>2703</v>
+      </c>
+      <c r="N30" s="8">
+        <v>0</v>
+      </c>
+      <c r="O30" s="8">
+        <v>0</v>
+      </c>
+      <c r="P30" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="8" t="s">
+        <v>2703</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30" t="s">
+        <v>2690</v>
+      </c>
+      <c r="T30" s="8">
+        <v>0</v>
+      </c>
+      <c r="U30" s="8">
+        <v>0</v>
+      </c>
+      <c r="V30" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C31">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>241</v>
+      </c>
+      <c r="E31" t="s">
+        <v>2705</v>
+      </c>
+      <c r="F31">
+        <v>21847434</v>
+      </c>
+      <c r="G31">
+        <v>79809616</v>
+      </c>
+      <c r="H31">
+        <v>221822</v>
+      </c>
+      <c r="I31" s="8">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>2643</v>
+      </c>
+      <c r="L31" s="8">
+        <v>0</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>2703</v>
+      </c>
+      <c r="N31" s="8">
+        <v>0</v>
+      </c>
+      <c r="O31" s="8">
+        <v>0</v>
+      </c>
+      <c r="P31" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="8" t="s">
+        <v>2703</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31" t="s">
+        <v>2690</v>
+      </c>
+      <c r="T31" s="8">
+        <v>0</v>
+      </c>
+      <c r="U31" s="8">
+        <v>0</v>
+      </c>
+      <c r="V31" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C32">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>241</v>
+      </c>
+      <c r="E32" t="s">
+        <v>2706</v>
+      </c>
+      <c r="F32">
+        <v>21847523</v>
+      </c>
+      <c r="G32">
+        <v>79809549</v>
+      </c>
+      <c r="H32">
+        <v>221821</v>
+      </c>
+      <c r="I32" s="8">
+        <v>0</v>
+      </c>
+      <c r="J32" s="8">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>2643</v>
+      </c>
+      <c r="L32" s="8">
+        <v>0</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>2707</v>
+      </c>
+      <c r="N32" s="8">
+        <v>0</v>
+      </c>
+      <c r="O32" s="8">
+        <v>0</v>
+      </c>
+      <c r="P32" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="8" t="s">
+        <v>2707</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32" t="s">
+        <v>2690</v>
+      </c>
+      <c r="T32" s="8">
+        <v>0</v>
+      </c>
+      <c r="U32" s="8">
+        <v>0</v>
+      </c>
+      <c r="V32" t="s">
+        <v>2691</v>
+      </c>
     </row>
     <row r="33" spans="9:21" x14ac:dyDescent="0.25">
       <c r="I33" s="8"/>

--- a/model/data/descriptions-buy_price.xlsx
+++ b/model/data/descriptions-buy_price.xlsx
@@ -13,7 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AC$2633</definedName>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8352" uniqueCount="2723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8972" uniqueCount="2924">
   <si>
     <t>brand</t>
   </si>
@@ -7954,9 +7954,6 @@
     <t>صابون ابرو الیت اوراما مدل شفاف</t>
   </si>
   <si>
-    <t>ناعدد</t>
-  </si>
-  <si>
     <t>صابون ابرو ورشیپ مدل 1 مجموعه 4 عددی</t>
   </si>
   <si>
@@ -8092,12 +8089,6 @@
     <t>روغن آرگان محافظت‌کننده، شاداب‌کننده، تقویت‌کننده ، ترمیم‌کننده گلدن رز مدل ارگانیک SMOOTH &amp; SHINE مناسب موهای خشک، شکننده، آسیب دیده، انواع مو، کراتین شده، دکلره شده حجم 100 میلی‌لیتر</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>محصول در اکسل تعریف نشده</t>
-  </si>
-  <si>
     <t>رژگونه مایع مات ورشیپ مدل SMART CHEEK شماره C04</t>
   </si>
   <si>
@@ -8131,9 +8122,6 @@
     <t>مداد لب گلدن رز مدل TATTOO SOFT شماره 216 رنگ صورتی</t>
   </si>
   <si>
-    <t>۹٬۵۰۰٬۰۰۰</t>
-  </si>
-  <si>
     <t>مداد لب گلدن رز مدل TATTOO SOFT شماره 215 رنگ قرمز تیره</t>
   </si>
   <si>
@@ -8192,6 +8180,621 @@
   </si>
   <si>
     <t>مداد لب گلدن رز مدل TATTOO SOFT شماره 203 رنگ کرم صورتی</t>
+  </si>
+  <si>
+    <t>گلدن رز اکسپرت</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 49</t>
+  </si>
+  <si>
+    <t>برق ناخن گلدن رز کد 01</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل 143</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل Color Expert شماره 129</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل Color Expert شماره 54</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 43</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 91</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 87</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 80</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 64</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 86</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 36</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 25</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 11</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 91</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 115</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 40</t>
+  </si>
+  <si>
+    <t>رژ لب مایع گلدن رز شماره 55</t>
+  </si>
+  <si>
+    <t>رژ لب مایع گلدن رز شماره 57</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز شماره 30</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 85</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 106</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 33</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 77</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 104</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 68</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 68</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 08</t>
+  </si>
+  <si>
+    <t>مداد لب گلدن رز مدل Dream شماره 505</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 103</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 105</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 110</t>
+  </si>
+  <si>
+    <t>رژ لب مایع گلدن رز شماره 52</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 66</t>
+  </si>
+  <si>
+    <t>مداد چشم گلدن رز مدل DREAM شماره 420</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل Color Expert 02</t>
+  </si>
+  <si>
+    <t>مداد لب گلدن رز مدل DREAM شماره 503</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 102</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 13</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 107</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 100</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 98</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 77</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 76</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 73</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 36</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 127</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 93</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 138</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 33</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 46</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 44</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 10</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 21</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 118</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 106</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 126</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 45</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 59</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 07</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 40</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل کالر اکسپرت شماره 71</t>
+  </si>
+  <si>
+    <t>رژ لب مایع گلدن رز مدل متالز شماره 56</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 42</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 67</t>
+  </si>
+  <si>
+    <t>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 216</t>
+  </si>
+  <si>
+    <t>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 210</t>
+  </si>
+  <si>
+    <t>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 211</t>
+  </si>
+  <si>
+    <t>رژ لب جامد گلدن رز مدل Silky Shine شماره 203</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 25</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 72</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 35</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 104</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 101</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 60</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 54</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 53</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 132</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 124</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 22</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 06</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 67</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 65</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 111</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 76</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 18</t>
+  </si>
+  <si>
+    <t>رژ لب مایع گلدن رز شماره 51</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل کالر اکسپرت شماره 14</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل کالر اکسپرت شماره 85</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 32</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل کالر اکسپرت شماره 95</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 113</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 139</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 134</t>
+  </si>
+  <si>
+    <t>رژ لب مایع گلدن رز مدل متالز شماره 58</t>
+  </si>
+  <si>
+    <t>مداد لب گلدن رز مدل Dream شماره 508</t>
+  </si>
+  <si>
+    <t>مداد چشم گلدن رز مدل Dream شماره 419</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 78</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل Color Expert شماره 157</t>
+  </si>
+  <si>
+    <t>رژلب مدادی گلدن رز شماره 03</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 51</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 52</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 79</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 27</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 19</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 72</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 93</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 23</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 81</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 74</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 43</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 94</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 90</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 83</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 75</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل Color Expert شماره 407</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل Color Expert شماره 100</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل Color Expert 144</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 99</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 136</t>
+  </si>
+  <si>
+    <t>رژلب گلدن رز مدل Velvet شماره 21</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 119</t>
+  </si>
+  <si>
+    <t>رژ لب مایع گلدن رز مدل METALS شماره 57</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 108</t>
+  </si>
+  <si>
+    <t>رژ لب مایع گلدن رز شماره 53</t>
+  </si>
+  <si>
+    <t>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 212</t>
+  </si>
+  <si>
+    <t>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 214</t>
+  </si>
+  <si>
+    <t>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 213</t>
+  </si>
+  <si>
+    <t>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 205</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 101</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 69</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 133</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز شماره 115</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل Color Expert شماره 88</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 35</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 27</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 06</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل کالر اکسپرت شماره 61</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 131</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 90</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 46</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل Color Expert شماره 96</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 57</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 14</t>
+  </si>
+  <si>
+    <t>رژ لب جامد براق گلدن رز مدل سیلکی شاین شماره 201</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 08</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 41</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 109</t>
+  </si>
+  <si>
+    <t>ژل ابرو گلدن رز مدل So Cute</t>
+  </si>
+  <si>
+    <t>کانتور گلدن رز مدل Look</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 66</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 31</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 69</t>
+  </si>
+  <si>
+    <t>رژ لب مایع گلدن رز مدل 1221 شماره 31</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 20</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 20</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 70</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 58</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 79</t>
+  </si>
+  <si>
+    <t>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 219</t>
+  </si>
+  <si>
+    <t>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 215</t>
+  </si>
+  <si>
+    <t>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 218</t>
+  </si>
+  <si>
+    <t>رژ لب جامد گلدن رز مدل Silky Shine شماره 207</t>
+  </si>
+  <si>
+    <t>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 209</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 17</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 99</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 112</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 105</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 39</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 37</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 44</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 29</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 34</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 32</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 22</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 15</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 26</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل کالر اکسپرت شماره 89</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 50</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 63</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 57</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل Expert شماره 021</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 113</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل 62</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 07</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 55</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 05</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 50</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 30</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 16</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 86</t>
+  </si>
+  <si>
+    <t>لاک ناخن گلدن رز مدل color expert شماره 103</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل EXPERT شماره 82</t>
+  </si>
+  <si>
+    <t>رژلب مایع گلدن رز مدل Long Lasting شماره 13 به همراه مداد لب گلدن رز مدل Dream شماره 503</t>
+  </si>
+  <si>
+    <t>لاک گلدن رز مدل اکسپرت گلدن رز شماره 24</t>
+  </si>
+  <si>
+    <t>رژلب مایع گلدن رز مدل Long Lasting به همراه مداد لب گلدن رز مدل Dream</t>
+  </si>
+  <si>
+    <t>رژلب مایع گلدن رز مدل Long Lasting شماره 18 به همراه مداد لب گلدن رز مدل Dream شماره 527</t>
+  </si>
+  <si>
+    <t>رژلب مایع گلدن رز مدل Long Lasting شماره 16 به همراه مداد لب گلدن رز مدل Dream شماره 531</t>
+  </si>
+  <si>
+    <t>برق لب مایع پاستل شماره 301</t>
+  </si>
+  <si>
+    <t>کرم پودر مایع SPF20 گلدن رز مدل Moisture Touch مناسب برای انواع پوست شماره 101 حجم 30 میلی‌لیتر</t>
+  </si>
+  <si>
+    <t>کرم پودر مایع SPF20 گلدن رز مدل Moisture Touch مناسب برای انواع پوست شماره 103 حجم 30 میلی لیتر</t>
+  </si>
+  <si>
+    <t>کرم پودر مایع SPF20 گلدن رز مدل Moisture Touch شماره 105 مناسب برای انواع پوست حجم 30 میلی لیتر</t>
+  </si>
+  <si>
+    <t>رژلب جامد مات گلدن رز مدل Mix شماره 02 مجموعه 4 عددی</t>
+  </si>
+  <si>
+    <t>رژلب جامد مات گلدن رز مدل Mix شماره 03 مجموعه 4 عددی</t>
   </si>
 </sst>
 </file>
@@ -8626,7 +9229,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AC2775"/>
+  <dimension ref="A1:AC2984"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" style="4" customWidth="1"/>
@@ -8713,7 +9316,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="G2" s="13">
         <f t="shared" ref="G2:G59" si="0">IF(J2&lt;&gt;"",J2*$J$1,K2)</f>
@@ -83089,7 +83692,7 @@
         <v>214</v>
       </c>
       <c r="B2710" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="C2710">
         <v>21340736</v>
@@ -83113,7 +83716,7 @@
         <v>214</v>
       </c>
       <c r="B2711" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="C2711">
         <v>21331881</v>
@@ -83137,7 +83740,7 @@
         <v>214</v>
       </c>
       <c r="B2712" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="C2712">
         <v>21331829</v>
@@ -83164,7 +83767,7 @@
         <v>214</v>
       </c>
       <c r="B2713" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="C2713">
         <v>21331800</v>
@@ -83191,7 +83794,7 @@
         <v>214</v>
       </c>
       <c r="B2714" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="C2714">
         <v>21331710</v>
@@ -83218,7 +83821,7 @@
         <v>241</v>
       </c>
       <c r="B2715" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="C2715">
         <v>21200331</v>
@@ -83242,7 +83845,7 @@
         <v>241</v>
       </c>
       <c r="B2716" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="C2716">
         <v>21524444</v>
@@ -83266,7 +83869,7 @@
         <v>241</v>
       </c>
       <c r="B2717" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="C2717">
         <v>21524496</v>
@@ -83290,7 +83893,7 @@
         <v>241</v>
       </c>
       <c r="B2718" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="C2718">
         <v>21524530</v>
@@ -83314,7 +83917,7 @@
         <v>241</v>
       </c>
       <c r="B2719" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="C2719">
         <v>21524824</v>
@@ -83338,7 +83941,7 @@
         <v>241</v>
       </c>
       <c r="B2720" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="C2720">
         <v>21524951</v>
@@ -83362,7 +83965,7 @@
         <v>241</v>
       </c>
       <c r="B2721" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
       <c r="C2721">
         <v>21524978</v>
@@ -83386,7 +83989,7 @@
         <v>241</v>
       </c>
       <c r="B2722" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="C2722">
         <v>21525006</v>
@@ -83410,7 +84013,7 @@
         <v>241</v>
       </c>
       <c r="B2723" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="C2723">
         <v>21525081</v>
@@ -83434,7 +84037,7 @@
         <v>241</v>
       </c>
       <c r="B2724" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="C2724">
         <v>21527272</v>
@@ -83458,7 +84061,7 @@
         <v>241</v>
       </c>
       <c r="B2725" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="C2725">
         <v>21527276</v>
@@ -83482,7 +84085,7 @@
         <v>241</v>
       </c>
       <c r="B2726" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="C2726">
         <v>21527286</v>
@@ -83506,7 +84109,7 @@
         <v>241</v>
       </c>
       <c r="B2727" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
       <c r="C2727">
         <v>21527290</v>
@@ -83530,7 +84133,7 @@
         <v>241</v>
       </c>
       <c r="B2728" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="C2728">
         <v>21538684</v>
@@ -83554,7 +84157,7 @@
         <v>241</v>
       </c>
       <c r="B2729" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="C2729">
         <v>21538698</v>
@@ -83578,7 +84181,7 @@
         <v>241</v>
       </c>
       <c r="B2730" t="s">
-        <v>2664</v>
+        <v>2663</v>
       </c>
       <c r="C2730">
         <v>21538714</v>
@@ -83602,7 +84205,7 @@
         <v>241</v>
       </c>
       <c r="B2731" t="s">
-        <v>2665</v>
+        <v>2664</v>
       </c>
       <c r="C2731">
         <v>21538729</v>
@@ -83626,7 +84229,7 @@
         <v>241</v>
       </c>
       <c r="B2732" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
       <c r="C2732">
         <v>21538904</v>
@@ -83650,7 +84253,7 @@
         <v>241</v>
       </c>
       <c r="B2733" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="C2733">
         <v>21538933</v>
@@ -83674,7 +84277,7 @@
         <v>241</v>
       </c>
       <c r="B2734" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="C2734">
         <v>21538951</v>
@@ -83698,7 +84301,7 @@
         <v>241</v>
       </c>
       <c r="B2735" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="C2735">
         <v>21538960</v>
@@ -83722,7 +84325,7 @@
         <v>241</v>
       </c>
       <c r="B2736" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
       <c r="C2736">
         <v>21538972</v>
@@ -83743,10 +84346,10 @@
     </row>
     <row r="2737" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2737" s="4" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="B2737" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="C2737">
         <v>17728589</v>
@@ -83767,7 +84370,7 @@
         <v>241</v>
       </c>
       <c r="B2738" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="C2738">
         <v>1764023</v>
@@ -83780,7 +84383,7 @@
         <v>6006000</v>
       </c>
       <c r="I2738" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2738" s="11">
         <v>2.86</v>
@@ -83791,7 +84394,7 @@
         <v>1304</v>
       </c>
       <c r="B2739" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
       <c r="C2739">
         <v>960798</v>
@@ -83800,7 +84403,7 @@
         <v>79041303</v>
       </c>
       <c r="E2739" s="4" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="F2739" s="8"/>
       <c r="G2739" s="13">
@@ -83809,7 +84412,7 @@
       </c>
       <c r="H2739"/>
       <c r="I2739" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2739" s="8"/>
     </row>
@@ -83818,7 +84421,7 @@
         <v>1304</v>
       </c>
       <c r="B2740" s="4" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
       <c r="C2740" s="2">
         <v>960855</v>
@@ -83827,14 +84430,14 @@
         <v>56188599</v>
       </c>
       <c r="E2740" s="2" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
       <c r="G2740" s="13">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="I2740" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="2741" spans="1:11" x14ac:dyDescent="0.25">
@@ -83842,7 +84445,7 @@
         <v>1304</v>
       </c>
       <c r="B2741" s="4" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="C2741" s="2">
         <v>960847</v>
@@ -83851,14 +84454,14 @@
         <v>56187760</v>
       </c>
       <c r="E2741" s="2" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
       <c r="G2741" s="13">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="I2741" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="2742" spans="1:11" x14ac:dyDescent="0.25">
@@ -83866,7 +84469,7 @@
         <v>1304</v>
       </c>
       <c r="B2742" s="4" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
       <c r="C2742" s="2">
         <v>14220359</v>
@@ -83875,14 +84478,14 @@
         <v>56278423</v>
       </c>
       <c r="E2742" s="2" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="G2742" s="13">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="I2742" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="2743" spans="1:11" x14ac:dyDescent="0.25">
@@ -83890,7 +84493,7 @@
         <v>6</v>
       </c>
       <c r="B2743" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
       <c r="C2743">
         <v>9653193</v>
@@ -83899,14 +84502,14 @@
         <v>79804490</v>
       </c>
       <c r="E2743" s="2" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="G2743" s="13">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="I2743" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="2744" spans="1:11" x14ac:dyDescent="0.25">
@@ -83914,7 +84517,7 @@
         <v>1984</v>
       </c>
       <c r="B2744" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="C2744">
         <v>665764</v>
@@ -83923,14 +84526,14 @@
         <v>79804782</v>
       </c>
       <c r="E2744" s="2" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="G2744" s="13">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="I2744" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="2745" spans="1:11" x14ac:dyDescent="0.25">
@@ -83938,7 +84541,7 @@
         <v>241</v>
       </c>
       <c r="B2745" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
       <c r="C2745">
         <v>21969878</v>
@@ -83954,7 +84557,7 @@
         <v>7581000</v>
       </c>
       <c r="I2745" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2745" s="11">
         <v>3.61</v>
@@ -83965,7 +84568,7 @@
         <v>214</v>
       </c>
       <c r="B2746" t="s">
-        <v>2691</v>
+        <v>2688</v>
       </c>
       <c r="C2746">
         <v>21970283</v>
@@ -83981,7 +84584,7 @@
         <v>3397000</v>
       </c>
       <c r="I2746" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="K2746" s="15">
         <v>3397000</v>
@@ -83992,7 +84595,7 @@
         <v>241</v>
       </c>
       <c r="B2747" t="s">
-        <v>2692</v>
+        <v>2689</v>
       </c>
       <c r="C2747">
         <v>21971527</v>
@@ -84008,7 +84611,7 @@
         <v>3045000</v>
       </c>
       <c r="I2747" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2747" s="11">
         <v>1.45</v>
@@ -84019,7 +84622,7 @@
         <v>214</v>
       </c>
       <c r="B2748" t="s">
-        <v>2693</v>
+        <v>2690</v>
       </c>
       <c r="C2748">
         <v>21976437</v>
@@ -84035,7 +84638,7 @@
         <v>3397000</v>
       </c>
       <c r="I2748" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="K2748" s="15">
         <v>3397000</v>
@@ -84046,7 +84649,7 @@
         <v>214</v>
       </c>
       <c r="B2749" t="s">
-        <v>2694</v>
+        <v>2691</v>
       </c>
       <c r="C2749">
         <v>21976447</v>
@@ -84062,7 +84665,7 @@
         <v>3397000</v>
       </c>
       <c r="I2749" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="K2749" s="15">
         <v>3397000</v>
@@ -84073,7 +84676,7 @@
         <v>214</v>
       </c>
       <c r="B2750" t="s">
-        <v>2695</v>
+        <v>2692</v>
       </c>
       <c r="C2750">
         <v>21969947</v>
@@ -84089,7 +84692,7 @@
         <v>3397000</v>
       </c>
       <c r="I2750" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="K2750" s="15">
         <v>3397000</v>
@@ -84100,7 +84703,7 @@
         <v>645</v>
       </c>
       <c r="B2751" t="s">
-        <v>2696</v>
+        <v>2693</v>
       </c>
       <c r="C2751">
         <v>21340899</v>
@@ -84116,7 +84719,7 @@
         <v>2150000</v>
       </c>
       <c r="I2751" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="K2751" s="15">
         <v>2150000</v>
@@ -84127,7 +84730,7 @@
         <v>241</v>
       </c>
       <c r="B2752" t="s">
-        <v>2697</v>
+        <v>2694</v>
       </c>
       <c r="C2752">
         <v>21847305</v>
@@ -84143,7 +84746,7 @@
         <v>3045000</v>
       </c>
       <c r="I2752" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2752" s="11">
         <v>1.45</v>
@@ -84154,7 +84757,7 @@
         <v>241</v>
       </c>
       <c r="B2753" t="s">
-        <v>2698</v>
+        <v>2695</v>
       </c>
       <c r="C2753">
         <v>21847371</v>
@@ -84170,7 +84773,7 @@
         <v>3045000</v>
       </c>
       <c r="I2753" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2753" s="11">
         <v>1.45</v>
@@ -84181,7 +84784,7 @@
         <v>241</v>
       </c>
       <c r="B2754" t="s">
-        <v>2699</v>
+        <v>2696</v>
       </c>
       <c r="C2754">
         <v>21847434</v>
@@ -84197,7 +84800,7 @@
         <v>3045000</v>
       </c>
       <c r="I2754" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2754" s="11">
         <v>1.45</v>
@@ -84208,7 +84811,7 @@
         <v>241</v>
       </c>
       <c r="B2755" t="s">
-        <v>2700</v>
+        <v>2697</v>
       </c>
       <c r="C2755">
         <v>21847523</v>
@@ -84224,7 +84827,7 @@
         <v>4494000</v>
       </c>
       <c r="I2755" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2755" s="11">
         <v>2.14</v>
@@ -84235,7 +84838,7 @@
         <v>241</v>
       </c>
       <c r="B2756" t="s">
-        <v>2701</v>
+        <v>2698</v>
       </c>
       <c r="C2756">
         <v>21988711</v>
@@ -84251,7 +84854,7 @@
         <v>5922000</v>
       </c>
       <c r="I2756" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2756" s="11">
         <v>2.82</v>
@@ -84262,7 +84865,7 @@
         <v>241</v>
       </c>
       <c r="B2757" t="s">
-        <v>2703</v>
+        <v>2699</v>
       </c>
       <c r="C2757">
         <v>21988696</v>
@@ -84278,7 +84881,7 @@
         <v>5922000</v>
       </c>
       <c r="I2757" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2757" s="11">
         <v>2.82</v>
@@ -84289,7 +84892,7 @@
         <v>241</v>
       </c>
       <c r="B2758" t="s">
-        <v>2704</v>
+        <v>2700</v>
       </c>
       <c r="C2758">
         <v>21988673</v>
@@ -84305,7 +84908,7 @@
         <v>5922000</v>
       </c>
       <c r="I2758" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2758" s="11">
         <v>2.82</v>
@@ -84316,7 +84919,7 @@
         <v>241</v>
       </c>
       <c r="B2759" t="s">
-        <v>2705</v>
+        <v>2701</v>
       </c>
       <c r="C2759">
         <v>21988586</v>
@@ -84332,7 +84935,7 @@
         <v>5922000</v>
       </c>
       <c r="I2759" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2759" s="11">
         <v>2.82</v>
@@ -84343,7 +84946,7 @@
         <v>241</v>
       </c>
       <c r="B2760" t="s">
-        <v>2706</v>
+        <v>2702</v>
       </c>
       <c r="C2760">
         <v>21988556</v>
@@ -84359,7 +84962,7 @@
         <v>5922000</v>
       </c>
       <c r="I2760" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2760" s="11">
         <v>2.82</v>
@@ -84370,7 +84973,7 @@
         <v>241</v>
       </c>
       <c r="B2761" t="s">
-        <v>2707</v>
+        <v>2703</v>
       </c>
       <c r="C2761">
         <v>21988508</v>
@@ -84386,7 +84989,7 @@
         <v>5922000</v>
       </c>
       <c r="I2761" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2761" s="11">
         <v>2.82</v>
@@ -84397,7 +85000,7 @@
         <v>241</v>
       </c>
       <c r="B2762" t="s">
-        <v>2708</v>
+        <v>2704</v>
       </c>
       <c r="C2762">
         <v>21988459</v>
@@ -84409,11 +85012,11 @@
         <v>221835</v>
       </c>
       <c r="G2762" s="13">
-        <f t="shared" ref="G2762:G2775" si="50">IF(J2762&lt;&gt;"",J2762*$J$1,K2762)</f>
+        <f t="shared" ref="G2762:G2825" si="50">IF(J2762&lt;&gt;"",J2762*$J$1,K2762)</f>
         <v>5922000</v>
       </c>
       <c r="I2762" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2762" s="11">
         <v>2.82</v>
@@ -84424,7 +85027,7 @@
         <v>241</v>
       </c>
       <c r="B2763" t="s">
-        <v>2709</v>
+        <v>2705</v>
       </c>
       <c r="C2763">
         <v>21988245</v>
@@ -84440,7 +85043,7 @@
         <v>5922000</v>
       </c>
       <c r="I2763" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2763" s="11">
         <v>2.82</v>
@@ -84451,7 +85054,7 @@
         <v>241</v>
       </c>
       <c r="B2764" t="s">
-        <v>2710</v>
+        <v>2706</v>
       </c>
       <c r="C2764">
         <v>21988214</v>
@@ -84467,7 +85070,7 @@
         <v>5922000</v>
       </c>
       <c r="I2764" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2764" s="11">
         <v>2.82</v>
@@ -84478,7 +85081,7 @@
         <v>241</v>
       </c>
       <c r="B2765" t="s">
-        <v>2711</v>
+        <v>2707</v>
       </c>
       <c r="C2765">
         <v>21988166</v>
@@ -84494,7 +85097,7 @@
         <v>5922000</v>
       </c>
       <c r="I2765" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2765" s="11">
         <v>2.82</v>
@@ -84505,7 +85108,7 @@
         <v>241</v>
       </c>
       <c r="B2766" t="s">
-        <v>2712</v>
+        <v>2708</v>
       </c>
       <c r="C2766">
         <v>21988087</v>
@@ -84521,7 +85124,7 @@
         <v>5922000</v>
       </c>
       <c r="I2766" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2766" s="11">
         <v>2.82</v>
@@ -84532,7 +85135,7 @@
         <v>241</v>
       </c>
       <c r="B2767" t="s">
-        <v>2713</v>
+        <v>2709</v>
       </c>
       <c r="C2767">
         <v>21988040</v>
@@ -84548,7 +85151,7 @@
         <v>5922000</v>
       </c>
       <c r="I2767" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2767" s="11">
         <v>2.82</v>
@@ -84559,7 +85162,7 @@
         <v>241</v>
       </c>
       <c r="B2768" t="s">
-        <v>2722</v>
+        <v>2718</v>
       </c>
       <c r="C2768">
         <v>21987809</v>
@@ -84575,7 +85178,7 @@
         <v>5922000</v>
       </c>
       <c r="I2768" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2768" s="11">
         <v>2.82</v>
@@ -84586,7 +85189,7 @@
         <v>241</v>
       </c>
       <c r="B2769" t="s">
-        <v>2714</v>
+        <v>2710</v>
       </c>
       <c r="C2769">
         <v>21987741</v>
@@ -84602,7 +85205,7 @@
         <v>5922000</v>
       </c>
       <c r="I2769" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2769" s="11">
         <v>2.82</v>
@@ -84613,7 +85216,7 @@
         <v>241</v>
       </c>
       <c r="B2770" t="s">
-        <v>2715</v>
+        <v>2711</v>
       </c>
       <c r="C2770">
         <v>21987678</v>
@@ -84629,7 +85232,7 @@
         <v>5922000</v>
       </c>
       <c r="I2770" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2770" s="11">
         <v>2.82</v>
@@ -84640,7 +85243,7 @@
         <v>241</v>
       </c>
       <c r="B2771" t="s">
-        <v>2716</v>
+        <v>2712</v>
       </c>
       <c r="C2771">
         <v>21979245</v>
@@ -84656,7 +85259,7 @@
         <v>1890000</v>
       </c>
       <c r="I2771" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2771" s="11">
         <v>0.9</v>
@@ -84667,7 +85270,7 @@
         <v>241</v>
       </c>
       <c r="B2772" t="s">
-        <v>2717</v>
+        <v>2713</v>
       </c>
       <c r="C2772">
         <v>21979219</v>
@@ -84683,7 +85286,7 @@
         <v>1890000</v>
       </c>
       <c r="I2772" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2772" s="11">
         <v>0.9</v>
@@ -84694,7 +85297,7 @@
         <v>241</v>
       </c>
       <c r="B2773" t="s">
-        <v>2718</v>
+        <v>2714</v>
       </c>
       <c r="C2773">
         <v>21978842</v>
@@ -84710,7 +85313,7 @@
         <v>1890000</v>
       </c>
       <c r="I2773" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2773" s="11">
         <v>0.9</v>
@@ -84721,7 +85324,7 @@
         <v>241</v>
       </c>
       <c r="B2774" t="s">
-        <v>2719</v>
+        <v>2715</v>
       </c>
       <c r="C2774">
         <v>21978798</v>
@@ -84737,7 +85340,7 @@
         <v>1890000</v>
       </c>
       <c r="I2774" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2774" s="11">
         <v>0.9</v>
@@ -84748,7 +85351,7 @@
         <v>241</v>
       </c>
       <c r="B2775" t="s">
-        <v>2720</v>
+        <v>2716</v>
       </c>
       <c r="C2775">
         <v>21988426</v>
@@ -84757,17 +85360,5657 @@
         <v>80628922</v>
       </c>
       <c r="E2775" s="2" t="s">
-        <v>2721</v>
+        <v>2717</v>
       </c>
       <c r="G2775" s="13">
         <f t="shared" si="50"/>
         <v>5922000</v>
       </c>
       <c r="I2775" s="4" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J2775" s="11">
         <v>2.82</v>
+      </c>
+    </row>
+    <row r="2776" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2776" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2776" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C2776">
+        <v>1664820</v>
+      </c>
+      <c r="D2776">
+        <v>81993925</v>
+      </c>
+      <c r="E2776">
+        <v>231040</v>
+      </c>
+      <c r="G2776" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2776" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2776" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2777" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2777" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2777" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C2777">
+        <v>4722851</v>
+      </c>
+      <c r="D2777">
+        <v>81993881</v>
+      </c>
+      <c r="E2777">
+        <v>231001</v>
+      </c>
+      <c r="G2777" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2777" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2777" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2778" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2778" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2778" t="s">
+        <v>2722</v>
+      </c>
+      <c r="C2778">
+        <v>16731094</v>
+      </c>
+      <c r="D2778">
+        <v>81993771</v>
+      </c>
+      <c r="E2778">
+        <v>231101</v>
+      </c>
+      <c r="G2778" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2778" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2778" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2779" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2779" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2779" t="s">
+        <v>2723</v>
+      </c>
+      <c r="C2779">
+        <v>16001660</v>
+      </c>
+      <c r="D2779">
+        <v>81993726</v>
+      </c>
+      <c r="E2779">
+        <v>231096</v>
+      </c>
+      <c r="G2779" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2779" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2779" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2780" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2780" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2780" t="s">
+        <v>2724</v>
+      </c>
+      <c r="C2780">
+        <v>16001383</v>
+      </c>
+      <c r="D2780">
+        <v>81993682</v>
+      </c>
+      <c r="E2780">
+        <v>231043</v>
+      </c>
+      <c r="G2780" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2780" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2780" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2781" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2781" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2781" t="s">
+        <v>2725</v>
+      </c>
+      <c r="C2781">
+        <v>1664638</v>
+      </c>
+      <c r="D2781">
+        <v>81993649</v>
+      </c>
+      <c r="E2781">
+        <v>231037</v>
+      </c>
+      <c r="G2781" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2781" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2781" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2782" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2782" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2782" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C2782">
+        <v>2928995</v>
+      </c>
+      <c r="D2782">
+        <v>81993606</v>
+      </c>
+      <c r="E2782">
+        <v>221677</v>
+      </c>
+      <c r="G2782" s="13">
+        <f t="shared" si="50"/>
+        <v>1890000</v>
+      </c>
+      <c r="I2782" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2782" s="11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="2783" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2783" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2783" t="s">
+        <v>2726</v>
+      </c>
+      <c r="C2783">
+        <v>1050804</v>
+      </c>
+      <c r="D2783">
+        <v>81993552</v>
+      </c>
+      <c r="E2783">
+        <v>231074</v>
+      </c>
+      <c r="G2783" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2783" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2783" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2784" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2784" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2784" t="s">
+        <v>2727</v>
+      </c>
+      <c r="C2784">
+        <v>1050752</v>
+      </c>
+      <c r="D2784">
+        <v>81993515</v>
+      </c>
+      <c r="E2784">
+        <v>231070</v>
+      </c>
+      <c r="G2784" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2784" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2784" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2785" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2785" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2785" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C2785">
+        <v>1050613</v>
+      </c>
+      <c r="D2785">
+        <v>81993481</v>
+      </c>
+      <c r="E2785">
+        <v>231064</v>
+      </c>
+      <c r="G2785" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2785" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2785" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2786" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2786" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2786" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C2786">
+        <v>1050418</v>
+      </c>
+      <c r="D2786">
+        <v>81993445</v>
+      </c>
+      <c r="E2786">
+        <v>231051</v>
+      </c>
+      <c r="G2786" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2786" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2786" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2787" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2787" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2787" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C2787">
+        <v>1681422</v>
+      </c>
+      <c r="D2787">
+        <v>81993412</v>
+      </c>
+      <c r="E2787">
+        <v>231069</v>
+      </c>
+      <c r="G2787" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2787" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2787" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2788" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2788" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2788" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C2788">
+        <v>1591908</v>
+      </c>
+      <c r="D2788">
+        <v>81993361</v>
+      </c>
+      <c r="E2788">
+        <v>221759</v>
+      </c>
+      <c r="G2788" s="13">
+        <f t="shared" si="50"/>
+        <v>3045000</v>
+      </c>
+      <c r="I2788" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2788" s="11">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="2789" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2789" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2789" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C2789">
+        <v>1049433</v>
+      </c>
+      <c r="D2789">
+        <v>81993297</v>
+      </c>
+      <c r="E2789">
+        <v>231036</v>
+      </c>
+      <c r="G2789" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2789" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2789" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2790" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2790" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2790" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C2790">
+        <v>1049324</v>
+      </c>
+      <c r="D2790">
+        <v>81993249</v>
+      </c>
+      <c r="E2790">
+        <v>231021</v>
+      </c>
+      <c r="G2790" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2790" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2790" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2791" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2791" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2791" t="s">
+        <v>2733</v>
+      </c>
+      <c r="C2791">
+        <v>1049284</v>
+      </c>
+      <c r="D2791">
+        <v>81993215</v>
+      </c>
+      <c r="E2791">
+        <v>231008</v>
+      </c>
+      <c r="G2791" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2791" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2791" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2792" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2792" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2792" t="s">
+        <v>2734</v>
+      </c>
+      <c r="C2792">
+        <v>1685324</v>
+      </c>
+      <c r="D2792">
+        <v>81993182</v>
+      </c>
+      <c r="E2792">
+        <v>231074</v>
+      </c>
+      <c r="G2792" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2792" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2792" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2793" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2793" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2793" t="s">
+        <v>2735</v>
+      </c>
+      <c r="C2793">
+        <v>1051254</v>
+      </c>
+      <c r="D2793">
+        <v>81993142</v>
+      </c>
+      <c r="E2793">
+        <v>231093</v>
+      </c>
+      <c r="G2793" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2793" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2793" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2794" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2794" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2794" t="s">
+        <v>2736</v>
+      </c>
+      <c r="C2794">
+        <v>1652796</v>
+      </c>
+      <c r="D2794">
+        <v>81993055</v>
+      </c>
+      <c r="E2794">
+        <v>231034</v>
+      </c>
+      <c r="G2794" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2794" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2794" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2795" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2795" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2795" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C2795">
+        <v>2244454</v>
+      </c>
+      <c r="D2795">
+        <v>81993022</v>
+      </c>
+      <c r="E2795">
+        <v>221709</v>
+      </c>
+      <c r="G2795" s="13">
+        <f t="shared" si="50"/>
+        <v>2730000</v>
+      </c>
+      <c r="I2795" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2795" s="11">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="2796" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2796" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2796" t="s">
+        <v>2738</v>
+      </c>
+      <c r="C2796">
+        <v>2244476</v>
+      </c>
+      <c r="D2796">
+        <v>81992990</v>
+      </c>
+      <c r="E2796">
+        <v>221705</v>
+      </c>
+      <c r="G2796" s="13">
+        <f t="shared" si="50"/>
+        <v>2730000</v>
+      </c>
+      <c r="I2796" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2796" s="11">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="2797" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2797" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2797" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C2797">
+        <v>2150611</v>
+      </c>
+      <c r="D2797">
+        <v>81992945</v>
+      </c>
+      <c r="E2797">
+        <v>231025</v>
+      </c>
+      <c r="G2797" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2797" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2797" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2798" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2798" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2798" t="s">
+        <v>2740</v>
+      </c>
+      <c r="C2798">
+        <v>2153551</v>
+      </c>
+      <c r="D2798">
+        <v>81992899</v>
+      </c>
+      <c r="E2798">
+        <v>231068</v>
+      </c>
+      <c r="G2798" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2798" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2798" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2799" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2799" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2799" t="s">
+        <v>2741</v>
+      </c>
+      <c r="C2799">
+        <v>1685480</v>
+      </c>
+      <c r="D2799">
+        <v>81992863</v>
+      </c>
+      <c r="E2799">
+        <v>231086</v>
+      </c>
+      <c r="G2799" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2799" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2799" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2800" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2800" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2800" t="s">
+        <v>2742</v>
+      </c>
+      <c r="C2800">
+        <v>1876082</v>
+      </c>
+      <c r="D2800">
+        <v>81992820</v>
+      </c>
+      <c r="E2800">
+        <v>231028</v>
+      </c>
+      <c r="G2800" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2800" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2800" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2801" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2801" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2801" t="s">
+        <v>2743</v>
+      </c>
+      <c r="C2801">
+        <v>1681314</v>
+      </c>
+      <c r="D2801">
+        <v>81992771</v>
+      </c>
+      <c r="E2801">
+        <v>231062</v>
+      </c>
+      <c r="G2801" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2801" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2801" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2802" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2802" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2802" t="s">
+        <v>2744</v>
+      </c>
+      <c r="C2802">
+        <v>1051042</v>
+      </c>
+      <c r="D2802">
+        <v>81992724</v>
+      </c>
+      <c r="E2802">
+        <v>231084</v>
+      </c>
+      <c r="G2802" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2802" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2802" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2803" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2803" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2803" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C2803">
+        <v>1050474</v>
+      </c>
+      <c r="D2803">
+        <v>81992667</v>
+      </c>
+      <c r="E2803">
+        <v>231055</v>
+      </c>
+      <c r="G2803" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2803" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2803" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2804" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2804" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2804" t="s">
+        <v>2746</v>
+      </c>
+      <c r="C2804">
+        <v>1677982</v>
+      </c>
+      <c r="D2804">
+        <v>81992596</v>
+      </c>
+      <c r="E2804">
+        <v>231055</v>
+      </c>
+      <c r="G2804" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2804" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2804" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2805" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2805" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2805" t="s">
+        <v>2747</v>
+      </c>
+      <c r="C2805">
+        <v>1049272</v>
+      </c>
+      <c r="D2805">
+        <v>81992547</v>
+      </c>
+      <c r="E2805">
+        <v>231006</v>
+      </c>
+      <c r="G2805" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2805" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2805" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2806" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2806" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2806" t="s">
+        <v>2748</v>
+      </c>
+      <c r="C2806">
+        <v>1595601</v>
+      </c>
+      <c r="D2806">
+        <v>81992494</v>
+      </c>
+      <c r="E2806">
+        <v>221704</v>
+      </c>
+      <c r="G2806" s="13">
+        <f t="shared" si="50"/>
+        <v>1890000</v>
+      </c>
+      <c r="I2806" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2806" s="11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="2807" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2807" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2807" t="s">
+        <v>2749</v>
+      </c>
+      <c r="C2807">
+        <v>1051029</v>
+      </c>
+      <c r="D2807">
+        <v>81992442</v>
+      </c>
+      <c r="E2807">
+        <v>231083</v>
+      </c>
+      <c r="G2807" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2807" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2807" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2808" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2808" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2808" t="s">
+        <v>2750</v>
+      </c>
+      <c r="C2808">
+        <v>1685465</v>
+      </c>
+      <c r="D2808">
+        <v>81992383</v>
+      </c>
+      <c r="E2808">
+        <v>231085</v>
+      </c>
+      <c r="G2808" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2808" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2808" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2809" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2809" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2809" t="s">
+        <v>2751</v>
+      </c>
+      <c r="C2809">
+        <v>1051164</v>
+      </c>
+      <c r="D2809">
+        <v>81992301</v>
+      </c>
+      <c r="E2809">
+        <v>231090</v>
+      </c>
+      <c r="G2809" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2809" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2809" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2810" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2810" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2810" t="s">
+        <v>2752</v>
+      </c>
+      <c r="C2810">
+        <v>2539651</v>
+      </c>
+      <c r="D2810">
+        <v>81992237</v>
+      </c>
+      <c r="E2810">
+        <v>221710</v>
+      </c>
+      <c r="G2810" s="13">
+        <f t="shared" si="50"/>
+        <v>2730000</v>
+      </c>
+      <c r="I2810" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2810" s="11">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="2811" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2811" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2811" t="s">
+        <v>2753</v>
+      </c>
+      <c r="C2811">
+        <v>1677963</v>
+      </c>
+      <c r="D2811">
+        <v>81992179</v>
+      </c>
+      <c r="E2811">
+        <v>231053</v>
+      </c>
+      <c r="G2811" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2811" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2811" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2812" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2812" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2812" t="s">
+        <v>2754</v>
+      </c>
+      <c r="C2812">
+        <v>1051844</v>
+      </c>
+      <c r="D2812">
+        <v>81992130</v>
+      </c>
+      <c r="E2812">
+        <v>221259</v>
+      </c>
+      <c r="G2812" s="13">
+        <f t="shared" si="50"/>
+        <v>1890000</v>
+      </c>
+      <c r="I2812" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2812" s="11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="2813" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2813" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2813" t="s">
+        <v>2755</v>
+      </c>
+      <c r="C2813">
+        <v>16000855</v>
+      </c>
+      <c r="D2813">
+        <v>81992064</v>
+      </c>
+      <c r="E2813">
+        <v>231002</v>
+      </c>
+      <c r="G2813" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2813" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2813" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2814" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2814" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2814" t="s">
+        <v>2756</v>
+      </c>
+      <c r="C2814">
+        <v>1051381</v>
+      </c>
+      <c r="D2814">
+        <v>81991958</v>
+      </c>
+      <c r="E2814">
+        <v>221540</v>
+      </c>
+      <c r="G2814" s="13">
+        <f t="shared" si="50"/>
+        <v>1890000</v>
+      </c>
+      <c r="I2814" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2814" s="11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="2815" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2815" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2815" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C2815">
+        <v>1051004</v>
+      </c>
+      <c r="D2815">
+        <v>81957919</v>
+      </c>
+      <c r="E2815">
+        <v>231082</v>
+      </c>
+      <c r="G2815" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2815" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2815" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2816" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2816" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2816" t="s">
+        <v>2758</v>
+      </c>
+      <c r="C2816">
+        <v>1624879</v>
+      </c>
+      <c r="D2816">
+        <v>81957860</v>
+      </c>
+      <c r="E2816">
+        <v>231009</v>
+      </c>
+      <c r="G2816" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2816" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2816" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2817" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2817" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2817" t="s">
+        <v>2759</v>
+      </c>
+      <c r="C2817">
+        <v>1051089</v>
+      </c>
+      <c r="D2817">
+        <v>81957768</v>
+      </c>
+      <c r="E2817">
+        <v>231087</v>
+      </c>
+      <c r="G2817" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2817" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2817" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2818" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2818" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2818" t="s">
+        <v>2760</v>
+      </c>
+      <c r="C2818">
+        <v>1050943</v>
+      </c>
+      <c r="D2818">
+        <v>81957713</v>
+      </c>
+      <c r="E2818">
+        <v>231080</v>
+      </c>
+      <c r="G2818" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2818" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2818" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2819" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2819" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2819" t="s">
+        <v>2761</v>
+      </c>
+      <c r="C2819">
+        <v>1050901</v>
+      </c>
+      <c r="D2819">
+        <v>81957650</v>
+      </c>
+      <c r="E2819">
+        <v>231078</v>
+      </c>
+      <c r="G2819" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2819" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2819" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2820" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2820" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2820" t="s">
+        <v>2762</v>
+      </c>
+      <c r="C2820">
+        <v>1050547</v>
+      </c>
+      <c r="D2820">
+        <v>81957577</v>
+      </c>
+      <c r="E2820">
+        <v>231062</v>
+      </c>
+      <c r="G2820" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2820" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2820" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2821" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2821" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2821" t="s">
+        <v>2763</v>
+      </c>
+      <c r="C2821">
+        <v>1681288</v>
+      </c>
+      <c r="D2821">
+        <v>81957541</v>
+      </c>
+      <c r="E2821">
+        <v>231104</v>
+      </c>
+      <c r="G2821" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2821" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2821" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2822" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2822" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2822" t="s">
+        <v>2764</v>
+      </c>
+      <c r="C2822">
+        <v>1050512</v>
+      </c>
+      <c r="D2822">
+        <v>81957501</v>
+      </c>
+      <c r="E2822">
+        <v>231105</v>
+      </c>
+      <c r="G2822" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2822" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2822" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2823" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2823" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2823" t="s">
+        <v>2765</v>
+      </c>
+      <c r="C2823">
+        <v>1652749</v>
+      </c>
+      <c r="D2823">
+        <v>81957468</v>
+      </c>
+      <c r="E2823">
+        <v>231031</v>
+      </c>
+      <c r="G2823" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2823" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2823" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2824" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2824" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2824" t="s">
+        <v>2766</v>
+      </c>
+      <c r="C2824">
+        <v>1051588</v>
+      </c>
+      <c r="D2824">
+        <v>81957437</v>
+      </c>
+      <c r="E2824">
+        <v>231106</v>
+      </c>
+      <c r="G2824" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2824" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2824" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2825" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2825" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2825" t="s">
+        <v>2767</v>
+      </c>
+      <c r="C2825">
+        <v>1050858</v>
+      </c>
+      <c r="D2825">
+        <v>81957416</v>
+      </c>
+      <c r="E2825">
+        <v>231075</v>
+      </c>
+      <c r="G2825" s="13">
+        <f t="shared" si="50"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2825" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2825" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2826" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2826" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2826" t="s">
+        <v>2768</v>
+      </c>
+      <c r="C2826">
+        <v>1051688</v>
+      </c>
+      <c r="D2826">
+        <v>81957389</v>
+      </c>
+      <c r="E2826">
+        <v>231107</v>
+      </c>
+      <c r="G2826" s="13">
+        <f t="shared" ref="G2826:G2889" si="51">IF(J2826&lt;&gt;"",J2826*$J$1,K2826)</f>
+        <v>1722000</v>
+      </c>
+      <c r="I2826" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2826" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2827" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2827" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2827" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2827">
+        <v>1049426</v>
+      </c>
+      <c r="D2827">
+        <v>81957352</v>
+      </c>
+      <c r="E2827">
+        <v>231028</v>
+      </c>
+      <c r="G2827" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2827" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2827" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2828" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2828" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2828" t="s">
+        <v>2770</v>
+      </c>
+      <c r="C2828">
+        <v>1050266</v>
+      </c>
+      <c r="D2828">
+        <v>81957313</v>
+      </c>
+      <c r="E2828">
+        <v>231039</v>
+      </c>
+      <c r="G2828" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2828" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2828" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2829" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2829" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2829" t="s">
+        <v>2771</v>
+      </c>
+      <c r="C2829">
+        <v>1050226</v>
+      </c>
+      <c r="D2829">
+        <v>81957294</v>
+      </c>
+      <c r="E2829">
+        <v>231038</v>
+      </c>
+      <c r="G2829" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2829" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2829" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2830" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2830" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2830" t="s">
+        <v>2772</v>
+      </c>
+      <c r="C2830">
+        <v>1624245</v>
+      </c>
+      <c r="D2830">
+        <v>81957256</v>
+      </c>
+      <c r="E2830">
+        <v>231007</v>
+      </c>
+      <c r="G2830" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2830" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2830" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2831" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2831" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2831" t="s">
+        <v>2773</v>
+      </c>
+      <c r="C2831">
+        <v>1631301</v>
+      </c>
+      <c r="D2831">
+        <v>81957216</v>
+      </c>
+      <c r="E2831">
+        <v>231017</v>
+      </c>
+      <c r="G2831" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2831" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2831" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2832" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2832" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2832" t="s">
+        <v>2774</v>
+      </c>
+      <c r="C2832">
+        <v>1051351</v>
+      </c>
+      <c r="D2832">
+        <v>81957166</v>
+      </c>
+      <c r="E2832">
+        <v>231108</v>
+      </c>
+      <c r="G2832" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2832" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2832" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2833" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2833" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2833" t="s">
+        <v>2775</v>
+      </c>
+      <c r="C2833">
+        <v>1051077</v>
+      </c>
+      <c r="D2833">
+        <v>81957123</v>
+      </c>
+      <c r="E2833">
+        <v>231086</v>
+      </c>
+      <c r="G2833" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2833" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2833" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2834" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2834" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2834" t="s">
+        <v>2776</v>
+      </c>
+      <c r="C2834">
+        <v>1051575</v>
+      </c>
+      <c r="D2834">
+        <v>81957083</v>
+      </c>
+      <c r="E2834">
+        <v>231109</v>
+      </c>
+      <c r="G2834" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2834" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2834" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2835" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2835" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2835" t="s">
+        <v>2777</v>
+      </c>
+      <c r="C2835">
+        <v>1050237</v>
+      </c>
+      <c r="D2835">
+        <v>81956966</v>
+      </c>
+      <c r="E2835">
+        <v>231110</v>
+      </c>
+      <c r="G2835" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2835" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2835" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2836" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2836" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2836" t="s">
+        <v>2778</v>
+      </c>
+      <c r="C2836">
+        <v>1050371</v>
+      </c>
+      <c r="D2836">
+        <v>81956926</v>
+      </c>
+      <c r="E2836">
+        <v>231111</v>
+      </c>
+      <c r="G2836" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2836" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2836" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2837" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2837" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2837" t="s">
+        <v>2779</v>
+      </c>
+      <c r="C2837">
+        <v>1623960</v>
+      </c>
+      <c r="D2837">
+        <v>81956873</v>
+      </c>
+      <c r="E2837">
+        <v>231005</v>
+      </c>
+      <c r="G2837" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2837" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2837" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2838" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2838" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2838" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C2838">
+        <v>1049435</v>
+      </c>
+      <c r="D2838">
+        <v>81956828</v>
+      </c>
+      <c r="E2838">
+        <v>231034</v>
+      </c>
+      <c r="G2838" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2838" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2838" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2839" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2839" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2839" t="s">
+        <v>2781</v>
+      </c>
+      <c r="C2839">
+        <v>958692</v>
+      </c>
+      <c r="D2839">
+        <v>81956784</v>
+      </c>
+      <c r="E2839">
+        <v>231058</v>
+      </c>
+      <c r="G2839" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2839" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2839" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2840" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2840" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2840" t="s">
+        <v>2782</v>
+      </c>
+      <c r="C2840">
+        <v>5687373</v>
+      </c>
+      <c r="D2840">
+        <v>81956756</v>
+      </c>
+      <c r="E2840">
+        <v>221711</v>
+      </c>
+      <c r="G2840" s="13">
+        <f t="shared" si="51"/>
+        <v>2730000</v>
+      </c>
+      <c r="I2840" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2840" s="11">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="2841" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2841" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2841" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C2841">
+        <v>1050202</v>
+      </c>
+      <c r="D2841">
+        <v>81956714</v>
+      </c>
+      <c r="E2841">
+        <v>231036</v>
+      </c>
+      <c r="G2841" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2841" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2841" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2842" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2842" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2842" t="s">
+        <v>2784</v>
+      </c>
+      <c r="C2842">
+        <v>1050455</v>
+      </c>
+      <c r="D2842">
+        <v>81956675</v>
+      </c>
+      <c r="E2842">
+        <v>231054</v>
+      </c>
+      <c r="G2842" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2842" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2842" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2843" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2843" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2843" t="s">
+        <v>2785</v>
+      </c>
+      <c r="C2843">
+        <v>22277033</v>
+      </c>
+      <c r="D2843">
+        <v>81956622</v>
+      </c>
+      <c r="E2843">
+        <v>221847</v>
+      </c>
+      <c r="G2843" s="13">
+        <f t="shared" si="51"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2843" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2843" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2844" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2844" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2844" t="s">
+        <v>2786</v>
+      </c>
+      <c r="C2844">
+        <v>22275579</v>
+      </c>
+      <c r="D2844">
+        <v>81956592</v>
+      </c>
+      <c r="E2844">
+        <v>221848</v>
+      </c>
+      <c r="G2844" s="13">
+        <f t="shared" si="51"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2844" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2844" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2845" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2845" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2845" t="s">
+        <v>2787</v>
+      </c>
+      <c r="C2845">
+        <v>22275718</v>
+      </c>
+      <c r="D2845">
+        <v>81956563</v>
+      </c>
+      <c r="E2845">
+        <v>221849</v>
+      </c>
+      <c r="G2845" s="13">
+        <f t="shared" si="51"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2845" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2845" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2846" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2846" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2846" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C2846">
+        <v>22265352</v>
+      </c>
+      <c r="D2846">
+        <v>81956529</v>
+      </c>
+      <c r="E2846">
+        <v>221850</v>
+      </c>
+      <c r="G2846" s="13">
+        <f t="shared" si="51"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2846" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2846" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2847" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2847" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2847" t="s">
+        <v>2789</v>
+      </c>
+      <c r="C2847">
+        <v>1648240</v>
+      </c>
+      <c r="D2847">
+        <v>81956508</v>
+      </c>
+      <c r="E2847">
+        <v>231021</v>
+      </c>
+      <c r="G2847" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2847" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2847" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2848" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2848" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2848" t="s">
+        <v>2790</v>
+      </c>
+      <c r="C2848">
+        <v>1050501</v>
+      </c>
+      <c r="D2848">
+        <v>81956485</v>
+      </c>
+      <c r="E2848">
+        <v>231059</v>
+      </c>
+      <c r="G2848" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2848" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2848" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2849" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2849" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2849" t="s">
+        <v>2791</v>
+      </c>
+      <c r="C2849">
+        <v>1049428</v>
+      </c>
+      <c r="D2849">
+        <v>81956461</v>
+      </c>
+      <c r="E2849">
+        <v>231030</v>
+      </c>
+      <c r="G2849" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2849" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2849" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2850" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2850" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2850" t="s">
+        <v>2792</v>
+      </c>
+      <c r="C2850">
+        <v>1685433</v>
+      </c>
+      <c r="D2850">
+        <v>81956437</v>
+      </c>
+      <c r="E2850">
+        <v>231084</v>
+      </c>
+      <c r="G2850" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2850" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2850" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2851" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2851" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2851" t="s">
+        <v>2793</v>
+      </c>
+      <c r="C2851">
+        <v>1685386</v>
+      </c>
+      <c r="D2851">
+        <v>81956404</v>
+      </c>
+      <c r="E2851">
+        <v>231081</v>
+      </c>
+      <c r="G2851" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2851" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2851" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2852" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2852" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2852" t="s">
+        <v>2794</v>
+      </c>
+      <c r="C2852">
+        <v>1050387</v>
+      </c>
+      <c r="D2852">
+        <v>81956385</v>
+      </c>
+      <c r="E2852">
+        <v>231047</v>
+      </c>
+      <c r="G2852" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2852" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2852" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2853" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2853" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2853" t="s">
+        <v>2795</v>
+      </c>
+      <c r="C2853">
+        <v>1050319</v>
+      </c>
+      <c r="D2853">
+        <v>81956359</v>
+      </c>
+      <c r="E2853">
+        <v>231043</v>
+      </c>
+      <c r="G2853" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2853" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2853" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2854" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2854" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2854" t="s">
+        <v>2796</v>
+      </c>
+      <c r="C2854">
+        <v>1050305</v>
+      </c>
+      <c r="D2854">
+        <v>81956335</v>
+      </c>
+      <c r="E2854">
+        <v>231042</v>
+      </c>
+      <c r="G2854" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2854" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2854" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2855" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2855" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2855" t="s">
+        <v>2797</v>
+      </c>
+      <c r="C2855">
+        <v>1051638</v>
+      </c>
+      <c r="D2855">
+        <v>81956302</v>
+      </c>
+      <c r="E2855">
+        <v>231098</v>
+      </c>
+      <c r="G2855" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2855" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2855" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2856" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2856" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2856" t="s">
+        <v>2798</v>
+      </c>
+      <c r="C2856">
+        <v>1051540</v>
+      </c>
+      <c r="D2856">
+        <v>81956259</v>
+      </c>
+      <c r="E2856">
+        <v>231095</v>
+      </c>
+      <c r="G2856" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2856" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2856" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2857" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2857" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2857" t="s">
+        <v>2799</v>
+      </c>
+      <c r="C2857">
+        <v>1049312</v>
+      </c>
+      <c r="D2857">
+        <v>81956215</v>
+      </c>
+      <c r="E2857">
+        <v>231018</v>
+      </c>
+      <c r="G2857" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2857" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2857" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2858" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2858" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2858" t="s">
+        <v>2800</v>
+      </c>
+      <c r="C2858">
+        <v>1049260</v>
+      </c>
+      <c r="D2858">
+        <v>81956170</v>
+      </c>
+      <c r="E2858">
+        <v>231004</v>
+      </c>
+      <c r="G2858" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2858" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2858" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2859" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2859" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2859" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C2859">
+        <v>1677976</v>
+      </c>
+      <c r="D2859">
+        <v>81956131</v>
+      </c>
+      <c r="E2859">
+        <v>231054</v>
+      </c>
+      <c r="G2859" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2859" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2859" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2860" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2860" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2860" t="s">
+        <v>2802</v>
+      </c>
+      <c r="C2860">
+        <v>1050430</v>
+      </c>
+      <c r="D2860">
+        <v>81956091</v>
+      </c>
+      <c r="E2860">
+        <v>231052</v>
+      </c>
+      <c r="G2860" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2860" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2860" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2861" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2861" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2861" t="s">
+        <v>2803</v>
+      </c>
+      <c r="C2861">
+        <v>1051181</v>
+      </c>
+      <c r="D2861">
+        <v>81956050</v>
+      </c>
+      <c r="E2861">
+        <v>231112</v>
+      </c>
+      <c r="G2861" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2861" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2861" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2862" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2862" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2862" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C2862">
+        <v>1050532</v>
+      </c>
+      <c r="D2862">
+        <v>81956017</v>
+      </c>
+      <c r="E2862">
+        <v>231104</v>
+      </c>
+      <c r="G2862" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2862" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2862" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2863" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2863" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2863" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C2863">
+        <v>1631250</v>
+      </c>
+      <c r="D2863">
+        <v>81955977</v>
+      </c>
+      <c r="E2863">
+        <v>231014</v>
+      </c>
+      <c r="G2863" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2863" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2863" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2864" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2864" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2864" t="s">
+        <v>2806</v>
+      </c>
+      <c r="C2864">
+        <v>5346155</v>
+      </c>
+      <c r="D2864">
+        <v>81955904</v>
+      </c>
+      <c r="E2864">
+        <v>221851</v>
+      </c>
+      <c r="G2864" s="13">
+        <f t="shared" si="51"/>
+        <v>2730000</v>
+      </c>
+      <c r="I2864" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2864" s="11">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="2865" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2865" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2865" t="s">
+        <v>2807</v>
+      </c>
+      <c r="C2865">
+        <v>958665</v>
+      </c>
+      <c r="D2865">
+        <v>81955860</v>
+      </c>
+      <c r="E2865">
+        <v>231010</v>
+      </c>
+      <c r="G2865" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2865" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2865" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2866" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2866" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2866" t="s">
+        <v>2808</v>
+      </c>
+      <c r="C2866">
+        <v>958642</v>
+      </c>
+      <c r="D2866">
+        <v>81955830</v>
+      </c>
+      <c r="E2866">
+        <v>231068</v>
+      </c>
+      <c r="G2866" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2866" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2866" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2867" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2867" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2867" t="s">
+        <v>2809</v>
+      </c>
+      <c r="C2867">
+        <v>1049421</v>
+      </c>
+      <c r="D2867">
+        <v>81955798</v>
+      </c>
+      <c r="E2867">
+        <v>231027</v>
+      </c>
+      <c r="G2867" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2867" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2867" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2868" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2868" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2868" t="s">
+        <v>2810</v>
+      </c>
+      <c r="C2868">
+        <v>958367</v>
+      </c>
+      <c r="D2868">
+        <v>81955762</v>
+      </c>
+      <c r="E2868">
+        <v>231113</v>
+      </c>
+      <c r="G2868" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2868" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2868" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2869" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2869" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2869" t="s">
+        <v>2811</v>
+      </c>
+      <c r="C2869">
+        <v>1051235</v>
+      </c>
+      <c r="D2869">
+        <v>81955737</v>
+      </c>
+      <c r="E2869">
+        <v>231092</v>
+      </c>
+      <c r="G2869" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2869" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2869" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2870" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2870" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2870" t="s">
+        <v>2812</v>
+      </c>
+      <c r="C2870">
+        <v>1051692</v>
+      </c>
+      <c r="D2870">
+        <v>81955686</v>
+      </c>
+      <c r="E2870">
+        <v>231114</v>
+      </c>
+      <c r="G2870" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2870" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2870" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2871" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2871" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2871" t="s">
+        <v>2813</v>
+      </c>
+      <c r="C2871">
+        <v>1051652</v>
+      </c>
+      <c r="D2871">
+        <v>81955630</v>
+      </c>
+      <c r="E2871">
+        <v>231115</v>
+      </c>
+      <c r="G2871" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2871" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2871" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2872" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2872" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2872" t="s">
+        <v>2814</v>
+      </c>
+      <c r="C2872">
+        <v>5690957</v>
+      </c>
+      <c r="D2872">
+        <v>81955557</v>
+      </c>
+      <c r="E2872">
+        <v>221852</v>
+      </c>
+      <c r="G2872" s="13">
+        <f t="shared" si="51"/>
+        <v>2730000</v>
+      </c>
+      <c r="I2872" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2872" s="11">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="2873" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2873" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2873" t="s">
+        <v>2815</v>
+      </c>
+      <c r="C2873">
+        <v>13192362</v>
+      </c>
+      <c r="D2873">
+        <v>81955334</v>
+      </c>
+      <c r="E2873">
+        <v>221853</v>
+      </c>
+      <c r="G2873" s="13">
+        <f t="shared" si="51"/>
+        <v>1890000</v>
+      </c>
+      <c r="I2873" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2873" s="11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="2874" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2874" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2874" t="s">
+        <v>2816</v>
+      </c>
+      <c r="C2874">
+        <v>1522843</v>
+      </c>
+      <c r="D2874">
+        <v>81954035</v>
+      </c>
+      <c r="E2874">
+        <v>221258</v>
+      </c>
+      <c r="G2874" s="13">
+        <f t="shared" si="51"/>
+        <v>1890000</v>
+      </c>
+      <c r="I2874" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2874" s="11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="2875" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2875" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2875" t="s">
+        <v>2748</v>
+      </c>
+      <c r="C2875">
+        <v>1583712</v>
+      </c>
+      <c r="D2875">
+        <v>81953985</v>
+      </c>
+      <c r="E2875">
+        <v>221704</v>
+      </c>
+      <c r="G2875" s="13">
+        <f t="shared" si="51"/>
+        <v>1890000</v>
+      </c>
+      <c r="I2875" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2875" s="11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="2876" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2876" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2876" t="s">
+        <v>2817</v>
+      </c>
+      <c r="C2876">
+        <v>1050564</v>
+      </c>
+      <c r="D2876">
+        <v>81953903</v>
+      </c>
+      <c r="E2876">
+        <v>231116</v>
+      </c>
+      <c r="G2876" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2876" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2876" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2877" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2877" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2877" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C2877">
+        <v>16000998</v>
+      </c>
+      <c r="D2877">
+        <v>81953861</v>
+      </c>
+      <c r="E2877">
+        <v>231117</v>
+      </c>
+      <c r="G2877" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2877" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2877" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2878" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2878" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2878" t="s">
+        <v>2819</v>
+      </c>
+      <c r="C2878">
+        <v>1559977</v>
+      </c>
+      <c r="D2878">
+        <v>81953837</v>
+      </c>
+      <c r="E2878">
+        <v>221854</v>
+      </c>
+      <c r="G2878" s="13">
+        <f t="shared" si="51"/>
+        <v>3045000</v>
+      </c>
+      <c r="I2878" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2878" s="11">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="2879" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2879" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2879" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C2879">
+        <v>1050287</v>
+      </c>
+      <c r="D2879">
+        <v>81953801</v>
+      </c>
+      <c r="E2879">
+        <v>231118</v>
+      </c>
+      <c r="G2879" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2879" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2879" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2880" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2880" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2880" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C2880">
+        <v>1050296</v>
+      </c>
+      <c r="D2880">
+        <v>81953563</v>
+      </c>
+      <c r="E2880">
+        <v>231119</v>
+      </c>
+      <c r="G2880" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2880" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2880" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2881" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2881" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2881" t="s">
+        <v>2822</v>
+      </c>
+      <c r="C2881">
+        <v>1050590</v>
+      </c>
+      <c r="D2881">
+        <v>81953540</v>
+      </c>
+      <c r="E2881">
+        <v>231063</v>
+      </c>
+      <c r="G2881" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2881" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2881" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2882" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2882" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2882" t="s">
+        <v>2823</v>
+      </c>
+      <c r="C2882">
+        <v>1049407</v>
+      </c>
+      <c r="D2882">
+        <v>81953492</v>
+      </c>
+      <c r="E2882">
+        <v>231023</v>
+      </c>
+      <c r="G2882" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2882" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2882" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2883" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2883" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2883" t="s">
+        <v>2824</v>
+      </c>
+      <c r="C2883">
+        <v>1631269</v>
+      </c>
+      <c r="D2883">
+        <v>81953440</v>
+      </c>
+      <c r="E2883">
+        <v>231015</v>
+      </c>
+      <c r="G2883" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2883" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2883" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2884" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2884" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2884" t="s">
+        <v>2825</v>
+      </c>
+      <c r="C2884">
+        <v>1678019</v>
+      </c>
+      <c r="D2884">
+        <v>81953376</v>
+      </c>
+      <c r="E2884">
+        <v>231059</v>
+      </c>
+      <c r="G2884" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2884" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2884" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2885" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2885" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2885" t="s">
+        <v>2826</v>
+      </c>
+      <c r="C2885">
+        <v>1685339</v>
+      </c>
+      <c r="D2885">
+        <v>81953341</v>
+      </c>
+      <c r="E2885">
+        <v>231075</v>
+      </c>
+      <c r="G2885" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2885" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2885" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2886" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2886" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2886" t="s">
+        <v>2827</v>
+      </c>
+      <c r="C2886">
+        <v>1648206</v>
+      </c>
+      <c r="D2886">
+        <v>81953275</v>
+      </c>
+      <c r="E2886">
+        <v>231019</v>
+      </c>
+      <c r="G2886" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2886" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2886" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2887" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2887" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2887" t="s">
+        <v>2828</v>
+      </c>
+      <c r="C2887">
+        <v>1050641</v>
+      </c>
+      <c r="D2887">
+        <v>81953240</v>
+      </c>
+      <c r="E2887">
+        <v>231065</v>
+      </c>
+      <c r="G2887" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2887" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2887" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2888" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2888" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2888" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C2888">
+        <v>1050517</v>
+      </c>
+      <c r="D2888">
+        <v>81953217</v>
+      </c>
+      <c r="E2888">
+        <v>231060</v>
+      </c>
+      <c r="G2888" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2888" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2888" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2889" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2889" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2889" t="s">
+        <v>2830</v>
+      </c>
+      <c r="C2889">
+        <v>1050212</v>
+      </c>
+      <c r="D2889">
+        <v>81953172</v>
+      </c>
+      <c r="E2889">
+        <v>231037</v>
+      </c>
+      <c r="G2889" s="13">
+        <f t="shared" si="51"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2889" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2889" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2890" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2890" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2890" t="s">
+        <v>2831</v>
+      </c>
+      <c r="C2890">
+        <v>1050872</v>
+      </c>
+      <c r="D2890">
+        <v>81953131</v>
+      </c>
+      <c r="E2890">
+        <v>231076</v>
+      </c>
+      <c r="G2890" s="13">
+        <f t="shared" ref="G2890:G2953" si="52">IF(J2890&lt;&gt;"",J2890*$J$1,K2890)</f>
+        <v>1722000</v>
+      </c>
+      <c r="I2890" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2890" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2891" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2891" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2891" t="s">
+        <v>2832</v>
+      </c>
+      <c r="C2891">
+        <v>1050775</v>
+      </c>
+      <c r="D2891">
+        <v>81953100</v>
+      </c>
+      <c r="E2891">
+        <v>231073</v>
+      </c>
+      <c r="G2891" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2891" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2891" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2892" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2892" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2892" t="s">
+        <v>2833</v>
+      </c>
+      <c r="C2892">
+        <v>1050686</v>
+      </c>
+      <c r="D2892">
+        <v>81953056</v>
+      </c>
+      <c r="E2892">
+        <v>231067</v>
+      </c>
+      <c r="G2892" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2892" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2892" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2893" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2893" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2893" t="s">
+        <v>2834</v>
+      </c>
+      <c r="C2893">
+        <v>1050528</v>
+      </c>
+      <c r="D2893">
+        <v>81953029</v>
+      </c>
+      <c r="E2893">
+        <v>231061</v>
+      </c>
+      <c r="G2893" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2893" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2893" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2894" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2894" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2894" t="s">
+        <v>2835</v>
+      </c>
+      <c r="C2894">
+        <v>16001632</v>
+      </c>
+      <c r="D2894">
+        <v>81952993</v>
+      </c>
+      <c r="E2894">
+        <v>231103</v>
+      </c>
+      <c r="G2894" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2894" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2894" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2895" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2895" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2895" t="s">
+        <v>2836</v>
+      </c>
+      <c r="C2895">
+        <v>16001298</v>
+      </c>
+      <c r="D2895">
+        <v>81952962</v>
+      </c>
+      <c r="E2895">
+        <v>231080</v>
+      </c>
+      <c r="G2895" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2895" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2895" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2896" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2896" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2896" t="s">
+        <v>2837</v>
+      </c>
+      <c r="C2896">
+        <v>16001096</v>
+      </c>
+      <c r="D2896">
+        <v>81952938</v>
+      </c>
+      <c r="E2896">
+        <v>231102</v>
+      </c>
+      <c r="G2896" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2896" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2896" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2897" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2897" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2897" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C2897">
+        <v>1050922</v>
+      </c>
+      <c r="D2897">
+        <v>81952895</v>
+      </c>
+      <c r="E2897">
+        <v>231079</v>
+      </c>
+      <c r="G2897" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2897" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2897" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2898" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2898" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2898" t="s">
+        <v>2839</v>
+      </c>
+      <c r="C2898">
+        <v>1051665</v>
+      </c>
+      <c r="D2898">
+        <v>81952851</v>
+      </c>
+      <c r="E2898">
+        <v>231100</v>
+      </c>
+      <c r="G2898" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2898" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2898" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2899" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2899" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2899" t="s">
+        <v>2840</v>
+      </c>
+      <c r="C2899">
+        <v>1527023</v>
+      </c>
+      <c r="D2899">
+        <v>81952783</v>
+      </c>
+      <c r="E2899">
+        <v>221765</v>
+      </c>
+      <c r="G2899" s="13">
+        <f t="shared" si="52"/>
+        <v>3885000</v>
+      </c>
+      <c r="I2899" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2899" s="11">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="2900" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2900" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2900" t="s">
+        <v>2841</v>
+      </c>
+      <c r="C2900">
+        <v>1051363</v>
+      </c>
+      <c r="D2900">
+        <v>81952757</v>
+      </c>
+      <c r="E2900">
+        <v>231094</v>
+      </c>
+      <c r="G2900" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2900" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2900" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2901" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2901" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2901" t="s">
+        <v>2842</v>
+      </c>
+      <c r="C2901">
+        <v>10391962</v>
+      </c>
+      <c r="D2901">
+        <v>81952655</v>
+      </c>
+      <c r="E2901">
+        <v>221705</v>
+      </c>
+      <c r="G2901" s="13">
+        <f t="shared" si="52"/>
+        <v>2730000</v>
+      </c>
+      <c r="I2901" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2901" s="11">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="2902" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2902" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2902" t="s">
+        <v>2843</v>
+      </c>
+      <c r="C2902">
+        <v>1051110</v>
+      </c>
+      <c r="D2902">
+        <v>81952600</v>
+      </c>
+      <c r="E2902">
+        <v>231088</v>
+      </c>
+      <c r="G2902" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2902" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2902" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2903" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2903" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2903" t="s">
+        <v>2844</v>
+      </c>
+      <c r="C2903">
+        <v>2539659</v>
+      </c>
+      <c r="D2903">
+        <v>81952517</v>
+      </c>
+      <c r="E2903">
+        <v>221855</v>
+      </c>
+      <c r="G2903" s="13">
+        <f t="shared" si="52"/>
+        <v>2730000</v>
+      </c>
+      <c r="I2903" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2903" s="11">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="2904" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2904" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2904" t="s">
+        <v>2845</v>
+      </c>
+      <c r="C2904">
+        <v>22275906</v>
+      </c>
+      <c r="D2904">
+        <v>81952465</v>
+      </c>
+      <c r="E2904">
+        <v>221857</v>
+      </c>
+      <c r="G2904" s="13">
+        <f t="shared" si="52"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2904" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2904" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2905" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2905" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2905" t="s">
+        <v>2846</v>
+      </c>
+      <c r="C2905">
+        <v>22276430</v>
+      </c>
+      <c r="D2905">
+        <v>81952413</v>
+      </c>
+      <c r="E2905">
+        <v>221859</v>
+      </c>
+      <c r="G2905" s="13">
+        <f t="shared" si="52"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2905" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2905" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2906" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2906" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2906" t="s">
+        <v>2847</v>
+      </c>
+      <c r="C2906">
+        <v>22276302</v>
+      </c>
+      <c r="D2906">
+        <v>81952378</v>
+      </c>
+      <c r="E2906">
+        <v>221858</v>
+      </c>
+      <c r="G2906" s="13">
+        <f t="shared" si="52"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2906" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2906" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2907" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2907" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2907" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C2907">
+        <v>22265948</v>
+      </c>
+      <c r="D2907">
+        <v>81952365</v>
+      </c>
+      <c r="E2907">
+        <v>221856</v>
+      </c>
+      <c r="G2907" s="13">
+        <f t="shared" si="52"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2907" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2907" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2908" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2908" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2908" t="s">
+        <v>2849</v>
+      </c>
+      <c r="C2908">
+        <v>1050988</v>
+      </c>
+      <c r="D2908">
+        <v>81952340</v>
+      </c>
+      <c r="E2908">
+        <v>231081</v>
+      </c>
+      <c r="G2908" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2908" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2908" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2909" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2909" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2909" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C2909">
+        <v>1677988</v>
+      </c>
+      <c r="D2909">
+        <v>81952319</v>
+      </c>
+      <c r="E2909">
+        <v>231056</v>
+      </c>
+      <c r="G2909" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2909" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2909" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2910" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2910" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2910" t="s">
+        <v>2851</v>
+      </c>
+      <c r="C2910">
+        <v>1051647</v>
+      </c>
+      <c r="D2910">
+        <v>81952247</v>
+      </c>
+      <c r="E2910">
+        <v>231099</v>
+      </c>
+      <c r="G2910" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2910" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2910" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2911" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2911" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2911" t="s">
+        <v>2852</v>
+      </c>
+      <c r="C2911">
+        <v>1876128</v>
+      </c>
+      <c r="D2911">
+        <v>81952147</v>
+      </c>
+      <c r="E2911">
+        <v>231093</v>
+      </c>
+      <c r="G2911" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2911" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2911" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2912" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2912" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2912" t="s">
+        <v>2853</v>
+      </c>
+      <c r="C2912">
+        <v>2361704</v>
+      </c>
+      <c r="D2912">
+        <v>81952067</v>
+      </c>
+      <c r="E2912">
+        <v>231071</v>
+      </c>
+      <c r="G2912" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2912" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2912" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2913" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2913" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2913" t="s">
+        <v>2854</v>
+      </c>
+      <c r="C2913">
+        <v>1652658</v>
+      </c>
+      <c r="D2913">
+        <v>81951992</v>
+      </c>
+      <c r="E2913">
+        <v>231030</v>
+      </c>
+      <c r="G2913" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2913" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2913" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2914" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2914" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2914" t="s">
+        <v>2855</v>
+      </c>
+      <c r="C2914">
+        <v>1648262</v>
+      </c>
+      <c r="D2914">
+        <v>81951917</v>
+      </c>
+      <c r="E2914">
+        <v>231023</v>
+      </c>
+      <c r="G2914" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2914" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2914" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2915" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2915" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2915" t="s">
+        <v>2856</v>
+      </c>
+      <c r="C2915">
+        <v>1623919</v>
+      </c>
+      <c r="D2915">
+        <v>81951885</v>
+      </c>
+      <c r="E2915">
+        <v>231004</v>
+      </c>
+      <c r="G2915" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2915" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2915" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2916" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2916" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2916" t="s">
+        <v>2857</v>
+      </c>
+      <c r="C2916">
+        <v>958520</v>
+      </c>
+      <c r="D2916">
+        <v>81951833</v>
+      </c>
+      <c r="E2916">
+        <v>231048</v>
+      </c>
+      <c r="G2916" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2916" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2916" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2917" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2917" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2917" t="s">
+        <v>2858</v>
+      </c>
+      <c r="C2917">
+        <v>1051633</v>
+      </c>
+      <c r="D2917">
+        <v>81951794</v>
+      </c>
+      <c r="E2917">
+        <v>231097</v>
+      </c>
+      <c r="G2917" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2917" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2917" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2918" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2918" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2918" t="s">
+        <v>2859</v>
+      </c>
+      <c r="C2918">
+        <v>1685310</v>
+      </c>
+      <c r="D2918">
+        <v>81951751</v>
+      </c>
+      <c r="E2918">
+        <v>231073</v>
+      </c>
+      <c r="G2918" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2918" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2918" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2919" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2919" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2919" t="s">
+        <v>2860</v>
+      </c>
+      <c r="C2919">
+        <v>1664978</v>
+      </c>
+      <c r="D2919">
+        <v>81951710</v>
+      </c>
+      <c r="E2919">
+        <v>231039</v>
+      </c>
+      <c r="G2919" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2919" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2919" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2920" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2920" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2920" t="s">
+        <v>2861</v>
+      </c>
+      <c r="C2920">
+        <v>4454428</v>
+      </c>
+      <c r="D2920">
+        <v>81951671</v>
+      </c>
+      <c r="E2920">
+        <v>231077</v>
+      </c>
+      <c r="G2920" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2920" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2920" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2921" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2921" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2921" t="s">
+        <v>2862</v>
+      </c>
+      <c r="C2921">
+        <v>1677934</v>
+      </c>
+      <c r="D2921">
+        <v>81951624</v>
+      </c>
+      <c r="E2921">
+        <v>231045</v>
+      </c>
+      <c r="G2921" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2921" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2921" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2922" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2922" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2922" t="s">
+        <v>2863</v>
+      </c>
+      <c r="C2922">
+        <v>1624828</v>
+      </c>
+      <c r="D2922">
+        <v>81951570</v>
+      </c>
+      <c r="E2922">
+        <v>231010</v>
+      </c>
+      <c r="G2922" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2922" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2922" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2923" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2923" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2923" t="s">
+        <v>2864</v>
+      </c>
+      <c r="C2923">
+        <v>22264991</v>
+      </c>
+      <c r="D2923">
+        <v>81951521</v>
+      </c>
+      <c r="E2923">
+        <v>221860</v>
+      </c>
+      <c r="G2923" s="13">
+        <f t="shared" si="52"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2923" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2923" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2924" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2924" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2924" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C2924">
+        <v>22265685</v>
+      </c>
+      <c r="D2924">
+        <v>81951484</v>
+      </c>
+      <c r="E2924">
+        <v>221850</v>
+      </c>
+      <c r="G2924" s="13">
+        <f t="shared" si="52"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2924" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2924" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2925" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2925" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2925" t="s">
+        <v>2865</v>
+      </c>
+      <c r="C2925">
+        <v>1624182</v>
+      </c>
+      <c r="D2925">
+        <v>81951445</v>
+      </c>
+      <c r="E2925">
+        <v>231006</v>
+      </c>
+      <c r="G2925" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2925" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2925" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2926" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2926" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2926" t="s">
+        <v>2866</v>
+      </c>
+      <c r="C2926">
+        <v>1050186</v>
+      </c>
+      <c r="D2926">
+        <v>81951350</v>
+      </c>
+      <c r="E2926">
+        <v>231035</v>
+      </c>
+      <c r="G2926" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2926" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2926" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2927" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2927" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2927" t="s">
+        <v>2867</v>
+      </c>
+      <c r="C2927">
+        <v>1051134</v>
+      </c>
+      <c r="D2927">
+        <v>81951263</v>
+      </c>
+      <c r="E2927">
+        <v>231089</v>
+      </c>
+      <c r="G2927" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2927" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2927" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2928" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2928" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2928" t="s">
+        <v>2868</v>
+      </c>
+      <c r="C2928">
+        <v>21847173</v>
+      </c>
+      <c r="D2928">
+        <v>81950832</v>
+      </c>
+      <c r="E2928">
+        <v>221861</v>
+      </c>
+      <c r="G2928" s="13">
+        <f t="shared" si="52"/>
+        <v>2478000</v>
+      </c>
+      <c r="I2928" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2928" s="11">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="2929" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2929" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2929" t="s">
+        <v>2869</v>
+      </c>
+      <c r="C2929">
+        <v>6483595</v>
+      </c>
+      <c r="D2929">
+        <v>81950488</v>
+      </c>
+      <c r="E2929">
+        <v>221862</v>
+      </c>
+      <c r="G2929" s="13">
+        <f t="shared" si="52"/>
+        <v>3171000</v>
+      </c>
+      <c r="I2929" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2929" s="11">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="2930" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2930" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2930" t="s">
+        <v>2870</v>
+      </c>
+      <c r="C2930">
+        <v>1050442</v>
+      </c>
+      <c r="D2930">
+        <v>81950390</v>
+      </c>
+      <c r="E2930">
+        <v>231053</v>
+      </c>
+      <c r="G2930" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2930" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2930" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2931" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2931" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2931" t="s">
+        <v>2871</v>
+      </c>
+      <c r="C2931">
+        <v>1049416</v>
+      </c>
+      <c r="D2931">
+        <v>81950357</v>
+      </c>
+      <c r="E2931">
+        <v>231026</v>
+      </c>
+      <c r="G2931" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2931" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2931" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2932" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2932" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2932" t="s">
+        <v>2872</v>
+      </c>
+      <c r="C2932">
+        <v>1050482</v>
+      </c>
+      <c r="D2932">
+        <v>81950315</v>
+      </c>
+      <c r="E2932">
+        <v>231056</v>
+      </c>
+      <c r="G2932" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2932" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2932" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2933" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2933" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2933" t="s">
+        <v>2873</v>
+      </c>
+      <c r="C2933">
+        <v>9400631</v>
+      </c>
+      <c r="D2933">
+        <v>81950279</v>
+      </c>
+      <c r="E2933">
+        <v>221863</v>
+      </c>
+      <c r="G2933" s="13">
+        <f t="shared" si="52"/>
+        <v>6006000</v>
+      </c>
+      <c r="I2933" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2933" s="11">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="2934" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2934" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2934" t="s">
+        <v>2874</v>
+      </c>
+      <c r="C2934">
+        <v>1049308</v>
+      </c>
+      <c r="D2934">
+        <v>81950225</v>
+      </c>
+      <c r="E2934">
+        <v>231016</v>
+      </c>
+      <c r="G2934" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2934" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2934" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2935" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2935" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2935" t="s">
+        <v>2875</v>
+      </c>
+      <c r="C2935">
+        <v>1631292</v>
+      </c>
+      <c r="D2935">
+        <v>81948788</v>
+      </c>
+      <c r="E2935">
+        <v>231016</v>
+      </c>
+      <c r="G2935" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2935" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2935" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2936" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2936" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2936" t="s">
+        <v>2876</v>
+      </c>
+      <c r="C2936">
+        <v>1050491</v>
+      </c>
+      <c r="D2936">
+        <v>81948746</v>
+      </c>
+      <c r="E2936">
+        <v>231057</v>
+      </c>
+      <c r="G2936" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2936" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2936" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2937" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2937" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2937" t="s">
+        <v>2877</v>
+      </c>
+      <c r="C2937">
+        <v>1050358</v>
+      </c>
+      <c r="D2937">
+        <v>81948716</v>
+      </c>
+      <c r="E2937">
+        <v>231046</v>
+      </c>
+      <c r="G2937" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2937" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2937" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2938" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2938" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2938" t="s">
+        <v>2878</v>
+      </c>
+      <c r="C2938">
+        <v>1681395</v>
+      </c>
+      <c r="D2938">
+        <v>81948676</v>
+      </c>
+      <c r="E2938">
+        <v>231063</v>
+      </c>
+      <c r="G2938" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2938" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2938" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2939" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2939" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2939" t="s">
+        <v>2879</v>
+      </c>
+      <c r="C2939">
+        <v>22277588</v>
+      </c>
+      <c r="D2939">
+        <v>81948634</v>
+      </c>
+      <c r="E2939">
+        <v>221868</v>
+      </c>
+      <c r="G2939" s="13">
+        <f t="shared" si="52"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2939" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2939" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2940" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2940" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2940" t="s">
+        <v>2880</v>
+      </c>
+      <c r="C2940">
+        <v>22276872</v>
+      </c>
+      <c r="D2940">
+        <v>81948608</v>
+      </c>
+      <c r="E2940">
+        <v>221866</v>
+      </c>
+      <c r="G2940" s="13">
+        <f t="shared" si="52"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2940" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2940" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2941" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2941" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2941" t="s">
+        <v>2881</v>
+      </c>
+      <c r="C2941">
+        <v>22277468</v>
+      </c>
+      <c r="D2941">
+        <v>81948575</v>
+      </c>
+      <c r="E2941">
+        <v>221867</v>
+      </c>
+      <c r="G2941" s="13">
+        <f t="shared" si="52"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2941" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2941" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2942" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2942" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2942" t="s">
+        <v>2882</v>
+      </c>
+      <c r="C2942">
+        <v>22266286</v>
+      </c>
+      <c r="D2942">
+        <v>81948555</v>
+      </c>
+      <c r="E2942">
+        <v>221864</v>
+      </c>
+      <c r="G2942" s="13">
+        <f t="shared" si="52"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2942" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2942" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2943" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2943" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2943" t="s">
+        <v>2883</v>
+      </c>
+      <c r="C2943">
+        <v>22266575</v>
+      </c>
+      <c r="D2943">
+        <v>81948527</v>
+      </c>
+      <c r="E2943">
+        <v>221865</v>
+      </c>
+      <c r="G2943" s="13">
+        <f t="shared" si="52"/>
+        <v>4431000</v>
+      </c>
+      <c r="I2943" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2943" s="11">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2944" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2944" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2944" t="s">
+        <v>2884</v>
+      </c>
+      <c r="C2944">
+        <v>1624930</v>
+      </c>
+      <c r="D2944">
+        <v>81948371</v>
+      </c>
+      <c r="E2944">
+        <v>231013</v>
+      </c>
+      <c r="G2944" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2944" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2944" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2945" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2945" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2945" t="s">
+        <v>2885</v>
+      </c>
+      <c r="C2945">
+        <v>1685370</v>
+      </c>
+      <c r="D2945">
+        <v>81948302</v>
+      </c>
+      <c r="E2945">
+        <v>231079</v>
+      </c>
+      <c r="G2945" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2945" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2945" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2946" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2946" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2946" t="s">
+        <v>2886</v>
+      </c>
+      <c r="C2946">
+        <v>1051202</v>
+      </c>
+      <c r="D2946">
+        <v>81948274</v>
+      </c>
+      <c r="E2946">
+        <v>231091</v>
+      </c>
+      <c r="G2946" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2946" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2946" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2947" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2947" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2947" t="s">
+        <v>2887</v>
+      </c>
+      <c r="C2947">
+        <v>1051052</v>
+      </c>
+      <c r="D2947">
+        <v>81948244</v>
+      </c>
+      <c r="E2947">
+        <v>231085</v>
+      </c>
+      <c r="G2947" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2947" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2947" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2948" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2948" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2948" t="s">
+        <v>2888</v>
+      </c>
+      <c r="C2948">
+        <v>1664756</v>
+      </c>
+      <c r="D2948">
+        <v>81948203</v>
+      </c>
+      <c r="E2948">
+        <v>231033</v>
+      </c>
+      <c r="G2948" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2948" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2948" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2949" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2949" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2949" t="s">
+        <v>2889</v>
+      </c>
+      <c r="C2949">
+        <v>1664711</v>
+      </c>
+      <c r="D2949">
+        <v>81948153</v>
+      </c>
+      <c r="E2949">
+        <v>231032</v>
+      </c>
+      <c r="G2949" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2949" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2949" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2950" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2950" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2950" t="s">
+        <v>2890</v>
+      </c>
+      <c r="C2950">
+        <v>1664654</v>
+      </c>
+      <c r="D2950">
+        <v>81948116</v>
+      </c>
+      <c r="E2950">
+        <v>231038</v>
+      </c>
+      <c r="G2950" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2950" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2950" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2951" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2951" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2951" t="s">
+        <v>2891</v>
+      </c>
+      <c r="C2951">
+        <v>1664894</v>
+      </c>
+      <c r="D2951">
+        <v>81948068</v>
+      </c>
+      <c r="E2951">
+        <v>231024</v>
+      </c>
+      <c r="G2951" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2951" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2951" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2952" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2952" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2952" t="s">
+        <v>2892</v>
+      </c>
+      <c r="C2952">
+        <v>1648611</v>
+      </c>
+      <c r="D2952">
+        <v>81948006</v>
+      </c>
+      <c r="E2952">
+        <v>231029</v>
+      </c>
+      <c r="G2952" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2952" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2952" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2953" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2953" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2953" t="s">
+        <v>2893</v>
+      </c>
+      <c r="C2953">
+        <v>1648296</v>
+      </c>
+      <c r="D2953">
+        <v>81947968</v>
+      </c>
+      <c r="E2953">
+        <v>231027</v>
+      </c>
+      <c r="G2953" s="13">
+        <f t="shared" si="52"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2953" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2953" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2954" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2954" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2954" t="s">
+        <v>2894</v>
+      </c>
+      <c r="C2954">
+        <v>1648043</v>
+      </c>
+      <c r="D2954">
+        <v>81947941</v>
+      </c>
+      <c r="E2954">
+        <v>231018</v>
+      </c>
+      <c r="G2954" s="13">
+        <f t="shared" ref="G2954:G2984" si="53">IF(J2954&lt;&gt;"",J2954*$J$1,K2954)</f>
+        <v>1722000</v>
+      </c>
+      <c r="I2954" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2954" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2955" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2955" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2955" t="s">
+        <v>2895</v>
+      </c>
+      <c r="C2955">
+        <v>1049291</v>
+      </c>
+      <c r="D2955">
+        <v>81947898</v>
+      </c>
+      <c r="E2955">
+        <v>231011</v>
+      </c>
+      <c r="G2955" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2955" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2955" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2956" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2956" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2956" t="s">
+        <v>2896</v>
+      </c>
+      <c r="C2956">
+        <v>1049389</v>
+      </c>
+      <c r="D2956">
+        <v>81947867</v>
+      </c>
+      <c r="E2956">
+        <v>231022</v>
+      </c>
+      <c r="G2956" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2956" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2956" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2957" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2957" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2957" t="s">
+        <v>2897</v>
+      </c>
+      <c r="C2957">
+        <v>958651</v>
+      </c>
+      <c r="D2957">
+        <v>81947803</v>
+      </c>
+      <c r="E2957">
+        <v>231072</v>
+      </c>
+      <c r="G2957" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2957" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2957" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2958" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2958" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2958" t="s">
+        <v>2898</v>
+      </c>
+      <c r="C2958">
+        <v>1050275</v>
+      </c>
+      <c r="D2958">
+        <v>81947766</v>
+      </c>
+      <c r="E2958">
+        <v>231041</v>
+      </c>
+      <c r="G2958" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2958" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2958" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2959" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2959" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2959" t="s">
+        <v>2899</v>
+      </c>
+      <c r="C2959">
+        <v>1050409</v>
+      </c>
+      <c r="D2959">
+        <v>81947719</v>
+      </c>
+      <c r="E2959">
+        <v>231050</v>
+      </c>
+      <c r="G2959" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2959" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2959" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2960" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2960" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2960" t="s">
+        <v>2900</v>
+      </c>
+      <c r="C2960">
+        <v>1050346</v>
+      </c>
+      <c r="D2960">
+        <v>81947681</v>
+      </c>
+      <c r="E2960">
+        <v>231045</v>
+      </c>
+      <c r="G2960" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2960" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2960" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2961" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2961" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2961" t="s">
+        <v>2901</v>
+      </c>
+      <c r="C2961">
+        <v>6293225</v>
+      </c>
+      <c r="D2961">
+        <v>81947637</v>
+      </c>
+      <c r="E2961">
+        <v>231017</v>
+      </c>
+      <c r="G2961" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2961" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2961" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2962" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2962" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2962" t="s">
+        <v>2902</v>
+      </c>
+      <c r="C2962">
+        <v>1687711</v>
+      </c>
+      <c r="D2962">
+        <v>81947559</v>
+      </c>
+      <c r="E2962">
+        <v>231092</v>
+      </c>
+      <c r="G2962" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2962" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2962" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2963" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2963" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2963" t="s">
+        <v>2903</v>
+      </c>
+      <c r="C2963">
+        <v>16731123</v>
+      </c>
+      <c r="D2963">
+        <v>81947473</v>
+      </c>
+      <c r="E2963">
+        <v>231049</v>
+      </c>
+      <c r="G2963" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2963" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2963" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2964" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2964" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2964" t="s">
+        <v>2904</v>
+      </c>
+      <c r="C2964">
+        <v>1049265</v>
+      </c>
+      <c r="D2964">
+        <v>81947433</v>
+      </c>
+      <c r="E2964">
+        <v>231005</v>
+      </c>
+      <c r="G2964" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2964" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2964" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2965" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2965" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2965" t="s">
+        <v>2905</v>
+      </c>
+      <c r="C2965">
+        <v>1050335</v>
+      </c>
+      <c r="D2965">
+        <v>81947385</v>
+      </c>
+      <c r="E2965">
+        <v>231044</v>
+      </c>
+      <c r="G2965" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2965" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2965" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2966" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2966" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2966" t="s">
+        <v>2906</v>
+      </c>
+      <c r="C2966">
+        <v>1049252</v>
+      </c>
+      <c r="D2966">
+        <v>81947361</v>
+      </c>
+      <c r="E2966">
+        <v>231003</v>
+      </c>
+      <c r="G2966" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2966" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2966" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2967" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2967" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2967" t="s">
+        <v>2907</v>
+      </c>
+      <c r="C2967">
+        <v>1664856</v>
+      </c>
+      <c r="D2967">
+        <v>81947315</v>
+      </c>
+      <c r="E2967">
+        <v>231041</v>
+      </c>
+      <c r="G2967" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2967" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2967" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2968" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2968" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2968" t="s">
+        <v>2908</v>
+      </c>
+      <c r="C2968">
+        <v>1049412</v>
+      </c>
+      <c r="D2968">
+        <v>81947263</v>
+      </c>
+      <c r="E2968">
+        <v>231025</v>
+      </c>
+      <c r="G2968" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2968" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2968" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2969" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2969" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2969" t="s">
+        <v>2909</v>
+      </c>
+      <c r="C2969">
+        <v>1049299</v>
+      </c>
+      <c r="D2969">
+        <v>81947200</v>
+      </c>
+      <c r="E2969">
+        <v>231012</v>
+      </c>
+      <c r="G2969" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2969" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2969" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2970" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2970" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2970" t="s">
+        <v>2910</v>
+      </c>
+      <c r="C2970">
+        <v>1050735</v>
+      </c>
+      <c r="D2970">
+        <v>81947150</v>
+      </c>
+      <c r="E2970">
+        <v>231069</v>
+      </c>
+      <c r="G2970" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2970" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2970" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2971" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2971" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2971" t="s">
+        <v>2911</v>
+      </c>
+      <c r="C2971">
+        <v>1685399</v>
+      </c>
+      <c r="D2971">
+        <v>81947109</v>
+      </c>
+      <c r="E2971">
+        <v>231083</v>
+      </c>
+      <c r="G2971" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2971" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2971" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2972" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2972" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2972" t="s">
+        <v>2912</v>
+      </c>
+      <c r="C2972">
+        <v>1050660</v>
+      </c>
+      <c r="D2972">
+        <v>81947037</v>
+      </c>
+      <c r="E2972">
+        <v>231066</v>
+      </c>
+      <c r="G2972" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2972" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2972" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2973" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2973" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2973" t="s">
+        <v>2913</v>
+      </c>
+      <c r="C2973">
+        <v>21847640</v>
+      </c>
+      <c r="D2973">
+        <v>81946928</v>
+      </c>
+      <c r="E2973">
+        <v>221869</v>
+      </c>
+      <c r="G2973" s="13">
+        <f t="shared" si="53"/>
+        <v>8169000</v>
+      </c>
+      <c r="I2973" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2973" s="11">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="2974" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2974" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2974" t="s">
+        <v>2914</v>
+      </c>
+      <c r="C2974">
+        <v>958657</v>
+      </c>
+      <c r="D2974">
+        <v>81946875</v>
+      </c>
+      <c r="E2974">
+        <v>231020</v>
+      </c>
+      <c r="G2974" s="13">
+        <f t="shared" si="53"/>
+        <v>1722000</v>
+      </c>
+      <c r="I2974" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2974" s="11">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2975" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2975" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2975" t="s">
+        <v>2915</v>
+      </c>
+      <c r="C2975">
+        <v>21847676</v>
+      </c>
+      <c r="D2975">
+        <v>81946776</v>
+      </c>
+      <c r="E2975">
+        <v>221870</v>
+      </c>
+      <c r="G2975" s="13">
+        <f t="shared" si="53"/>
+        <v>8169000</v>
+      </c>
+      <c r="I2975" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2975" s="11">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="2976" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2976" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2976" t="s">
+        <v>2915</v>
+      </c>
+      <c r="C2976">
+        <v>21847707</v>
+      </c>
+      <c r="D2976">
+        <v>81946690</v>
+      </c>
+      <c r="E2976">
+        <v>221871</v>
+      </c>
+      <c r="G2976" s="13">
+        <f t="shared" si="53"/>
+        <v>8169000</v>
+      </c>
+      <c r="I2976" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2976" s="11">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="2977" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2977" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2977" t="s">
+        <v>2916</v>
+      </c>
+      <c r="C2977">
+        <v>21847663</v>
+      </c>
+      <c r="D2977">
+        <v>81946635</v>
+      </c>
+      <c r="E2977">
+        <v>221872</v>
+      </c>
+      <c r="G2977" s="13">
+        <f t="shared" si="53"/>
+        <v>8169000</v>
+      </c>
+      <c r="I2977" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2977" s="11">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="2978" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2978" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2978" t="s">
+        <v>2917</v>
+      </c>
+      <c r="C2978">
+        <v>21847784</v>
+      </c>
+      <c r="D2978">
+        <v>81946535</v>
+      </c>
+      <c r="E2978">
+        <v>221873</v>
+      </c>
+      <c r="G2978" s="13">
+        <f t="shared" si="53"/>
+        <v>8169000</v>
+      </c>
+      <c r="I2978" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2978" s="11">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="2979" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2979" t="s">
+        <v>236</v>
+      </c>
+      <c r="B2979" t="s">
+        <v>2918</v>
+      </c>
+      <c r="C2979">
+        <v>16008051</v>
+      </c>
+      <c r="D2979">
+        <v>81946373</v>
+      </c>
+      <c r="E2979">
+        <v>220032</v>
+      </c>
+      <c r="G2979" s="13">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="I2979" s="4" t="s">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="2980" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2980" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2980" t="s">
+        <v>2919</v>
+      </c>
+      <c r="C2980">
+        <v>21200394</v>
+      </c>
+      <c r="D2980">
+        <v>81587375</v>
+      </c>
+      <c r="E2980">
+        <v>221874</v>
+      </c>
+      <c r="G2980" s="13">
+        <f t="shared" si="53"/>
+        <v>7665000</v>
+      </c>
+      <c r="I2980" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2980" s="11">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="2981" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2981" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2981" t="s">
+        <v>2920</v>
+      </c>
+      <c r="C2981">
+        <v>21200412</v>
+      </c>
+      <c r="D2981">
+        <v>81587308</v>
+      </c>
+      <c r="E2981">
+        <v>221875</v>
+      </c>
+      <c r="G2981" s="13">
+        <f t="shared" si="53"/>
+        <v>7665000</v>
+      </c>
+      <c r="I2981" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2981" s="11">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="2982" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2982" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2982" t="s">
+        <v>2921</v>
+      </c>
+      <c r="C2982">
+        <v>21200425</v>
+      </c>
+      <c r="D2982">
+        <v>81587246</v>
+      </c>
+      <c r="E2982">
+        <v>221876</v>
+      </c>
+      <c r="G2982" s="13">
+        <f t="shared" si="53"/>
+        <v>7665000</v>
+      </c>
+      <c r="I2982" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2982" s="11">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="2983" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2983" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2983" t="s">
+        <v>2922</v>
+      </c>
+      <c r="C2983">
+        <v>21847589</v>
+      </c>
+      <c r="D2983">
+        <v>81587078</v>
+      </c>
+      <c r="E2983">
+        <v>221877</v>
+      </c>
+      <c r="G2983" s="13">
+        <f t="shared" si="53"/>
+        <v>4368000</v>
+      </c>
+      <c r="I2983" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2983" s="11">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="2984" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2984" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2984" t="s">
+        <v>2923</v>
+      </c>
+      <c r="C2984">
+        <v>21847610</v>
+      </c>
+      <c r="D2984">
+        <v>81586973</v>
+      </c>
+      <c r="E2984">
+        <v>221878</v>
+      </c>
+      <c r="G2984" s="13">
+        <f t="shared" si="53"/>
+        <v>4368000</v>
+      </c>
+      <c r="I2984" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J2984" s="11">
+        <v>2.08</v>
       </c>
     </row>
   </sheetData>
@@ -84779,743 +91022,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="D5:W71"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="28.85546875" customWidth="1"/>
-    <col min="6" max="6" width="43.140625" customWidth="1"/>
-    <col min="23" max="23" width="13.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="5" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="T5" s="8"/>
-    </row>
-    <row r="6" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="T6" s="8"/>
-    </row>
-    <row r="7" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="V7" s="8"/>
-    </row>
-    <row r="8" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="V8" s="8"/>
-    </row>
-    <row r="9" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="V9" s="8"/>
-    </row>
-    <row r="10" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="V10" s="8"/>
-    </row>
-    <row r="11" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="V11" s="8"/>
-    </row>
-    <row r="12" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="V12" s="8"/>
-    </row>
-    <row r="13" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="V13" s="8"/>
-    </row>
-    <row r="14" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="V14" s="8"/>
-    </row>
-    <row r="15" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="T15" s="8"/>
-    </row>
-    <row r="16" spans="9:22" x14ac:dyDescent="0.25">
-      <c r="I16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="T16" s="8"/>
-    </row>
-    <row r="17" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="T17" s="8"/>
-    </row>
-    <row r="18" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="T18" s="8"/>
-    </row>
-    <row r="19" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="T19" s="8"/>
-    </row>
-    <row r="20" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="T20" s="8"/>
-    </row>
-    <row r="21" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
-        <v>2720</v>
-      </c>
-      <c r="G21">
-        <v>21988426</v>
-      </c>
-      <c r="H21">
-        <v>80628922</v>
-      </c>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8">
-        <v>1</v>
-      </c>
-      <c r="K21" t="s">
-        <v>2643</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>2643</v>
-      </c>
-      <c r="M21" s="8">
-        <v>1</v>
-      </c>
-      <c r="N21" t="s">
-        <v>2702</v>
-      </c>
-      <c r="O21" s="8">
-        <v>0</v>
-      </c>
-      <c r="P21" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>0</v>
-      </c>
-      <c r="R21" t="s">
-        <v>2702</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21" s="8" t="s">
-        <v>2689</v>
-      </c>
-      <c r="U21" s="8">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21" t="s">
-        <v>2690</v>
-      </c>
-    </row>
-    <row r="22" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="T22" s="8"/>
-    </row>
-    <row r="23" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
-      <c r="T23" s="8"/>
-    </row>
-    <row r="24" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-    </row>
-    <row r="25" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-    </row>
-    <row r="26" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-    </row>
-    <row r="27" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-    </row>
-    <row r="28" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="8"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
-    </row>
-    <row r="29" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="8"/>
-    </row>
-    <row r="30" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="8"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="8"/>
-    </row>
-    <row r="31" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="8"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="8"/>
-    </row>
-    <row r="32" spans="4:23" x14ac:dyDescent="0.25">
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-      <c r="P32" s="8"/>
-      <c r="Q32" s="8"/>
-      <c r="T32" s="8"/>
-      <c r="U32" s="8"/>
-    </row>
-    <row r="33" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="8"/>
-      <c r="T33" s="8"/>
-      <c r="U33" s="8"/>
-    </row>
-    <row r="34" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="8"/>
-      <c r="T34" s="8"/>
-      <c r="U34" s="8"/>
-    </row>
-    <row r="35" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8"/>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="8"/>
-      <c r="T35" s="8"/>
-      <c r="U35" s="8"/>
-    </row>
-    <row r="36" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="8"/>
-      <c r="P36" s="8"/>
-      <c r="Q36" s="8"/>
-      <c r="T36" s="8"/>
-      <c r="U36" s="8"/>
-    </row>
-    <row r="37" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-      <c r="P37" s="8"/>
-      <c r="Q37" s="8"/>
-      <c r="T37" s="8"/>
-      <c r="U37" s="8"/>
-    </row>
-    <row r="38" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="8"/>
-      <c r="P38" s="8"/>
-      <c r="Q38" s="8"/>
-      <c r="T38" s="8"/>
-      <c r="U38" s="8"/>
-    </row>
-    <row r="39" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="8"/>
-      <c r="P39" s="8"/>
-      <c r="Q39" s="8"/>
-      <c r="T39" s="8"/>
-      <c r="U39" s="8"/>
-    </row>
-    <row r="40" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I40" s="8"/>
-      <c r="J40" s="8"/>
-      <c r="L40" s="8"/>
-      <c r="M40" s="8"/>
-      <c r="N40" s="8"/>
-      <c r="O40" s="8"/>
-      <c r="P40" s="8"/>
-      <c r="Q40" s="8"/>
-      <c r="T40" s="8"/>
-      <c r="U40" s="8"/>
-    </row>
-    <row r="41" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8"/>
-      <c r="O41" s="8"/>
-      <c r="P41" s="8"/>
-      <c r="Q41" s="8"/>
-      <c r="T41" s="8"/>
-      <c r="U41" s="8"/>
-    </row>
-    <row r="42" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
-      <c r="O42" s="8"/>
-      <c r="P42" s="8"/>
-      <c r="Q42" s="8"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="8"/>
-    </row>
-    <row r="43" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="8"/>
-      <c r="N43" s="8"/>
-      <c r="O43" s="8"/>
-      <c r="P43" s="8"/>
-      <c r="Q43" s="8"/>
-      <c r="T43" s="8"/>
-      <c r="U43" s="8"/>
-    </row>
-    <row r="44" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="L44" s="8"/>
-      <c r="M44" s="8"/>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
-      <c r="P44" s="8"/>
-      <c r="Q44" s="8"/>
-      <c r="T44" s="8"/>
-      <c r="U44" s="8"/>
-    </row>
-    <row r="45" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8"/>
-      <c r="O45" s="8"/>
-      <c r="P45" s="8"/>
-      <c r="Q45" s="8"/>
-      <c r="T45" s="8"/>
-      <c r="U45" s="8"/>
-    </row>
-    <row r="46" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="L46" s="8"/>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8"/>
-      <c r="O46" s="8"/>
-      <c r="P46" s="8"/>
-      <c r="Q46" s="8"/>
-      <c r="T46" s="8"/>
-      <c r="U46" s="8"/>
-    </row>
-    <row r="47" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8"/>
-      <c r="N47" s="8"/>
-      <c r="O47" s="8"/>
-      <c r="P47" s="8"/>
-      <c r="Q47" s="8"/>
-      <c r="T47" s="8"/>
-      <c r="U47" s="8"/>
-    </row>
-    <row r="48" spans="9:21" x14ac:dyDescent="0.25">
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="8"/>
-      <c r="N48" s="8"/>
-      <c r="O48" s="8"/>
-      <c r="P48" s="8"/>
-      <c r="T48" s="8"/>
-      <c r="U48" s="8"/>
-    </row>
-    <row r="49" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="N49" s="8"/>
-      <c r="O49" s="8"/>
-      <c r="P49" s="8"/>
-      <c r="T49" s="8"/>
-    </row>
-    <row r="50" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I50" s="8"/>
-      <c r="J50" s="8"/>
-      <c r="L50" s="8"/>
-      <c r="N50" s="8"/>
-      <c r="O50" s="8"/>
-      <c r="P50" s="8"/>
-      <c r="T50" s="8"/>
-    </row>
-    <row r="51" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="N51" s="8"/>
-      <c r="O51" s="8"/>
-      <c r="P51" s="8"/>
-      <c r="T51" s="8"/>
-    </row>
-    <row r="52" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I52" s="8"/>
-      <c r="J52" s="8"/>
-      <c r="L52" s="8"/>
-      <c r="N52" s="8"/>
-      <c r="O52" s="8"/>
-      <c r="P52" s="8"/>
-      <c r="T52" s="8"/>
-    </row>
-    <row r="53" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="L53" s="8"/>
-      <c r="N53" s="8"/>
-      <c r="O53" s="8"/>
-      <c r="P53" s="8"/>
-      <c r="T53" s="8"/>
-    </row>
-    <row r="54" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="L54" s="8"/>
-      <c r="N54" s="8"/>
-      <c r="O54" s="8"/>
-      <c r="P54" s="8"/>
-      <c r="T54" s="8"/>
-    </row>
-    <row r="55" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="L55" s="8"/>
-      <c r="N55" s="8"/>
-      <c r="O55" s="8"/>
-      <c r="P55" s="8"/>
-      <c r="T55" s="8"/>
-    </row>
-    <row r="56" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I56" s="8"/>
-      <c r="J56" s="8"/>
-      <c r="L56" s="8"/>
-      <c r="N56" s="8"/>
-      <c r="O56" s="8"/>
-      <c r="P56" s="8"/>
-      <c r="T56" s="8"/>
-    </row>
-    <row r="57" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="N57" s="8"/>
-      <c r="O57" s="8"/>
-      <c r="P57" s="8"/>
-      <c r="T57" s="8"/>
-    </row>
-    <row r="58" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="L58" s="8"/>
-      <c r="N58" s="8"/>
-      <c r="O58" s="8"/>
-      <c r="P58" s="8"/>
-      <c r="T58" s="8"/>
-    </row>
-    <row r="59" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I59" s="8"/>
-      <c r="J59" s="8"/>
-      <c r="L59" s="8"/>
-      <c r="N59" s="8"/>
-      <c r="O59" s="8"/>
-      <c r="P59" s="8"/>
-      <c r="T59" s="8"/>
-    </row>
-    <row r="60" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I60" s="8"/>
-      <c r="J60" s="8"/>
-      <c r="L60" s="8"/>
-      <c r="N60" s="8"/>
-      <c r="O60" s="8"/>
-      <c r="P60" s="8"/>
-      <c r="T60" s="8"/>
-    </row>
-    <row r="61" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
-      <c r="L61" s="8"/>
-      <c r="N61" s="8"/>
-      <c r="O61" s="8"/>
-      <c r="P61" s="8"/>
-      <c r="T61" s="8"/>
-    </row>
-    <row r="62" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="N62" s="8"/>
-      <c r="O62" s="8"/>
-      <c r="P62" s="8"/>
-      <c r="T62" s="8"/>
-    </row>
-    <row r="63" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I63" s="8"/>
-      <c r="J63" s="8"/>
-      <c r="L63" s="8"/>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
-      <c r="P63" s="8"/>
-      <c r="T63" s="8"/>
-    </row>
-    <row r="64" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="N64" s="8"/>
-      <c r="O64" s="8"/>
-      <c r="P64" s="8"/>
-      <c r="T64" s="8"/>
-    </row>
-    <row r="65" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-      <c r="L65" s="8"/>
-      <c r="N65" s="8"/>
-      <c r="O65" s="8"/>
-      <c r="P65" s="8"/>
-      <c r="T65" s="8"/>
-    </row>
-    <row r="66" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-      <c r="L66" s="8"/>
-      <c r="N66" s="8"/>
-      <c r="O66" s="8"/>
-      <c r="P66" s="8"/>
-      <c r="T66" s="8"/>
-    </row>
-    <row r="67" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I67" s="8"/>
-      <c r="J67" s="8"/>
-      <c r="L67" s="8"/>
-      <c r="N67" s="8"/>
-      <c r="O67" s="8"/>
-      <c r="P67" s="8"/>
-      <c r="T67" s="8"/>
-    </row>
-    <row r="68" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="N68" s="8"/>
-      <c r="O68" s="8"/>
-      <c r="P68" s="8"/>
-      <c r="T68" s="8"/>
-    </row>
-    <row r="69" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="L69" s="8"/>
-      <c r="N69" s="8"/>
-      <c r="O69" s="8"/>
-      <c r="P69" s="8"/>
-      <c r="T69" s="8"/>
-    </row>
-    <row r="70" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="O70" s="8"/>
-      <c r="T70" s="8"/>
-    </row>
-    <row r="71" spans="9:20" x14ac:dyDescent="0.25">
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="N71" s="8"/>
-      <c r="O71" s="8"/>
-      <c r="P71" s="8"/>
-      <c r="T71" s="8"/>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>